--- a/frontend/static/templates/PM_Task_Plan_Template.xlsx
+++ b/frontend/static/templates/PM_Task_Plan_Template.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:C23"/>
+  <dimension ref="A2:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3" customWidth="1" style="27" min="1" max="1"/>
@@ -567,108 +567,108 @@
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" s="27">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Equipment type</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Pick from the dropdown (Inverter, Transformer, VCB Panel, OLTC(RTCC), WMS…). If not listed, pick "Other".</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1" s="27">
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Plant(s)</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Which plant this task is for, written exactly as in the portal. For several plants, separate with commas: Kerli, Nagaur. Write All plants for every plant. Leave blank to assign the plant later.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="31.5" customHeight="1" s="27">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Task – what to do</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Short name of the job. Example: "Clean inverter cooling fans and filters".</t>
         </is>
       </c>
     </row>
     <row r="9" ht="31.5" customHeight="1" s="27">
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>How to do it</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Steps / checklist in plain words. Example: "1. Isolate. 2. Open cover. 3. Clean filter. 4. Record temperature."</t>
         </is>
       </c>
     </row>
     <row r="10" ht="31.5" customHeight="1" s="27">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Frequency – when</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Pick how often: Daily, Weekly, Monthly, Quarterly, Half-yearly or Annual.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="31.5" customHeight="1" s="27">
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Start date</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>First date the task is due. Type as DD-MM-YYYY or YYYY-MM-DD. Next dates are calculated from Frequency.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="31.5" customHeight="1" s="27">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Assignee(s)</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Name of the O&amp;M team member. For more than one person, separate with commas: Ravi Kumar, Anita Sharma.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="31.5" customHeight="1" s="27">
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Safety needed</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Pick from the dropdown: — (none), PTW required, LOTO required, or PTW + LOTO required.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="31.5" customHeight="1" s="27">
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Est. time (hours)</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Approximate hours the task takes, as a number such as 2 or 0.5.</t>
         </is>
@@ -698,64 +698,75 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="B18" s="10" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Remarks (optional)</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>What is going on right now, in plain words (e.g. 'Spare filters ordered; fans at INV-04 noisy'). Added to the log of every task the row creates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="30" customHeight="1" s="27">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>How rows become tasks</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Each row creates one task for every plant listed and every assignee listed — or, when units are known, one task per unit for each plant, spread across days by Units per day. One assignee looks after all units of a plant.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" s="27"/>
-    <row r="20" ht="30" customHeight="1" s="27">
-      <c r="B20" s="10" t="inlineStr">
+    <row r="20" ht="30" customHeight="1" s="27"/>
+    <row r="21" ht="30" customHeight="1" s="27">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1" s="27">
-      <c r="B21" s="13" t="inlineStr">
+    <row r="22" ht="15.75" customHeight="1" s="27">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Yellow cells</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Cells for you to fill in on the "PM Tasks" sheet.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="27">
-      <c r="B22" s="16" t="inlineStr">
+    <row r="23" ht="15.75" customHeight="1" s="27">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Grey row</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Row 2 is an EXAMPLE of the format. Overwrite or delete it — rows starting with "EXAMPLE" are ignored on import.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="27">
-      <c r="B23" s="18" t="inlineStr">
+    <row r="24" ht="15.75" customHeight="1" s="27">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>Need ideas?</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>See the "Task ideas" sheet for common checks for each equipment type.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="27"/>
     <row r="25" ht="15.75" customHeight="1" s="27"/>
     <row r="26" ht="15.75" customHeight="1" s="27"/>
     <row r="27" ht="15.75" customHeight="1" s="27"/>
@@ -1744,7 +1755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K301"/>
+  <dimension ref="A1:L301"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24" customWidth="1" style="27" min="1" max="1"/>
@@ -1758,40 +1769,41 @@
     <col width="16" customWidth="1" style="27" min="9" max="9"/>
     <col width="14" customWidth="1" style="27" min="10" max="10"/>
     <col width="14" customWidth="1" style="27" min="11" max="11"/>
+    <col width="40" customWidth="1" style="27" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="27">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>Equipment type</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Plant(s)</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Task – what to do</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Frequency – when</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Assignee(s)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>Safety needed</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="30" t="inlineStr">
         <is>
           <t>Est. time (hours)</t>
         </is>
@@ -1816,14 +1828,19 @@
           <t>Units per day</t>
         </is>
       </c>
+      <c r="L1" s="30" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>Kerli, Nagaur</t>
         </is>
@@ -1833,22 +1850,22 @@
           <t>EXAMPLE – Clean inverter cooling fans and filters</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>Ravi Kumar, Anita Sharma</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr">
         <is>
           <t>PTW + LOTO required</t>
         </is>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="31" t="n">
         <v>2</v>
       </c>
       <c r="H2" s="31" t="inlineStr">
@@ -1862,6 +1879,11 @@
       </c>
       <c r="K2" s="31" t="n">
         <v>2</v>
+      </c>
+      <c r="L2" s="31" t="inlineStr">
+        <is>
+          <t>Spare filters ordered; fans at INV-04 noisy</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1869,2834 +1891,3052 @@
       <c r="B3" s="12" t="n"/>
       <c r="C3" s="15" t="n"/>
       <c r="D3" s="15" t="n"/>
-      <c r="E3" s="21" t="n"/>
+      <c r="E3" s="32" t="n"/>
       <c r="F3" s="15" t="n"/>
-      <c r="G3" s="21" t="n"/>
+      <c r="G3" s="32" t="n"/>
       <c r="H3" s="32" t="n"/>
       <c r="I3" s="32" t="n"/>
       <c r="J3" s="32" t="n"/>
       <c r="K3" s="32" t="n"/>
+      <c r="L3" s="32" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="n"/>
       <c r="B4" s="22" t="n"/>
       <c r="C4" s="15" t="n"/>
       <c r="D4" s="15" t="n"/>
-      <c r="E4" s="21" t="n"/>
+      <c r="E4" s="32" t="n"/>
       <c r="F4" s="15" t="n"/>
-      <c r="G4" s="21" t="n"/>
+      <c r="G4" s="32" t="n"/>
       <c r="H4" s="32" t="n"/>
       <c r="I4" s="32" t="n"/>
       <c r="J4" s="32" t="n"/>
       <c r="K4" s="32" t="n"/>
+      <c r="L4" s="32" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n"/>
       <c r="B5" s="22" t="n"/>
       <c r="C5" s="15" t="n"/>
       <c r="D5" s="15" t="n"/>
-      <c r="E5" s="21" t="n"/>
+      <c r="E5" s="32" t="n"/>
       <c r="F5" s="15" t="n"/>
-      <c r="G5" s="21" t="n"/>
+      <c r="G5" s="32" t="n"/>
       <c r="H5" s="32" t="n"/>
       <c r="I5" s="32" t="n"/>
       <c r="J5" s="32" t="n"/>
       <c r="K5" s="32" t="n"/>
+      <c r="L5" s="32" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="12" t="n"/>
       <c r="C6" s="15" t="n"/>
       <c r="D6" s="15" t="n"/>
-      <c r="E6" s="21" t="n"/>
+      <c r="E6" s="32" t="n"/>
       <c r="F6" s="15" t="n"/>
-      <c r="G6" s="21" t="n"/>
+      <c r="G6" s="32" t="n"/>
       <c r="H6" s="32" t="n"/>
       <c r="I6" s="32" t="n"/>
       <c r="J6" s="32" t="n"/>
       <c r="K6" s="32" t="n"/>
+      <c r="L6" s="32" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n"/>
       <c r="B7" s="12" t="n"/>
       <c r="C7" s="15" t="n"/>
       <c r="D7" s="15" t="n"/>
-      <c r="E7" s="21" t="n"/>
+      <c r="E7" s="32" t="n"/>
       <c r="F7" s="15" t="n"/>
-      <c r="G7" s="21" t="n"/>
+      <c r="G7" s="32" t="n"/>
       <c r="H7" s="32" t="n"/>
       <c r="I7" s="32" t="n"/>
       <c r="J7" s="32" t="n"/>
       <c r="K7" s="32" t="n"/>
+      <c r="L7" s="32" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n"/>
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="15" t="n"/>
       <c r="D8" s="15" t="n"/>
-      <c r="E8" s="21" t="n"/>
+      <c r="E8" s="32" t="n"/>
       <c r="F8" s="15" t="n"/>
-      <c r="G8" s="21" t="n"/>
+      <c r="G8" s="32" t="n"/>
       <c r="H8" s="32" t="n"/>
       <c r="I8" s="32" t="n"/>
       <c r="J8" s="32" t="n"/>
       <c r="K8" s="32" t="n"/>
+      <c r="L8" s="32" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n"/>
       <c r="B9" s="12" t="n"/>
       <c r="C9" s="15" t="n"/>
       <c r="D9" s="15" t="n"/>
-      <c r="E9" s="21" t="n"/>
+      <c r="E9" s="32" t="n"/>
       <c r="F9" s="15" t="n"/>
-      <c r="G9" s="21" t="n"/>
+      <c r="G9" s="32" t="n"/>
       <c r="H9" s="32" t="n"/>
       <c r="I9" s="32" t="n"/>
       <c r="J9" s="32" t="n"/>
       <c r="K9" s="32" t="n"/>
+      <c r="L9" s="32" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n"/>
       <c r="B10" s="12" t="n"/>
       <c r="C10" s="15" t="n"/>
       <c r="D10" s="15" t="n"/>
-      <c r="E10" s="21" t="n"/>
+      <c r="E10" s="32" t="n"/>
       <c r="F10" s="15" t="n"/>
-      <c r="G10" s="21" t="n"/>
+      <c r="G10" s="32" t="n"/>
       <c r="H10" s="32" t="n"/>
       <c r="I10" s="32" t="n"/>
       <c r="J10" s="32" t="n"/>
       <c r="K10" s="32" t="n"/>
+      <c r="L10" s="32" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n"/>
       <c r="B11" s="12" t="n"/>
       <c r="C11" s="15" t="n"/>
       <c r="D11" s="15" t="n"/>
-      <c r="E11" s="21" t="n"/>
+      <c r="E11" s="32" t="n"/>
       <c r="F11" s="15" t="n"/>
-      <c r="G11" s="21" t="n"/>
+      <c r="G11" s="32" t="n"/>
       <c r="H11" s="32" t="n"/>
       <c r="I11" s="32" t="n"/>
       <c r="J11" s="32" t="n"/>
       <c r="K11" s="32" t="n"/>
+      <c r="L11" s="32" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n"/>
       <c r="B12" s="12" t="n"/>
       <c r="C12" s="15" t="n"/>
       <c r="D12" s="15" t="n"/>
-      <c r="E12" s="21" t="n"/>
+      <c r="E12" s="32" t="n"/>
       <c r="F12" s="15" t="n"/>
-      <c r="G12" s="21" t="n"/>
+      <c r="G12" s="32" t="n"/>
       <c r="H12" s="32" t="n"/>
       <c r="I12" s="32" t="n"/>
       <c r="J12" s="32" t="n"/>
       <c r="K12" s="32" t="n"/>
+      <c r="L12" s="32" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n"/>
       <c r="B13" s="12" t="n"/>
       <c r="C13" s="15" t="n"/>
       <c r="D13" s="15" t="n"/>
-      <c r="E13" s="21" t="n"/>
+      <c r="E13" s="32" t="n"/>
       <c r="F13" s="15" t="n"/>
-      <c r="G13" s="21" t="n"/>
+      <c r="G13" s="32" t="n"/>
       <c r="H13" s="32" t="n"/>
       <c r="I13" s="32" t="n"/>
       <c r="J13" s="32" t="n"/>
       <c r="K13" s="32" t="n"/>
+      <c r="L13" s="32" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n"/>
       <c r="B14" s="12" t="n"/>
       <c r="C14" s="15" t="n"/>
       <c r="D14" s="15" t="n"/>
-      <c r="E14" s="21" t="n"/>
+      <c r="E14" s="32" t="n"/>
       <c r="F14" s="15" t="n"/>
-      <c r="G14" s="21" t="n"/>
+      <c r="G14" s="32" t="n"/>
       <c r="H14" s="32" t="n"/>
       <c r="I14" s="32" t="n"/>
       <c r="J14" s="32" t="n"/>
       <c r="K14" s="32" t="n"/>
+      <c r="L14" s="32" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n"/>
       <c r="B15" s="12" t="n"/>
       <c r="C15" s="15" t="n"/>
       <c r="D15" s="15" t="n"/>
-      <c r="E15" s="21" t="n"/>
+      <c r="E15" s="32" t="n"/>
       <c r="F15" s="15" t="n"/>
-      <c r="G15" s="21" t="n"/>
+      <c r="G15" s="32" t="n"/>
       <c r="H15" s="32" t="n"/>
       <c r="I15" s="32" t="n"/>
       <c r="J15" s="32" t="n"/>
       <c r="K15" s="32" t="n"/>
+      <c r="L15" s="32" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n"/>
       <c r="B16" s="12" t="n"/>
       <c r="C16" s="15" t="n"/>
       <c r="D16" s="15" t="n"/>
-      <c r="E16" s="21" t="n"/>
+      <c r="E16" s="32" t="n"/>
       <c r="F16" s="15" t="n"/>
-      <c r="G16" s="21" t="n"/>
+      <c r="G16" s="32" t="n"/>
       <c r="H16" s="32" t="n"/>
       <c r="I16" s="32" t="n"/>
       <c r="J16" s="32" t="n"/>
       <c r="K16" s="32" t="n"/>
+      <c r="L16" s="32" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n"/>
       <c r="B17" s="12" t="n"/>
       <c r="C17" s="15" t="n"/>
       <c r="D17" s="15" t="n"/>
-      <c r="E17" s="21" t="n"/>
+      <c r="E17" s="32" t="n"/>
       <c r="F17" s="15" t="n"/>
-      <c r="G17" s="21" t="n"/>
+      <c r="G17" s="32" t="n"/>
       <c r="H17" s="32" t="n"/>
       <c r="I17" s="32" t="n"/>
       <c r="J17" s="32" t="n"/>
       <c r="K17" s="32" t="n"/>
+      <c r="L17" s="32" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n"/>
       <c r="B18" s="12" t="n"/>
       <c r="C18" s="15" t="n"/>
       <c r="D18" s="15" t="n"/>
-      <c r="E18" s="21" t="n"/>
+      <c r="E18" s="32" t="n"/>
       <c r="F18" s="15" t="n"/>
-      <c r="G18" s="21" t="n"/>
+      <c r="G18" s="32" t="n"/>
       <c r="H18" s="32" t="n"/>
       <c r="I18" s="32" t="n"/>
       <c r="J18" s="32" t="n"/>
       <c r="K18" s="32" t="n"/>
+      <c r="L18" s="32" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n"/>
       <c r="B19" s="12" t="n"/>
       <c r="C19" s="15" t="n"/>
       <c r="D19" s="15" t="n"/>
-      <c r="E19" s="21" t="n"/>
+      <c r="E19" s="32" t="n"/>
       <c r="F19" s="15" t="n"/>
-      <c r="G19" s="21" t="n"/>
+      <c r="G19" s="32" t="n"/>
       <c r="H19" s="32" t="n"/>
       <c r="I19" s="32" t="n"/>
       <c r="J19" s="32" t="n"/>
       <c r="K19" s="32" t="n"/>
+      <c r="L19" s="32" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n"/>
       <c r="B20" s="12" t="n"/>
       <c r="C20" s="15" t="n"/>
       <c r="D20" s="15" t="n"/>
-      <c r="E20" s="21" t="n"/>
+      <c r="E20" s="32" t="n"/>
       <c r="F20" s="15" t="n"/>
-      <c r="G20" s="21" t="n"/>
+      <c r="G20" s="32" t="n"/>
       <c r="H20" s="32" t="n"/>
       <c r="I20" s="32" t="n"/>
       <c r="J20" s="32" t="n"/>
       <c r="K20" s="32" t="n"/>
+      <c r="L20" s="32" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="27">
       <c r="A21" s="9" t="n"/>
       <c r="B21" s="12" t="n"/>
       <c r="C21" s="15" t="n"/>
       <c r="D21" s="15" t="n"/>
-      <c r="E21" s="21" t="n"/>
+      <c r="E21" s="32" t="n"/>
       <c r="F21" s="15" t="n"/>
-      <c r="G21" s="21" t="n"/>
+      <c r="G21" s="32" t="n"/>
       <c r="H21" s="32" t="n"/>
       <c r="I21" s="32" t="n"/>
       <c r="J21" s="32" t="n"/>
       <c r="K21" s="32" t="n"/>
+      <c r="L21" s="32" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="27">
       <c r="A22" s="9" t="n"/>
       <c r="B22" s="12" t="n"/>
       <c r="C22" s="15" t="n"/>
       <c r="D22" s="15" t="n"/>
-      <c r="E22" s="21" t="n"/>
+      <c r="E22" s="32" t="n"/>
       <c r="F22" s="15" t="n"/>
-      <c r="G22" s="21" t="n"/>
+      <c r="G22" s="32" t="n"/>
       <c r="H22" s="32" t="n"/>
       <c r="I22" s="32" t="n"/>
       <c r="J22" s="32" t="n"/>
       <c r="K22" s="32" t="n"/>
+      <c r="L22" s="32" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="27">
       <c r="A23" s="9" t="n"/>
       <c r="B23" s="12" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="15" t="n"/>
-      <c r="E23" s="21" t="n"/>
+      <c r="E23" s="32" t="n"/>
       <c r="F23" s="15" t="n"/>
-      <c r="G23" s="21" t="n"/>
+      <c r="G23" s="32" t="n"/>
       <c r="H23" s="32" t="n"/>
       <c r="I23" s="32" t="n"/>
       <c r="J23" s="32" t="n"/>
       <c r="K23" s="32" t="n"/>
+      <c r="L23" s="32" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="27">
       <c r="A24" s="9" t="n"/>
       <c r="B24" s="12" t="n"/>
       <c r="C24" s="15" t="n"/>
       <c r="D24" s="15" t="n"/>
-      <c r="E24" s="21" t="n"/>
+      <c r="E24" s="32" t="n"/>
       <c r="F24" s="15" t="n"/>
-      <c r="G24" s="21" t="n"/>
+      <c r="G24" s="32" t="n"/>
       <c r="H24" s="32" t="n"/>
       <c r="I24" s="32" t="n"/>
       <c r="J24" s="32" t="n"/>
       <c r="K24" s="32" t="n"/>
+      <c r="L24" s="32" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="27">
       <c r="A25" s="9" t="n"/>
       <c r="B25" s="12" t="n"/>
       <c r="C25" s="15" t="n"/>
       <c r="D25" s="15" t="n"/>
-      <c r="E25" s="21" t="n"/>
+      <c r="E25" s="32" t="n"/>
       <c r="F25" s="15" t="n"/>
-      <c r="G25" s="21" t="n"/>
+      <c r="G25" s="32" t="n"/>
       <c r="H25" s="32" t="n"/>
       <c r="I25" s="32" t="n"/>
       <c r="J25" s="32" t="n"/>
       <c r="K25" s="32" t="n"/>
+      <c r="L25" s="32" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="27">
       <c r="A26" s="9" t="n"/>
       <c r="B26" s="12" t="n"/>
       <c r="C26" s="15" t="n"/>
       <c r="D26" s="15" t="n"/>
-      <c r="E26" s="21" t="n"/>
+      <c r="E26" s="32" t="n"/>
       <c r="F26" s="15" t="n"/>
-      <c r="G26" s="21" t="n"/>
+      <c r="G26" s="32" t="n"/>
       <c r="H26" s="32" t="n"/>
       <c r="I26" s="32" t="n"/>
       <c r="J26" s="32" t="n"/>
       <c r="K26" s="32" t="n"/>
+      <c r="L26" s="32" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="27">
       <c r="A27" s="9" t="n"/>
       <c r="B27" s="12" t="n"/>
       <c r="C27" s="15" t="n"/>
       <c r="D27" s="15" t="n"/>
-      <c r="E27" s="21" t="n"/>
+      <c r="E27" s="32" t="n"/>
       <c r="F27" s="15" t="n"/>
-      <c r="G27" s="21" t="n"/>
+      <c r="G27" s="32" t="n"/>
       <c r="H27" s="32" t="n"/>
       <c r="I27" s="32" t="n"/>
       <c r="J27" s="32" t="n"/>
       <c r="K27" s="32" t="n"/>
+      <c r="L27" s="32" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="27">
       <c r="A28" s="9" t="n"/>
       <c r="B28" s="12" t="n"/>
       <c r="C28" s="15" t="n"/>
       <c r="D28" s="15" t="n"/>
-      <c r="E28" s="21" t="n"/>
+      <c r="E28" s="32" t="n"/>
       <c r="F28" s="15" t="n"/>
-      <c r="G28" s="21" t="n"/>
+      <c r="G28" s="32" t="n"/>
       <c r="H28" s="32" t="n"/>
       <c r="I28" s="32" t="n"/>
       <c r="J28" s="32" t="n"/>
       <c r="K28" s="32" t="n"/>
+      <c r="L28" s="32" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="27">
       <c r="A29" s="9" t="n"/>
       <c r="B29" s="12" t="n"/>
       <c r="C29" s="15" t="n"/>
       <c r="D29" s="15" t="n"/>
-      <c r="E29" s="21" t="n"/>
+      <c r="E29" s="32" t="n"/>
       <c r="F29" s="15" t="n"/>
-      <c r="G29" s="21" t="n"/>
+      <c r="G29" s="32" t="n"/>
       <c r="H29" s="32" t="n"/>
       <c r="I29" s="32" t="n"/>
       <c r="J29" s="32" t="n"/>
       <c r="K29" s="32" t="n"/>
+      <c r="L29" s="32" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="27">
       <c r="A30" s="9" t="n"/>
       <c r="B30" s="12" t="n"/>
       <c r="C30" s="15" t="n"/>
       <c r="D30" s="15" t="n"/>
-      <c r="E30" s="21" t="n"/>
+      <c r="E30" s="32" t="n"/>
       <c r="F30" s="15" t="n"/>
-      <c r="G30" s="21" t="n"/>
+      <c r="G30" s="32" t="n"/>
       <c r="H30" s="32" t="n"/>
       <c r="I30" s="32" t="n"/>
       <c r="J30" s="32" t="n"/>
       <c r="K30" s="32" t="n"/>
+      <c r="L30" s="32" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="27">
       <c r="A31" s="9" t="n"/>
       <c r="B31" s="12" t="n"/>
       <c r="C31" s="15" t="n"/>
       <c r="D31" s="15" t="n"/>
-      <c r="E31" s="21" t="n"/>
+      <c r="E31" s="32" t="n"/>
       <c r="F31" s="15" t="n"/>
-      <c r="G31" s="21" t="n"/>
+      <c r="G31" s="32" t="n"/>
       <c r="H31" s="32" t="n"/>
       <c r="I31" s="32" t="n"/>
       <c r="J31" s="32" t="n"/>
       <c r="K31" s="32" t="n"/>
+      <c r="L31" s="32" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="27">
       <c r="A32" s="9" t="n"/>
       <c r="B32" s="12" t="n"/>
       <c r="C32" s="15" t="n"/>
       <c r="D32" s="15" t="n"/>
-      <c r="E32" s="21" t="n"/>
+      <c r="E32" s="32" t="n"/>
       <c r="F32" s="15" t="n"/>
-      <c r="G32" s="21" t="n"/>
+      <c r="G32" s="32" t="n"/>
       <c r="H32" s="32" t="n"/>
       <c r="I32" s="32" t="n"/>
       <c r="J32" s="32" t="n"/>
       <c r="K32" s="32" t="n"/>
+      <c r="L32" s="32" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="27">
       <c r="A33" s="9" t="n"/>
       <c r="B33" s="12" t="n"/>
       <c r="C33" s="15" t="n"/>
       <c r="D33" s="15" t="n"/>
-      <c r="E33" s="21" t="n"/>
+      <c r="E33" s="32" t="n"/>
       <c r="F33" s="15" t="n"/>
-      <c r="G33" s="21" t="n"/>
+      <c r="G33" s="32" t="n"/>
       <c r="H33" s="32" t="n"/>
       <c r="I33" s="32" t="n"/>
       <c r="J33" s="32" t="n"/>
       <c r="K33" s="32" t="n"/>
+      <c r="L33" s="32" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="27">
       <c r="A34" s="9" t="n"/>
       <c r="B34" s="12" t="n"/>
       <c r="C34" s="15" t="n"/>
       <c r="D34" s="15" t="n"/>
-      <c r="E34" s="21" t="n"/>
+      <c r="E34" s="32" t="n"/>
       <c r="F34" s="15" t="n"/>
-      <c r="G34" s="21" t="n"/>
+      <c r="G34" s="32" t="n"/>
       <c r="H34" s="32" t="n"/>
       <c r="I34" s="32" t="n"/>
       <c r="J34" s="32" t="n"/>
       <c r="K34" s="32" t="n"/>
+      <c r="L34" s="32" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="27">
       <c r="A35" s="9" t="n"/>
       <c r="B35" s="12" t="n"/>
       <c r="C35" s="15" t="n"/>
       <c r="D35" s="15" t="n"/>
-      <c r="E35" s="21" t="n"/>
+      <c r="E35" s="32" t="n"/>
       <c r="F35" s="15" t="n"/>
-      <c r="G35" s="21" t="n"/>
+      <c r="G35" s="32" t="n"/>
       <c r="H35" s="32" t="n"/>
       <c r="I35" s="32" t="n"/>
       <c r="J35" s="32" t="n"/>
       <c r="K35" s="32" t="n"/>
+      <c r="L35" s="32" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="27">
       <c r="A36" s="9" t="n"/>
       <c r="B36" s="24" t="n"/>
       <c r="C36" s="15" t="n"/>
       <c r="D36" s="15" t="n"/>
-      <c r="E36" s="21" t="n"/>
+      <c r="E36" s="32" t="n"/>
       <c r="F36" s="15" t="n"/>
-      <c r="G36" s="21" t="n"/>
+      <c r="G36" s="32" t="n"/>
       <c r="H36" s="32" t="n"/>
       <c r="I36" s="32" t="n"/>
       <c r="J36" s="32" t="n"/>
       <c r="K36" s="32" t="n"/>
+      <c r="L36" s="32" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="27">
       <c r="A37" s="9" t="n"/>
       <c r="B37" s="12" t="n"/>
       <c r="C37" s="15" t="n"/>
       <c r="D37" s="15" t="n"/>
-      <c r="E37" s="21" t="n"/>
+      <c r="E37" s="32" t="n"/>
       <c r="F37" s="15" t="n"/>
-      <c r="G37" s="21" t="n"/>
+      <c r="G37" s="32" t="n"/>
       <c r="H37" s="32" t="n"/>
       <c r="I37" s="32" t="n"/>
       <c r="J37" s="32" t="n"/>
       <c r="K37" s="32" t="n"/>
+      <c r="L37" s="32" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="27">
       <c r="A38" s="9" t="n"/>
       <c r="B38" s="25" t="n"/>
       <c r="C38" s="15" t="n"/>
       <c r="D38" s="15" t="n"/>
-      <c r="E38" s="21" t="n"/>
+      <c r="E38" s="32" t="n"/>
       <c r="F38" s="15" t="n"/>
-      <c r="G38" s="21" t="n"/>
+      <c r="G38" s="32" t="n"/>
       <c r="H38" s="32" t="n"/>
       <c r="I38" s="32" t="n"/>
       <c r="J38" s="32" t="n"/>
       <c r="K38" s="32" t="n"/>
+      <c r="L38" s="32" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="27">
       <c r="A39" s="9" t="n"/>
       <c r="B39" s="25" t="n"/>
       <c r="C39" s="15" t="n"/>
       <c r="D39" s="15" t="n"/>
-      <c r="E39" s="21" t="n"/>
+      <c r="E39" s="32" t="n"/>
       <c r="F39" s="15" t="n"/>
-      <c r="G39" s="21" t="n"/>
+      <c r="G39" s="32" t="n"/>
       <c r="H39" s="32" t="n"/>
       <c r="I39" s="32" t="n"/>
       <c r="J39" s="32" t="n"/>
       <c r="K39" s="32" t="n"/>
+      <c r="L39" s="32" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="27">
       <c r="A40" s="9" t="n"/>
       <c r="B40" s="25" t="n"/>
       <c r="C40" s="15" t="n"/>
       <c r="D40" s="15" t="n"/>
-      <c r="E40" s="21" t="n"/>
+      <c r="E40" s="32" t="n"/>
       <c r="F40" s="15" t="n"/>
-      <c r="G40" s="21" t="n"/>
+      <c r="G40" s="32" t="n"/>
       <c r="H40" s="32" t="n"/>
       <c r="I40" s="32" t="n"/>
       <c r="J40" s="32" t="n"/>
       <c r="K40" s="32" t="n"/>
+      <c r="L40" s="32" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="27">
       <c r="A41" s="9" t="n"/>
       <c r="B41" s="25" t="n"/>
       <c r="C41" s="15" t="n"/>
       <c r="D41" s="15" t="n"/>
-      <c r="E41" s="21" t="n"/>
+      <c r="E41" s="32" t="n"/>
       <c r="F41" s="15" t="n"/>
-      <c r="G41" s="21" t="n"/>
+      <c r="G41" s="32" t="n"/>
       <c r="H41" s="32" t="n"/>
       <c r="I41" s="32" t="n"/>
       <c r="J41" s="32" t="n"/>
       <c r="K41" s="32" t="n"/>
+      <c r="L41" s="32" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="27">
       <c r="A42" s="9" t="n"/>
       <c r="B42" s="25" t="n"/>
       <c r="C42" s="15" t="n"/>
       <c r="D42" s="15" t="n"/>
-      <c r="E42" s="21" t="n"/>
+      <c r="E42" s="32" t="n"/>
       <c r="F42" s="15" t="n"/>
-      <c r="G42" s="21" t="n"/>
+      <c r="G42" s="32" t="n"/>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="32" t="n"/>
       <c r="J42" s="32" t="n"/>
       <c r="K42" s="32" t="n"/>
+      <c r="L42" s="32" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="27">
-      <c r="A43" s="21" t="n"/>
-      <c r="B43" s="21" t="n"/>
-      <c r="C43" s="21" t="n"/>
-      <c r="D43" s="21" t="n"/>
-      <c r="E43" s="21" t="n"/>
-      <c r="F43" s="21" t="n"/>
-      <c r="G43" s="21" t="n"/>
+      <c r="A43" s="32" t="n"/>
+      <c r="B43" s="32" t="n"/>
+      <c r="C43" s="32" t="n"/>
+      <c r="D43" s="32" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="32" t="n"/>
       <c r="H43" s="32" t="n"/>
       <c r="I43" s="32" t="n"/>
       <c r="J43" s="32" t="n"/>
       <c r="K43" s="32" t="n"/>
+      <c r="L43" s="32" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="27">
-      <c r="A44" s="21" t="n"/>
-      <c r="B44" s="21" t="n"/>
-      <c r="C44" s="21" t="n"/>
-      <c r="D44" s="21" t="n"/>
-      <c r="E44" s="21" t="n"/>
-      <c r="F44" s="21" t="n"/>
-      <c r="G44" s="21" t="n"/>
+      <c r="A44" s="32" t="n"/>
+      <c r="B44" s="32" t="n"/>
+      <c r="C44" s="32" t="n"/>
+      <c r="D44" s="32" t="n"/>
+      <c r="E44" s="32" t="n"/>
+      <c r="F44" s="32" t="n"/>
+      <c r="G44" s="32" t="n"/>
       <c r="H44" s="32" t="n"/>
       <c r="I44" s="32" t="n"/>
       <c r="J44" s="32" t="n"/>
       <c r="K44" s="32" t="n"/>
+      <c r="L44" s="32" t="n"/>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="27">
-      <c r="A45" s="21" t="n"/>
-      <c r="B45" s="21" t="n"/>
-      <c r="C45" s="21" t="n"/>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="21" t="n"/>
-      <c r="F45" s="21" t="n"/>
-      <c r="G45" s="21" t="n"/>
+      <c r="A45" s="32" t="n"/>
+      <c r="B45" s="32" t="n"/>
+      <c r="C45" s="32" t="n"/>
+      <c r="D45" s="32" t="n"/>
+      <c r="E45" s="32" t="n"/>
+      <c r="F45" s="32" t="n"/>
+      <c r="G45" s="32" t="n"/>
       <c r="H45" s="32" t="n"/>
       <c r="I45" s="32" t="n"/>
       <c r="J45" s="32" t="n"/>
       <c r="K45" s="32" t="n"/>
+      <c r="L45" s="32" t="n"/>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="27">
-      <c r="A46" s="21" t="n"/>
-      <c r="B46" s="21" t="n"/>
-      <c r="C46" s="21" t="n"/>
-      <c r="D46" s="21" t="n"/>
-      <c r="E46" s="21" t="n"/>
-      <c r="F46" s="21" t="n"/>
-      <c r="G46" s="21" t="n"/>
+      <c r="A46" s="32" t="n"/>
+      <c r="B46" s="32" t="n"/>
+      <c r="C46" s="32" t="n"/>
+      <c r="D46" s="32" t="n"/>
+      <c r="E46" s="32" t="n"/>
+      <c r="F46" s="32" t="n"/>
+      <c r="G46" s="32" t="n"/>
       <c r="H46" s="32" t="n"/>
       <c r="I46" s="32" t="n"/>
       <c r="J46" s="32" t="n"/>
       <c r="K46" s="32" t="n"/>
+      <c r="L46" s="32" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="27">
-      <c r="A47" s="21" t="n"/>
-      <c r="B47" s="21" t="n"/>
-      <c r="C47" s="21" t="n"/>
-      <c r="D47" s="21" t="n"/>
-      <c r="E47" s="21" t="n"/>
-      <c r="F47" s="21" t="n"/>
-      <c r="G47" s="21" t="n"/>
+      <c r="A47" s="32" t="n"/>
+      <c r="B47" s="32" t="n"/>
+      <c r="C47" s="32" t="n"/>
+      <c r="D47" s="32" t="n"/>
+      <c r="E47" s="32" t="n"/>
+      <c r="F47" s="32" t="n"/>
+      <c r="G47" s="32" t="n"/>
       <c r="H47" s="32" t="n"/>
       <c r="I47" s="32" t="n"/>
       <c r="J47" s="32" t="n"/>
       <c r="K47" s="32" t="n"/>
+      <c r="L47" s="32" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="27">
-      <c r="A48" s="21" t="n"/>
-      <c r="B48" s="21" t="n"/>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="21" t="n"/>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="21" t="n"/>
+      <c r="A48" s="32" t="n"/>
+      <c r="B48" s="32" t="n"/>
+      <c r="C48" s="32" t="n"/>
+      <c r="D48" s="32" t="n"/>
+      <c r="E48" s="32" t="n"/>
+      <c r="F48" s="32" t="n"/>
+      <c r="G48" s="32" t="n"/>
       <c r="H48" s="32" t="n"/>
       <c r="I48" s="32" t="n"/>
       <c r="J48" s="32" t="n"/>
       <c r="K48" s="32" t="n"/>
+      <c r="L48" s="32" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="27">
-      <c r="A49" s="21" t="n"/>
-      <c r="B49" s="21" t="n"/>
-      <c r="C49" s="21" t="n"/>
-      <c r="D49" s="21" t="n"/>
-      <c r="E49" s="21" t="n"/>
-      <c r="F49" s="21" t="n"/>
-      <c r="G49" s="21" t="n"/>
+      <c r="A49" s="32" t="n"/>
+      <c r="B49" s="32" t="n"/>
+      <c r="C49" s="32" t="n"/>
+      <c r="D49" s="32" t="n"/>
+      <c r="E49" s="32" t="n"/>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="32" t="n"/>
       <c r="H49" s="32" t="n"/>
       <c r="I49" s="32" t="n"/>
       <c r="J49" s="32" t="n"/>
       <c r="K49" s="32" t="n"/>
+      <c r="L49" s="32" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="27">
-      <c r="A50" s="21" t="n"/>
-      <c r="B50" s="21" t="n"/>
-      <c r="C50" s="21" t="n"/>
-      <c r="D50" s="21" t="n"/>
-      <c r="E50" s="21" t="n"/>
-      <c r="F50" s="21" t="n"/>
-      <c r="G50" s="21" t="n"/>
+      <c r="A50" s="32" t="n"/>
+      <c r="B50" s="32" t="n"/>
+      <c r="C50" s="32" t="n"/>
+      <c r="D50" s="32" t="n"/>
+      <c r="E50" s="32" t="n"/>
+      <c r="F50" s="32" t="n"/>
+      <c r="G50" s="32" t="n"/>
       <c r="H50" s="32" t="n"/>
       <c r="I50" s="32" t="n"/>
       <c r="J50" s="32" t="n"/>
       <c r="K50" s="32" t="n"/>
+      <c r="L50" s="32" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="27">
-      <c r="A51" s="21" t="n"/>
-      <c r="B51" s="21" t="n"/>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="21" t="n"/>
-      <c r="E51" s="21" t="n"/>
-      <c r="F51" s="21" t="n"/>
-      <c r="G51" s="21" t="n"/>
+      <c r="A51" s="32" t="n"/>
+      <c r="B51" s="32" t="n"/>
+      <c r="C51" s="32" t="n"/>
+      <c r="D51" s="32" t="n"/>
+      <c r="E51" s="32" t="n"/>
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="32" t="n"/>
       <c r="H51" s="32" t="n"/>
       <c r="I51" s="32" t="n"/>
       <c r="J51" s="32" t="n"/>
       <c r="K51" s="32" t="n"/>
+      <c r="L51" s="32" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="27">
-      <c r="A52" s="21" t="n"/>
-      <c r="B52" s="21" t="n"/>
-      <c r="C52" s="21" t="n"/>
-      <c r="D52" s="21" t="n"/>
-      <c r="E52" s="21" t="n"/>
-      <c r="F52" s="21" t="n"/>
-      <c r="G52" s="21" t="n"/>
+      <c r="A52" s="32" t="n"/>
+      <c r="B52" s="32" t="n"/>
+      <c r="C52" s="32" t="n"/>
+      <c r="D52" s="32" t="n"/>
+      <c r="E52" s="32" t="n"/>
+      <c r="F52" s="32" t="n"/>
+      <c r="G52" s="32" t="n"/>
       <c r="H52" s="32" t="n"/>
       <c r="I52" s="32" t="n"/>
       <c r="J52" s="32" t="n"/>
       <c r="K52" s="32" t="n"/>
+      <c r="L52" s="32" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="27">
-      <c r="A53" s="21" t="n"/>
-      <c r="B53" s="21" t="n"/>
-      <c r="C53" s="21" t="n"/>
-      <c r="D53" s="21" t="n"/>
-      <c r="E53" s="21" t="n"/>
-      <c r="F53" s="21" t="n"/>
-      <c r="G53" s="21" t="n"/>
+      <c r="A53" s="32" t="n"/>
+      <c r="B53" s="32" t="n"/>
+      <c r="C53" s="32" t="n"/>
+      <c r="D53" s="32" t="n"/>
+      <c r="E53" s="32" t="n"/>
+      <c r="F53" s="32" t="n"/>
+      <c r="G53" s="32" t="n"/>
       <c r="H53" s="32" t="n"/>
       <c r="I53" s="32" t="n"/>
       <c r="J53" s="32" t="n"/>
       <c r="K53" s="32" t="n"/>
+      <c r="L53" s="32" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="27">
-      <c r="A54" s="21" t="n"/>
-      <c r="B54" s="21" t="n"/>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="21" t="n"/>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="21" t="n"/>
+      <c r="A54" s="32" t="n"/>
+      <c r="B54" s="32" t="n"/>
+      <c r="C54" s="32" t="n"/>
+      <c r="D54" s="32" t="n"/>
+      <c r="E54" s="32" t="n"/>
+      <c r="F54" s="32" t="n"/>
+      <c r="G54" s="32" t="n"/>
       <c r="H54" s="32" t="n"/>
       <c r="I54" s="32" t="n"/>
       <c r="J54" s="32" t="n"/>
       <c r="K54" s="32" t="n"/>
+      <c r="L54" s="32" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="27">
-      <c r="A55" s="21" t="n"/>
-      <c r="B55" s="21" t="n"/>
-      <c r="C55" s="21" t="n"/>
-      <c r="D55" s="21" t="n"/>
-      <c r="E55" s="21" t="n"/>
-      <c r="F55" s="21" t="n"/>
-      <c r="G55" s="21" t="n"/>
+      <c r="A55" s="32" t="n"/>
+      <c r="B55" s="32" t="n"/>
+      <c r="C55" s="32" t="n"/>
+      <c r="D55" s="32" t="n"/>
+      <c r="E55" s="32" t="n"/>
+      <c r="F55" s="32" t="n"/>
+      <c r="G55" s="32" t="n"/>
       <c r="H55" s="32" t="n"/>
       <c r="I55" s="32" t="n"/>
       <c r="J55" s="32" t="n"/>
       <c r="K55" s="32" t="n"/>
+      <c r="L55" s="32" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="27">
-      <c r="A56" s="21" t="n"/>
-      <c r="B56" s="21" t="n"/>
-      <c r="C56" s="21" t="n"/>
-      <c r="D56" s="21" t="n"/>
-      <c r="E56" s="21" t="n"/>
-      <c r="F56" s="21" t="n"/>
-      <c r="G56" s="21" t="n"/>
+      <c r="A56" s="32" t="n"/>
+      <c r="B56" s="32" t="n"/>
+      <c r="C56" s="32" t="n"/>
+      <c r="D56" s="32" t="n"/>
+      <c r="E56" s="32" t="n"/>
+      <c r="F56" s="32" t="n"/>
+      <c r="G56" s="32" t="n"/>
       <c r="H56" s="32" t="n"/>
       <c r="I56" s="32" t="n"/>
       <c r="J56" s="32" t="n"/>
       <c r="K56" s="32" t="n"/>
+      <c r="L56" s="32" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="27">
-      <c r="A57" s="21" t="n"/>
-      <c r="B57" s="21" t="n"/>
-      <c r="C57" s="21" t="n"/>
-      <c r="D57" s="21" t="n"/>
-      <c r="E57" s="21" t="n"/>
-      <c r="F57" s="21" t="n"/>
-      <c r="G57" s="21" t="n"/>
+      <c r="A57" s="32" t="n"/>
+      <c r="B57" s="32" t="n"/>
+      <c r="C57" s="32" t="n"/>
+      <c r="D57" s="32" t="n"/>
+      <c r="E57" s="32" t="n"/>
+      <c r="F57" s="32" t="n"/>
+      <c r="G57" s="32" t="n"/>
       <c r="H57" s="32" t="n"/>
       <c r="I57" s="32" t="n"/>
       <c r="J57" s="32" t="n"/>
       <c r="K57" s="32" t="n"/>
+      <c r="L57" s="32" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="27">
-      <c r="A58" s="21" t="n"/>
-      <c r="B58" s="21" t="n"/>
-      <c r="C58" s="21" t="n"/>
-      <c r="D58" s="21" t="n"/>
-      <c r="E58" s="21" t="n"/>
-      <c r="F58" s="21" t="n"/>
-      <c r="G58" s="21" t="n"/>
+      <c r="A58" s="32" t="n"/>
+      <c r="B58" s="32" t="n"/>
+      <c r="C58" s="32" t="n"/>
+      <c r="D58" s="32" t="n"/>
+      <c r="E58" s="32" t="n"/>
+      <c r="F58" s="32" t="n"/>
+      <c r="G58" s="32" t="n"/>
       <c r="H58" s="32" t="n"/>
       <c r="I58" s="32" t="n"/>
       <c r="J58" s="32" t="n"/>
       <c r="K58" s="32" t="n"/>
+      <c r="L58" s="32" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="27">
-      <c r="A59" s="21" t="n"/>
-      <c r="B59" s="21" t="n"/>
-      <c r="C59" s="21" t="n"/>
-      <c r="D59" s="21" t="n"/>
-      <c r="E59" s="21" t="n"/>
-      <c r="F59" s="21" t="n"/>
-      <c r="G59" s="21" t="n"/>
+      <c r="A59" s="32" t="n"/>
+      <c r="B59" s="32" t="n"/>
+      <c r="C59" s="32" t="n"/>
+      <c r="D59" s="32" t="n"/>
+      <c r="E59" s="32" t="n"/>
+      <c r="F59" s="32" t="n"/>
+      <c r="G59" s="32" t="n"/>
       <c r="H59" s="32" t="n"/>
       <c r="I59" s="32" t="n"/>
       <c r="J59" s="32" t="n"/>
       <c r="K59" s="32" t="n"/>
+      <c r="L59" s="32" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="27">
-      <c r="A60" s="21" t="n"/>
-      <c r="B60" s="21" t="n"/>
-      <c r="C60" s="21" t="n"/>
-      <c r="D60" s="21" t="n"/>
-      <c r="E60" s="21" t="n"/>
-      <c r="F60" s="21" t="n"/>
-      <c r="G60" s="21" t="n"/>
+      <c r="A60" s="32" t="n"/>
+      <c r="B60" s="32" t="n"/>
+      <c r="C60" s="32" t="n"/>
+      <c r="D60" s="32" t="n"/>
+      <c r="E60" s="32" t="n"/>
+      <c r="F60" s="32" t="n"/>
+      <c r="G60" s="32" t="n"/>
       <c r="H60" s="32" t="n"/>
       <c r="I60" s="32" t="n"/>
       <c r="J60" s="32" t="n"/>
       <c r="K60" s="32" t="n"/>
+      <c r="L60" s="32" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="27">
-      <c r="A61" s="21" t="n"/>
-      <c r="B61" s="21" t="n"/>
-      <c r="C61" s="21" t="n"/>
-      <c r="D61" s="21" t="n"/>
-      <c r="E61" s="21" t="n"/>
-      <c r="F61" s="21" t="n"/>
-      <c r="G61" s="21" t="n"/>
+      <c r="A61" s="32" t="n"/>
+      <c r="B61" s="32" t="n"/>
+      <c r="C61" s="32" t="n"/>
+      <c r="D61" s="32" t="n"/>
+      <c r="E61" s="32" t="n"/>
+      <c r="F61" s="32" t="n"/>
+      <c r="G61" s="32" t="n"/>
       <c r="H61" s="32" t="n"/>
       <c r="I61" s="32" t="n"/>
       <c r="J61" s="32" t="n"/>
       <c r="K61" s="32" t="n"/>
+      <c r="L61" s="32" t="n"/>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="27">
-      <c r="A62" s="21" t="n"/>
-      <c r="B62" s="21" t="n"/>
-      <c r="C62" s="21" t="n"/>
-      <c r="D62" s="21" t="n"/>
-      <c r="E62" s="21" t="n"/>
-      <c r="F62" s="21" t="n"/>
-      <c r="G62" s="21" t="n"/>
+      <c r="A62" s="32" t="n"/>
+      <c r="B62" s="32" t="n"/>
+      <c r="C62" s="32" t="n"/>
+      <c r="D62" s="32" t="n"/>
+      <c r="E62" s="32" t="n"/>
+      <c r="F62" s="32" t="n"/>
+      <c r="G62" s="32" t="n"/>
       <c r="H62" s="32" t="n"/>
       <c r="I62" s="32" t="n"/>
       <c r="J62" s="32" t="n"/>
       <c r="K62" s="32" t="n"/>
+      <c r="L62" s="32" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="27">
-      <c r="A63" s="21" t="n"/>
-      <c r="B63" s="21" t="n"/>
-      <c r="C63" s="21" t="n"/>
-      <c r="D63" s="21" t="n"/>
-      <c r="E63" s="21" t="n"/>
-      <c r="F63" s="21" t="n"/>
-      <c r="G63" s="21" t="n"/>
+      <c r="A63" s="32" t="n"/>
+      <c r="B63" s="32" t="n"/>
+      <c r="C63" s="32" t="n"/>
+      <c r="D63" s="32" t="n"/>
+      <c r="E63" s="32" t="n"/>
+      <c r="F63" s="32" t="n"/>
+      <c r="G63" s="32" t="n"/>
       <c r="H63" s="32" t="n"/>
       <c r="I63" s="32" t="n"/>
       <c r="J63" s="32" t="n"/>
       <c r="K63" s="32" t="n"/>
+      <c r="L63" s="32" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="27">
-      <c r="A64" s="21" t="n"/>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
-      <c r="D64" s="21" t="n"/>
-      <c r="E64" s="21" t="n"/>
-      <c r="F64" s="21" t="n"/>
-      <c r="G64" s="21" t="n"/>
+      <c r="A64" s="32" t="n"/>
+      <c r="B64" s="32" t="n"/>
+      <c r="C64" s="32" t="n"/>
+      <c r="D64" s="32" t="n"/>
+      <c r="E64" s="32" t="n"/>
+      <c r="F64" s="32" t="n"/>
+      <c r="G64" s="32" t="n"/>
       <c r="H64" s="32" t="n"/>
       <c r="I64" s="32" t="n"/>
       <c r="J64" s="32" t="n"/>
       <c r="K64" s="32" t="n"/>
+      <c r="L64" s="32" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="27">
-      <c r="A65" s="21" t="n"/>
-      <c r="B65" s="21" t="n"/>
-      <c r="C65" s="21" t="n"/>
-      <c r="D65" s="21" t="n"/>
-      <c r="E65" s="21" t="n"/>
-      <c r="F65" s="21" t="n"/>
-      <c r="G65" s="21" t="n"/>
+      <c r="A65" s="32" t="n"/>
+      <c r="B65" s="32" t="n"/>
+      <c r="C65" s="32" t="n"/>
+      <c r="D65" s="32" t="n"/>
+      <c r="E65" s="32" t="n"/>
+      <c r="F65" s="32" t="n"/>
+      <c r="G65" s="32" t="n"/>
       <c r="H65" s="32" t="n"/>
       <c r="I65" s="32" t="n"/>
       <c r="J65" s="32" t="n"/>
       <c r="K65" s="32" t="n"/>
+      <c r="L65" s="32" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="27">
-      <c r="A66" s="21" t="n"/>
-      <c r="B66" s="21" t="n"/>
-      <c r="C66" s="21" t="n"/>
-      <c r="D66" s="21" t="n"/>
-      <c r="E66" s="21" t="n"/>
-      <c r="F66" s="21" t="n"/>
-      <c r="G66" s="21" t="n"/>
+      <c r="A66" s="32" t="n"/>
+      <c r="B66" s="32" t="n"/>
+      <c r="C66" s="32" t="n"/>
+      <c r="D66" s="32" t="n"/>
+      <c r="E66" s="32" t="n"/>
+      <c r="F66" s="32" t="n"/>
+      <c r="G66" s="32" t="n"/>
       <c r="H66" s="32" t="n"/>
       <c r="I66" s="32" t="n"/>
       <c r="J66" s="32" t="n"/>
       <c r="K66" s="32" t="n"/>
+      <c r="L66" s="32" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="27">
-      <c r="A67" s="21" t="n"/>
-      <c r="B67" s="21" t="n"/>
-      <c r="C67" s="21" t="n"/>
-      <c r="D67" s="21" t="n"/>
-      <c r="E67" s="21" t="n"/>
-      <c r="F67" s="21" t="n"/>
-      <c r="G67" s="21" t="n"/>
+      <c r="A67" s="32" t="n"/>
+      <c r="B67" s="32" t="n"/>
+      <c r="C67" s="32" t="n"/>
+      <c r="D67" s="32" t="n"/>
+      <c r="E67" s="32" t="n"/>
+      <c r="F67" s="32" t="n"/>
+      <c r="G67" s="32" t="n"/>
       <c r="H67" s="32" t="n"/>
       <c r="I67" s="32" t="n"/>
       <c r="J67" s="32" t="n"/>
       <c r="K67" s="32" t="n"/>
+      <c r="L67" s="32" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="27">
-      <c r="A68" s="21" t="n"/>
-      <c r="B68" s="21" t="n"/>
-      <c r="C68" s="21" t="n"/>
-      <c r="D68" s="21" t="n"/>
-      <c r="E68" s="21" t="n"/>
-      <c r="F68" s="21" t="n"/>
-      <c r="G68" s="21" t="n"/>
+      <c r="A68" s="32" t="n"/>
+      <c r="B68" s="32" t="n"/>
+      <c r="C68" s="32" t="n"/>
+      <c r="D68" s="32" t="n"/>
+      <c r="E68" s="32" t="n"/>
+      <c r="F68" s="32" t="n"/>
+      <c r="G68" s="32" t="n"/>
       <c r="H68" s="32" t="n"/>
       <c r="I68" s="32" t="n"/>
       <c r="J68" s="32" t="n"/>
       <c r="K68" s="32" t="n"/>
+      <c r="L68" s="32" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="27">
-      <c r="A69" s="21" t="n"/>
-      <c r="B69" s="21" t="n"/>
-      <c r="C69" s="21" t="n"/>
-      <c r="D69" s="21" t="n"/>
-      <c r="E69" s="21" t="n"/>
-      <c r="F69" s="21" t="n"/>
-      <c r="G69" s="21" t="n"/>
+      <c r="A69" s="32" t="n"/>
+      <c r="B69" s="32" t="n"/>
+      <c r="C69" s="32" t="n"/>
+      <c r="D69" s="32" t="n"/>
+      <c r="E69" s="32" t="n"/>
+      <c r="F69" s="32" t="n"/>
+      <c r="G69" s="32" t="n"/>
       <c r="H69" s="32" t="n"/>
       <c r="I69" s="32" t="n"/>
       <c r="J69" s="32" t="n"/>
       <c r="K69" s="32" t="n"/>
+      <c r="L69" s="32" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="27">
-      <c r="A70" s="21" t="n"/>
-      <c r="B70" s="21" t="n"/>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
+      <c r="A70" s="32" t="n"/>
+      <c r="B70" s="32" t="n"/>
+      <c r="C70" s="32" t="n"/>
+      <c r="D70" s="32" t="n"/>
+      <c r="E70" s="32" t="n"/>
+      <c r="F70" s="32" t="n"/>
+      <c r="G70" s="32" t="n"/>
       <c r="H70" s="32" t="n"/>
       <c r="I70" s="32" t="n"/>
       <c r="J70" s="32" t="n"/>
       <c r="K70" s="32" t="n"/>
+      <c r="L70" s="32" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="27">
-      <c r="A71" s="21" t="n"/>
-      <c r="B71" s="21" t="n"/>
-      <c r="C71" s="21" t="n"/>
-      <c r="D71" s="21" t="n"/>
-      <c r="E71" s="21" t="n"/>
-      <c r="F71" s="21" t="n"/>
-      <c r="G71" s="21" t="n"/>
+      <c r="A71" s="32" t="n"/>
+      <c r="B71" s="32" t="n"/>
+      <c r="C71" s="32" t="n"/>
+      <c r="D71" s="32" t="n"/>
+      <c r="E71" s="32" t="n"/>
+      <c r="F71" s="32" t="n"/>
+      <c r="G71" s="32" t="n"/>
       <c r="H71" s="32" t="n"/>
       <c r="I71" s="32" t="n"/>
       <c r="J71" s="32" t="n"/>
       <c r="K71" s="32" t="n"/>
+      <c r="L71" s="32" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="27">
-      <c r="A72" s="21" t="n"/>
-      <c r="B72" s="21" t="n"/>
-      <c r="C72" s="21" t="n"/>
-      <c r="D72" s="21" t="n"/>
-      <c r="E72" s="21" t="n"/>
-      <c r="F72" s="21" t="n"/>
-      <c r="G72" s="21" t="n"/>
+      <c r="A72" s="32" t="n"/>
+      <c r="B72" s="32" t="n"/>
+      <c r="C72" s="32" t="n"/>
+      <c r="D72" s="32" t="n"/>
+      <c r="E72" s="32" t="n"/>
+      <c r="F72" s="32" t="n"/>
+      <c r="G72" s="32" t="n"/>
       <c r="H72" s="32" t="n"/>
       <c r="I72" s="32" t="n"/>
       <c r="J72" s="32" t="n"/>
       <c r="K72" s="32" t="n"/>
+      <c r="L72" s="32" t="n"/>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="27">
-      <c r="A73" s="21" t="n"/>
-      <c r="B73" s="21" t="n"/>
-      <c r="C73" s="21" t="n"/>
-      <c r="D73" s="21" t="n"/>
-      <c r="E73" s="21" t="n"/>
-      <c r="F73" s="21" t="n"/>
-      <c r="G73" s="21" t="n"/>
+      <c r="A73" s="32" t="n"/>
+      <c r="B73" s="32" t="n"/>
+      <c r="C73" s="32" t="n"/>
+      <c r="D73" s="32" t="n"/>
+      <c r="E73" s="32" t="n"/>
+      <c r="F73" s="32" t="n"/>
+      <c r="G73" s="32" t="n"/>
       <c r="H73" s="32" t="n"/>
       <c r="I73" s="32" t="n"/>
       <c r="J73" s="32" t="n"/>
       <c r="K73" s="32" t="n"/>
+      <c r="L73" s="32" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="27">
-      <c r="A74" s="21" t="n"/>
-      <c r="B74" s="21" t="n"/>
-      <c r="C74" s="21" t="n"/>
-      <c r="D74" s="21" t="n"/>
-      <c r="E74" s="21" t="n"/>
-      <c r="F74" s="21" t="n"/>
-      <c r="G74" s="21" t="n"/>
+      <c r="A74" s="32" t="n"/>
+      <c r="B74" s="32" t="n"/>
+      <c r="C74" s="32" t="n"/>
+      <c r="D74" s="32" t="n"/>
+      <c r="E74" s="32" t="n"/>
+      <c r="F74" s="32" t="n"/>
+      <c r="G74" s="32" t="n"/>
       <c r="H74" s="32" t="n"/>
       <c r="I74" s="32" t="n"/>
       <c r="J74" s="32" t="n"/>
       <c r="K74" s="32" t="n"/>
+      <c r="L74" s="32" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="27">
-      <c r="A75" s="21" t="n"/>
-      <c r="B75" s="21" t="n"/>
-      <c r="C75" s="21" t="n"/>
-      <c r="D75" s="21" t="n"/>
-      <c r="E75" s="21" t="n"/>
-      <c r="F75" s="21" t="n"/>
-      <c r="G75" s="21" t="n"/>
+      <c r="A75" s="32" t="n"/>
+      <c r="B75" s="32" t="n"/>
+      <c r="C75" s="32" t="n"/>
+      <c r="D75" s="32" t="n"/>
+      <c r="E75" s="32" t="n"/>
+      <c r="F75" s="32" t="n"/>
+      <c r="G75" s="32" t="n"/>
       <c r="H75" s="32" t="n"/>
       <c r="I75" s="32" t="n"/>
       <c r="J75" s="32" t="n"/>
       <c r="K75" s="32" t="n"/>
+      <c r="L75" s="32" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="27">
-      <c r="A76" s="21" t="n"/>
-      <c r="B76" s="21" t="n"/>
-      <c r="C76" s="21" t="n"/>
-      <c r="D76" s="21" t="n"/>
-      <c r="E76" s="21" t="n"/>
-      <c r="F76" s="21" t="n"/>
-      <c r="G76" s="21" t="n"/>
+      <c r="A76" s="32" t="n"/>
+      <c r="B76" s="32" t="n"/>
+      <c r="C76" s="32" t="n"/>
+      <c r="D76" s="32" t="n"/>
+      <c r="E76" s="32" t="n"/>
+      <c r="F76" s="32" t="n"/>
+      <c r="G76" s="32" t="n"/>
       <c r="H76" s="32" t="n"/>
       <c r="I76" s="32" t="n"/>
       <c r="J76" s="32" t="n"/>
       <c r="K76" s="32" t="n"/>
+      <c r="L76" s="32" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="27">
-      <c r="A77" s="21" t="n"/>
-      <c r="B77" s="21" t="n"/>
-      <c r="C77" s="21" t="n"/>
-      <c r="D77" s="21" t="n"/>
-      <c r="E77" s="21" t="n"/>
-      <c r="F77" s="21" t="n"/>
-      <c r="G77" s="21" t="n"/>
+      <c r="A77" s="32" t="n"/>
+      <c r="B77" s="32" t="n"/>
+      <c r="C77" s="32" t="n"/>
+      <c r="D77" s="32" t="n"/>
+      <c r="E77" s="32" t="n"/>
+      <c r="F77" s="32" t="n"/>
+      <c r="G77" s="32" t="n"/>
       <c r="H77" s="32" t="n"/>
       <c r="I77" s="32" t="n"/>
       <c r="J77" s="32" t="n"/>
       <c r="K77" s="32" t="n"/>
+      <c r="L77" s="32" t="n"/>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="27">
-      <c r="A78" s="21" t="n"/>
-      <c r="B78" s="21" t="n"/>
-      <c r="C78" s="21" t="n"/>
-      <c r="D78" s="21" t="n"/>
-      <c r="E78" s="21" t="n"/>
-      <c r="F78" s="21" t="n"/>
-      <c r="G78" s="21" t="n"/>
+      <c r="A78" s="32" t="n"/>
+      <c r="B78" s="32" t="n"/>
+      <c r="C78" s="32" t="n"/>
+      <c r="D78" s="32" t="n"/>
+      <c r="E78" s="32" t="n"/>
+      <c r="F78" s="32" t="n"/>
+      <c r="G78" s="32" t="n"/>
       <c r="H78" s="32" t="n"/>
       <c r="I78" s="32" t="n"/>
       <c r="J78" s="32" t="n"/>
       <c r="K78" s="32" t="n"/>
+      <c r="L78" s="32" t="n"/>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="27">
-      <c r="A79" s="21" t="n"/>
-      <c r="B79" s="21" t="n"/>
-      <c r="C79" s="21" t="n"/>
-      <c r="D79" s="21" t="n"/>
-      <c r="E79" s="21" t="n"/>
-      <c r="F79" s="21" t="n"/>
-      <c r="G79" s="21" t="n"/>
+      <c r="A79" s="32" t="n"/>
+      <c r="B79" s="32" t="n"/>
+      <c r="C79" s="32" t="n"/>
+      <c r="D79" s="32" t="n"/>
+      <c r="E79" s="32" t="n"/>
+      <c r="F79" s="32" t="n"/>
+      <c r="G79" s="32" t="n"/>
       <c r="H79" s="32" t="n"/>
       <c r="I79" s="32" t="n"/>
       <c r="J79" s="32" t="n"/>
       <c r="K79" s="32" t="n"/>
+      <c r="L79" s="32" t="n"/>
     </row>
     <row r="80" ht="15.75" customHeight="1" s="27">
-      <c r="A80" s="21" t="n"/>
-      <c r="B80" s="21" t="n"/>
-      <c r="C80" s="21" t="n"/>
-      <c r="D80" s="21" t="n"/>
-      <c r="E80" s="21" t="n"/>
-      <c r="F80" s="21" t="n"/>
-      <c r="G80" s="21" t="n"/>
+      <c r="A80" s="32" t="n"/>
+      <c r="B80" s="32" t="n"/>
+      <c r="C80" s="32" t="n"/>
+      <c r="D80" s="32" t="n"/>
+      <c r="E80" s="32" t="n"/>
+      <c r="F80" s="32" t="n"/>
+      <c r="G80" s="32" t="n"/>
       <c r="H80" s="32" t="n"/>
       <c r="I80" s="32" t="n"/>
       <c r="J80" s="32" t="n"/>
       <c r="K80" s="32" t="n"/>
+      <c r="L80" s="32" t="n"/>
     </row>
     <row r="81" ht="15.75" customHeight="1" s="27">
-      <c r="A81" s="21" t="n"/>
-      <c r="B81" s="21" t="n"/>
-      <c r="C81" s="21" t="n"/>
-      <c r="D81" s="21" t="n"/>
-      <c r="E81" s="21" t="n"/>
-      <c r="F81" s="21" t="n"/>
-      <c r="G81" s="21" t="n"/>
+      <c r="A81" s="32" t="n"/>
+      <c r="B81" s="32" t="n"/>
+      <c r="C81" s="32" t="n"/>
+      <c r="D81" s="32" t="n"/>
+      <c r="E81" s="32" t="n"/>
+      <c r="F81" s="32" t="n"/>
+      <c r="G81" s="32" t="n"/>
       <c r="H81" s="32" t="n"/>
       <c r="I81" s="32" t="n"/>
       <c r="J81" s="32" t="n"/>
       <c r="K81" s="32" t="n"/>
+      <c r="L81" s="32" t="n"/>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="27">
-      <c r="A82" s="21" t="n"/>
-      <c r="B82" s="21" t="n"/>
-      <c r="C82" s="21" t="n"/>
-      <c r="D82" s="21" t="n"/>
-      <c r="E82" s="21" t="n"/>
-      <c r="F82" s="21" t="n"/>
-      <c r="G82" s="21" t="n"/>
+      <c r="A82" s="32" t="n"/>
+      <c r="B82" s="32" t="n"/>
+      <c r="C82" s="32" t="n"/>
+      <c r="D82" s="32" t="n"/>
+      <c r="E82" s="32" t="n"/>
+      <c r="F82" s="32" t="n"/>
+      <c r="G82" s="32" t="n"/>
       <c r="H82" s="32" t="n"/>
       <c r="I82" s="32" t="n"/>
       <c r="J82" s="32" t="n"/>
       <c r="K82" s="32" t="n"/>
+      <c r="L82" s="32" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="27">
-      <c r="A83" s="21" t="n"/>
-      <c r="B83" s="21" t="n"/>
-      <c r="C83" s="21" t="n"/>
-      <c r="D83" s="21" t="n"/>
-      <c r="E83" s="21" t="n"/>
-      <c r="F83" s="21" t="n"/>
-      <c r="G83" s="21" t="n"/>
+      <c r="A83" s="32" t="n"/>
+      <c r="B83" s="32" t="n"/>
+      <c r="C83" s="32" t="n"/>
+      <c r="D83" s="32" t="n"/>
+      <c r="E83" s="32" t="n"/>
+      <c r="F83" s="32" t="n"/>
+      <c r="G83" s="32" t="n"/>
       <c r="H83" s="32" t="n"/>
       <c r="I83" s="32" t="n"/>
       <c r="J83" s="32" t="n"/>
       <c r="K83" s="32" t="n"/>
+      <c r="L83" s="32" t="n"/>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="27">
-      <c r="A84" s="21" t="n"/>
-      <c r="B84" s="21" t="n"/>
-      <c r="C84" s="21" t="n"/>
-      <c r="D84" s="21" t="n"/>
-      <c r="E84" s="21" t="n"/>
-      <c r="F84" s="21" t="n"/>
-      <c r="G84" s="21" t="n"/>
+      <c r="A84" s="32" t="n"/>
+      <c r="B84" s="32" t="n"/>
+      <c r="C84" s="32" t="n"/>
+      <c r="D84" s="32" t="n"/>
+      <c r="E84" s="32" t="n"/>
+      <c r="F84" s="32" t="n"/>
+      <c r="G84" s="32" t="n"/>
       <c r="H84" s="32" t="n"/>
       <c r="I84" s="32" t="n"/>
       <c r="J84" s="32" t="n"/>
       <c r="K84" s="32" t="n"/>
+      <c r="L84" s="32" t="n"/>
     </row>
     <row r="85" ht="15.75" customHeight="1" s="27">
-      <c r="A85" s="21" t="n"/>
-      <c r="B85" s="21" t="n"/>
-      <c r="C85" s="21" t="n"/>
-      <c r="D85" s="21" t="n"/>
-      <c r="E85" s="21" t="n"/>
-      <c r="F85" s="21" t="n"/>
-      <c r="G85" s="21" t="n"/>
+      <c r="A85" s="32" t="n"/>
+      <c r="B85" s="32" t="n"/>
+      <c r="C85" s="32" t="n"/>
+      <c r="D85" s="32" t="n"/>
+      <c r="E85" s="32" t="n"/>
+      <c r="F85" s="32" t="n"/>
+      <c r="G85" s="32" t="n"/>
       <c r="H85" s="32" t="n"/>
       <c r="I85" s="32" t="n"/>
       <c r="J85" s="32" t="n"/>
       <c r="K85" s="32" t="n"/>
+      <c r="L85" s="32" t="n"/>
     </row>
     <row r="86" ht="15.75" customHeight="1" s="27">
-      <c r="A86" s="21" t="n"/>
-      <c r="B86" s="21" t="n"/>
-      <c r="C86" s="21" t="n"/>
-      <c r="D86" s="21" t="n"/>
-      <c r="E86" s="21" t="n"/>
-      <c r="F86" s="21" t="n"/>
-      <c r="G86" s="21" t="n"/>
+      <c r="A86" s="32" t="n"/>
+      <c r="B86" s="32" t="n"/>
+      <c r="C86" s="32" t="n"/>
+      <c r="D86" s="32" t="n"/>
+      <c r="E86" s="32" t="n"/>
+      <c r="F86" s="32" t="n"/>
+      <c r="G86" s="32" t="n"/>
       <c r="H86" s="32" t="n"/>
       <c r="I86" s="32" t="n"/>
       <c r="J86" s="32" t="n"/>
       <c r="K86" s="32" t="n"/>
+      <c r="L86" s="32" t="n"/>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="27">
-      <c r="A87" s="21" t="n"/>
-      <c r="B87" s="21" t="n"/>
-      <c r="C87" s="21" t="n"/>
-      <c r="D87" s="21" t="n"/>
-      <c r="E87" s="21" t="n"/>
-      <c r="F87" s="21" t="n"/>
-      <c r="G87" s="21" t="n"/>
+      <c r="A87" s="32" t="n"/>
+      <c r="B87" s="32" t="n"/>
+      <c r="C87" s="32" t="n"/>
+      <c r="D87" s="32" t="n"/>
+      <c r="E87" s="32" t="n"/>
+      <c r="F87" s="32" t="n"/>
+      <c r="G87" s="32" t="n"/>
       <c r="H87" s="32" t="n"/>
       <c r="I87" s="32" t="n"/>
       <c r="J87" s="32" t="n"/>
       <c r="K87" s="32" t="n"/>
+      <c r="L87" s="32" t="n"/>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="27">
-      <c r="A88" s="21" t="n"/>
-      <c r="B88" s="21" t="n"/>
-      <c r="C88" s="21" t="n"/>
-      <c r="D88" s="21" t="n"/>
-      <c r="E88" s="21" t="n"/>
-      <c r="F88" s="21" t="n"/>
-      <c r="G88" s="21" t="n"/>
+      <c r="A88" s="32" t="n"/>
+      <c r="B88" s="32" t="n"/>
+      <c r="C88" s="32" t="n"/>
+      <c r="D88" s="32" t="n"/>
+      <c r="E88" s="32" t="n"/>
+      <c r="F88" s="32" t="n"/>
+      <c r="G88" s="32" t="n"/>
       <c r="H88" s="32" t="n"/>
       <c r="I88" s="32" t="n"/>
       <c r="J88" s="32" t="n"/>
       <c r="K88" s="32" t="n"/>
+      <c r="L88" s="32" t="n"/>
     </row>
     <row r="89" ht="15.75" customHeight="1" s="27">
-      <c r="A89" s="21" t="n"/>
-      <c r="B89" s="21" t="n"/>
-      <c r="C89" s="21" t="n"/>
-      <c r="D89" s="21" t="n"/>
-      <c r="E89" s="21" t="n"/>
-      <c r="F89" s="21" t="n"/>
-      <c r="G89" s="21" t="n"/>
+      <c r="A89" s="32" t="n"/>
+      <c r="B89" s="32" t="n"/>
+      <c r="C89" s="32" t="n"/>
+      <c r="D89" s="32" t="n"/>
+      <c r="E89" s="32" t="n"/>
+      <c r="F89" s="32" t="n"/>
+      <c r="G89" s="32" t="n"/>
       <c r="H89" s="32" t="n"/>
       <c r="I89" s="32" t="n"/>
       <c r="J89" s="32" t="n"/>
       <c r="K89" s="32" t="n"/>
+      <c r="L89" s="32" t="n"/>
     </row>
     <row r="90" ht="15.75" customHeight="1" s="27">
-      <c r="A90" s="21" t="n"/>
-      <c r="B90" s="21" t="n"/>
-      <c r="C90" s="21" t="n"/>
-      <c r="D90" s="21" t="n"/>
-      <c r="E90" s="21" t="n"/>
-      <c r="F90" s="21" t="n"/>
-      <c r="G90" s="21" t="n"/>
+      <c r="A90" s="32" t="n"/>
+      <c r="B90" s="32" t="n"/>
+      <c r="C90" s="32" t="n"/>
+      <c r="D90" s="32" t="n"/>
+      <c r="E90" s="32" t="n"/>
+      <c r="F90" s="32" t="n"/>
+      <c r="G90" s="32" t="n"/>
       <c r="H90" s="32" t="n"/>
       <c r="I90" s="32" t="n"/>
       <c r="J90" s="32" t="n"/>
       <c r="K90" s="32" t="n"/>
+      <c r="L90" s="32" t="n"/>
     </row>
     <row r="91" ht="15.75" customHeight="1" s="27">
-      <c r="A91" s="21" t="n"/>
-      <c r="B91" s="21" t="n"/>
-      <c r="C91" s="21" t="n"/>
-      <c r="D91" s="21" t="n"/>
-      <c r="E91" s="21" t="n"/>
-      <c r="F91" s="21" t="n"/>
-      <c r="G91" s="21" t="n"/>
+      <c r="A91" s="32" t="n"/>
+      <c r="B91" s="32" t="n"/>
+      <c r="C91" s="32" t="n"/>
+      <c r="D91" s="32" t="n"/>
+      <c r="E91" s="32" t="n"/>
+      <c r="F91" s="32" t="n"/>
+      <c r="G91" s="32" t="n"/>
       <c r="H91" s="32" t="n"/>
       <c r="I91" s="32" t="n"/>
       <c r="J91" s="32" t="n"/>
       <c r="K91" s="32" t="n"/>
+      <c r="L91" s="32" t="n"/>
     </row>
     <row r="92" ht="15.75" customHeight="1" s="27">
-      <c r="A92" s="21" t="n"/>
-      <c r="B92" s="21" t="n"/>
-      <c r="C92" s="21" t="n"/>
-      <c r="D92" s="21" t="n"/>
-      <c r="E92" s="21" t="n"/>
-      <c r="F92" s="21" t="n"/>
-      <c r="G92" s="21" t="n"/>
+      <c r="A92" s="32" t="n"/>
+      <c r="B92" s="32" t="n"/>
+      <c r="C92" s="32" t="n"/>
+      <c r="D92" s="32" t="n"/>
+      <c r="E92" s="32" t="n"/>
+      <c r="F92" s="32" t="n"/>
+      <c r="G92" s="32" t="n"/>
       <c r="H92" s="32" t="n"/>
       <c r="I92" s="32" t="n"/>
       <c r="J92" s="32" t="n"/>
       <c r="K92" s="32" t="n"/>
+      <c r="L92" s="32" t="n"/>
     </row>
     <row r="93" ht="15.75" customHeight="1" s="27">
-      <c r="A93" s="21" t="n"/>
-      <c r="B93" s="21" t="n"/>
-      <c r="C93" s="21" t="n"/>
-      <c r="D93" s="21" t="n"/>
-      <c r="E93" s="21" t="n"/>
-      <c r="F93" s="21" t="n"/>
-      <c r="G93" s="21" t="n"/>
+      <c r="A93" s="32" t="n"/>
+      <c r="B93" s="32" t="n"/>
+      <c r="C93" s="32" t="n"/>
+      <c r="D93" s="32" t="n"/>
+      <c r="E93" s="32" t="n"/>
+      <c r="F93" s="32" t="n"/>
+      <c r="G93" s="32" t="n"/>
       <c r="H93" s="32" t="n"/>
       <c r="I93" s="32" t="n"/>
       <c r="J93" s="32" t="n"/>
       <c r="K93" s="32" t="n"/>
+      <c r="L93" s="32" t="n"/>
     </row>
     <row r="94" ht="15.75" customHeight="1" s="27">
-      <c r="A94" s="21" t="n"/>
-      <c r="B94" s="21" t="n"/>
-      <c r="C94" s="21" t="n"/>
-      <c r="D94" s="21" t="n"/>
-      <c r="E94" s="21" t="n"/>
-      <c r="F94" s="21" t="n"/>
-      <c r="G94" s="21" t="n"/>
+      <c r="A94" s="32" t="n"/>
+      <c r="B94" s="32" t="n"/>
+      <c r="C94" s="32" t="n"/>
+      <c r="D94" s="32" t="n"/>
+      <c r="E94" s="32" t="n"/>
+      <c r="F94" s="32" t="n"/>
+      <c r="G94" s="32" t="n"/>
       <c r="H94" s="32" t="n"/>
       <c r="I94" s="32" t="n"/>
       <c r="J94" s="32" t="n"/>
       <c r="K94" s="32" t="n"/>
+      <c r="L94" s="32" t="n"/>
     </row>
     <row r="95" ht="15.75" customHeight="1" s="27">
-      <c r="A95" s="21" t="n"/>
-      <c r="B95" s="21" t="n"/>
-      <c r="C95" s="21" t="n"/>
-      <c r="D95" s="21" t="n"/>
-      <c r="E95" s="21" t="n"/>
-      <c r="F95" s="21" t="n"/>
-      <c r="G95" s="21" t="n"/>
+      <c r="A95" s="32" t="n"/>
+      <c r="B95" s="32" t="n"/>
+      <c r="C95" s="32" t="n"/>
+      <c r="D95" s="32" t="n"/>
+      <c r="E95" s="32" t="n"/>
+      <c r="F95" s="32" t="n"/>
+      <c r="G95" s="32" t="n"/>
       <c r="H95" s="32" t="n"/>
       <c r="I95" s="32" t="n"/>
       <c r="J95" s="32" t="n"/>
       <c r="K95" s="32" t="n"/>
+      <c r="L95" s="32" t="n"/>
     </row>
     <row r="96" ht="15.75" customHeight="1" s="27">
-      <c r="A96" s="21" t="n"/>
-      <c r="B96" s="21" t="n"/>
-      <c r="C96" s="21" t="n"/>
-      <c r="D96" s="21" t="n"/>
-      <c r="E96" s="21" t="n"/>
-      <c r="F96" s="21" t="n"/>
-      <c r="G96" s="21" t="n"/>
+      <c r="A96" s="32" t="n"/>
+      <c r="B96" s="32" t="n"/>
+      <c r="C96" s="32" t="n"/>
+      <c r="D96" s="32" t="n"/>
+      <c r="E96" s="32" t="n"/>
+      <c r="F96" s="32" t="n"/>
+      <c r="G96" s="32" t="n"/>
       <c r="H96" s="32" t="n"/>
       <c r="I96" s="32" t="n"/>
       <c r="J96" s="32" t="n"/>
       <c r="K96" s="32" t="n"/>
+      <c r="L96" s="32" t="n"/>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="27">
-      <c r="A97" s="21" t="n"/>
-      <c r="B97" s="21" t="n"/>
-      <c r="C97" s="21" t="n"/>
-      <c r="D97" s="21" t="n"/>
-      <c r="E97" s="21" t="n"/>
-      <c r="F97" s="21" t="n"/>
-      <c r="G97" s="21" t="n"/>
+      <c r="A97" s="32" t="n"/>
+      <c r="B97" s="32" t="n"/>
+      <c r="C97" s="32" t="n"/>
+      <c r="D97" s="32" t="n"/>
+      <c r="E97" s="32" t="n"/>
+      <c r="F97" s="32" t="n"/>
+      <c r="G97" s="32" t="n"/>
       <c r="H97" s="32" t="n"/>
       <c r="I97" s="32" t="n"/>
       <c r="J97" s="32" t="n"/>
       <c r="K97" s="32" t="n"/>
+      <c r="L97" s="32" t="n"/>
     </row>
     <row r="98" ht="15.75" customHeight="1" s="27">
-      <c r="A98" s="21" t="n"/>
-      <c r="B98" s="21" t="n"/>
-      <c r="C98" s="21" t="n"/>
-      <c r="D98" s="21" t="n"/>
-      <c r="E98" s="21" t="n"/>
-      <c r="F98" s="21" t="n"/>
-      <c r="G98" s="21" t="n"/>
+      <c r="A98" s="32" t="n"/>
+      <c r="B98" s="32" t="n"/>
+      <c r="C98" s="32" t="n"/>
+      <c r="D98" s="32" t="n"/>
+      <c r="E98" s="32" t="n"/>
+      <c r="F98" s="32" t="n"/>
+      <c r="G98" s="32" t="n"/>
       <c r="H98" s="32" t="n"/>
       <c r="I98" s="32" t="n"/>
       <c r="J98" s="32" t="n"/>
       <c r="K98" s="32" t="n"/>
+      <c r="L98" s="32" t="n"/>
     </row>
     <row r="99" ht="15.75" customHeight="1" s="27">
-      <c r="A99" s="21" t="n"/>
-      <c r="B99" s="21" t="n"/>
-      <c r="C99" s="21" t="n"/>
-      <c r="D99" s="21" t="n"/>
-      <c r="E99" s="21" t="n"/>
-      <c r="F99" s="21" t="n"/>
-      <c r="G99" s="21" t="n"/>
+      <c r="A99" s="32" t="n"/>
+      <c r="B99" s="32" t="n"/>
+      <c r="C99" s="32" t="n"/>
+      <c r="D99" s="32" t="n"/>
+      <c r="E99" s="32" t="n"/>
+      <c r="F99" s="32" t="n"/>
+      <c r="G99" s="32" t="n"/>
       <c r="H99" s="32" t="n"/>
       <c r="I99" s="32" t="n"/>
       <c r="J99" s="32" t="n"/>
       <c r="K99" s="32" t="n"/>
+      <c r="L99" s="32" t="n"/>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="27">
-      <c r="A100" s="21" t="n"/>
-      <c r="B100" s="21" t="n"/>
-      <c r="C100" s="21" t="n"/>
-      <c r="D100" s="21" t="n"/>
-      <c r="E100" s="21" t="n"/>
-      <c r="F100" s="21" t="n"/>
-      <c r="G100" s="21" t="n"/>
+      <c r="A100" s="32" t="n"/>
+      <c r="B100" s="32" t="n"/>
+      <c r="C100" s="32" t="n"/>
+      <c r="D100" s="32" t="n"/>
+      <c r="E100" s="32" t="n"/>
+      <c r="F100" s="32" t="n"/>
+      <c r="G100" s="32" t="n"/>
       <c r="H100" s="32" t="n"/>
       <c r="I100" s="32" t="n"/>
       <c r="J100" s="32" t="n"/>
       <c r="K100" s="32" t="n"/>
+      <c r="L100" s="32" t="n"/>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="27">
-      <c r="A101" s="21" t="n"/>
-      <c r="B101" s="21" t="n"/>
-      <c r="C101" s="21" t="n"/>
-      <c r="D101" s="21" t="n"/>
-      <c r="E101" s="21" t="n"/>
-      <c r="F101" s="21" t="n"/>
-      <c r="G101" s="21" t="n"/>
+      <c r="A101" s="32" t="n"/>
+      <c r="B101" s="32" t="n"/>
+      <c r="C101" s="32" t="n"/>
+      <c r="D101" s="32" t="n"/>
+      <c r="E101" s="32" t="n"/>
+      <c r="F101" s="32" t="n"/>
+      <c r="G101" s="32" t="n"/>
       <c r="H101" s="32" t="n"/>
       <c r="I101" s="32" t="n"/>
       <c r="J101" s="32" t="n"/>
       <c r="K101" s="32" t="n"/>
+      <c r="L101" s="32" t="n"/>
     </row>
     <row r="102" ht="15.75" customHeight="1" s="27">
-      <c r="A102" s="21" t="n"/>
-      <c r="B102" s="21" t="n"/>
-      <c r="C102" s="21" t="n"/>
-      <c r="D102" s="21" t="n"/>
-      <c r="E102" s="21" t="n"/>
-      <c r="F102" s="21" t="n"/>
-      <c r="G102" s="21" t="n"/>
+      <c r="A102" s="32" t="n"/>
+      <c r="B102" s="32" t="n"/>
+      <c r="C102" s="32" t="n"/>
+      <c r="D102" s="32" t="n"/>
+      <c r="E102" s="32" t="n"/>
+      <c r="F102" s="32" t="n"/>
+      <c r="G102" s="32" t="n"/>
       <c r="H102" s="32" t="n"/>
       <c r="I102" s="32" t="n"/>
       <c r="J102" s="32" t="n"/>
       <c r="K102" s="32" t="n"/>
+      <c r="L102" s="32" t="n"/>
     </row>
     <row r="103" ht="15.75" customHeight="1" s="27">
-      <c r="A103" s="21" t="n"/>
-      <c r="B103" s="21" t="n"/>
-      <c r="C103" s="21" t="n"/>
-      <c r="D103" s="21" t="n"/>
-      <c r="E103" s="21" t="n"/>
-      <c r="F103" s="21" t="n"/>
-      <c r="G103" s="21" t="n"/>
+      <c r="A103" s="32" t="n"/>
+      <c r="B103" s="32" t="n"/>
+      <c r="C103" s="32" t="n"/>
+      <c r="D103" s="32" t="n"/>
+      <c r="E103" s="32" t="n"/>
+      <c r="F103" s="32" t="n"/>
+      <c r="G103" s="32" t="n"/>
       <c r="H103" s="32" t="n"/>
       <c r="I103" s="32" t="n"/>
       <c r="J103" s="32" t="n"/>
       <c r="K103" s="32" t="n"/>
+      <c r="L103" s="32" t="n"/>
     </row>
     <row r="104" ht="15.75" customHeight="1" s="27">
-      <c r="A104" s="21" t="n"/>
-      <c r="B104" s="21" t="n"/>
-      <c r="C104" s="21" t="n"/>
-      <c r="D104" s="21" t="n"/>
-      <c r="E104" s="21" t="n"/>
-      <c r="F104" s="21" t="n"/>
-      <c r="G104" s="21" t="n"/>
+      <c r="A104" s="32" t="n"/>
+      <c r="B104" s="32" t="n"/>
+      <c r="C104" s="32" t="n"/>
+      <c r="D104" s="32" t="n"/>
+      <c r="E104" s="32" t="n"/>
+      <c r="F104" s="32" t="n"/>
+      <c r="G104" s="32" t="n"/>
       <c r="H104" s="32" t="n"/>
       <c r="I104" s="32" t="n"/>
       <c r="J104" s="32" t="n"/>
       <c r="K104" s="32" t="n"/>
+      <c r="L104" s="32" t="n"/>
     </row>
     <row r="105" ht="15.75" customHeight="1" s="27">
-      <c r="A105" s="21" t="n"/>
-      <c r="B105" s="21" t="n"/>
-      <c r="C105" s="21" t="n"/>
-      <c r="D105" s="21" t="n"/>
-      <c r="E105" s="21" t="n"/>
-      <c r="F105" s="21" t="n"/>
-      <c r="G105" s="21" t="n"/>
+      <c r="A105" s="32" t="n"/>
+      <c r="B105" s="32" t="n"/>
+      <c r="C105" s="32" t="n"/>
+      <c r="D105" s="32" t="n"/>
+      <c r="E105" s="32" t="n"/>
+      <c r="F105" s="32" t="n"/>
+      <c r="G105" s="32" t="n"/>
       <c r="H105" s="32" t="n"/>
       <c r="I105" s="32" t="n"/>
       <c r="J105" s="32" t="n"/>
       <c r="K105" s="32" t="n"/>
+      <c r="L105" s="32" t="n"/>
     </row>
     <row r="106" ht="15.75" customHeight="1" s="27">
-      <c r="A106" s="21" t="n"/>
-      <c r="B106" s="21" t="n"/>
-      <c r="C106" s="21" t="n"/>
-      <c r="D106" s="21" t="n"/>
-      <c r="E106" s="21" t="n"/>
-      <c r="F106" s="21" t="n"/>
-      <c r="G106" s="21" t="n"/>
+      <c r="A106" s="32" t="n"/>
+      <c r="B106" s="32" t="n"/>
+      <c r="C106" s="32" t="n"/>
+      <c r="D106" s="32" t="n"/>
+      <c r="E106" s="32" t="n"/>
+      <c r="F106" s="32" t="n"/>
+      <c r="G106" s="32" t="n"/>
       <c r="H106" s="32" t="n"/>
       <c r="I106" s="32" t="n"/>
       <c r="J106" s="32" t="n"/>
       <c r="K106" s="32" t="n"/>
+      <c r="L106" s="32" t="n"/>
     </row>
     <row r="107" ht="15.75" customHeight="1" s="27">
-      <c r="A107" s="21" t="n"/>
-      <c r="B107" s="21" t="n"/>
-      <c r="C107" s="21" t="n"/>
-      <c r="D107" s="21" t="n"/>
-      <c r="E107" s="21" t="n"/>
-      <c r="F107" s="21" t="n"/>
-      <c r="G107" s="21" t="n"/>
+      <c r="A107" s="32" t="n"/>
+      <c r="B107" s="32" t="n"/>
+      <c r="C107" s="32" t="n"/>
+      <c r="D107" s="32" t="n"/>
+      <c r="E107" s="32" t="n"/>
+      <c r="F107" s="32" t="n"/>
+      <c r="G107" s="32" t="n"/>
       <c r="H107" s="32" t="n"/>
       <c r="I107" s="32" t="n"/>
       <c r="J107" s="32" t="n"/>
       <c r="K107" s="32" t="n"/>
+      <c r="L107" s="32" t="n"/>
     </row>
     <row r="108" ht="15.75" customHeight="1" s="27">
-      <c r="A108" s="21" t="n"/>
-      <c r="B108" s="21" t="n"/>
-      <c r="C108" s="21" t="n"/>
-      <c r="D108" s="21" t="n"/>
-      <c r="E108" s="21" t="n"/>
-      <c r="F108" s="21" t="n"/>
-      <c r="G108" s="21" t="n"/>
+      <c r="A108" s="32" t="n"/>
+      <c r="B108" s="32" t="n"/>
+      <c r="C108" s="32" t="n"/>
+      <c r="D108" s="32" t="n"/>
+      <c r="E108" s="32" t="n"/>
+      <c r="F108" s="32" t="n"/>
+      <c r="G108" s="32" t="n"/>
       <c r="H108" s="32" t="n"/>
       <c r="I108" s="32" t="n"/>
       <c r="J108" s="32" t="n"/>
       <c r="K108" s="32" t="n"/>
+      <c r="L108" s="32" t="n"/>
     </row>
     <row r="109" ht="15.75" customHeight="1" s="27">
-      <c r="A109" s="21" t="n"/>
-      <c r="B109" s="21" t="n"/>
-      <c r="C109" s="21" t="n"/>
-      <c r="D109" s="21" t="n"/>
-      <c r="E109" s="21" t="n"/>
-      <c r="F109" s="21" t="n"/>
-      <c r="G109" s="21" t="n"/>
+      <c r="A109" s="32" t="n"/>
+      <c r="B109" s="32" t="n"/>
+      <c r="C109" s="32" t="n"/>
+      <c r="D109" s="32" t="n"/>
+      <c r="E109" s="32" t="n"/>
+      <c r="F109" s="32" t="n"/>
+      <c r="G109" s="32" t="n"/>
       <c r="H109" s="32" t="n"/>
       <c r="I109" s="32" t="n"/>
       <c r="J109" s="32" t="n"/>
       <c r="K109" s="32" t="n"/>
+      <c r="L109" s="32" t="n"/>
     </row>
     <row r="110" ht="15.75" customHeight="1" s="27">
-      <c r="A110" s="21" t="n"/>
-      <c r="B110" s="21" t="n"/>
-      <c r="C110" s="21" t="n"/>
-      <c r="D110" s="21" t="n"/>
-      <c r="E110" s="21" t="n"/>
-      <c r="F110" s="21" t="n"/>
-      <c r="G110" s="21" t="n"/>
+      <c r="A110" s="32" t="n"/>
+      <c r="B110" s="32" t="n"/>
+      <c r="C110" s="32" t="n"/>
+      <c r="D110" s="32" t="n"/>
+      <c r="E110" s="32" t="n"/>
+      <c r="F110" s="32" t="n"/>
+      <c r="G110" s="32" t="n"/>
       <c r="H110" s="32" t="n"/>
       <c r="I110" s="32" t="n"/>
       <c r="J110" s="32" t="n"/>
       <c r="K110" s="32" t="n"/>
+      <c r="L110" s="32" t="n"/>
     </row>
     <row r="111" ht="15.75" customHeight="1" s="27">
-      <c r="A111" s="21" t="n"/>
-      <c r="B111" s="21" t="n"/>
-      <c r="C111" s="21" t="n"/>
-      <c r="D111" s="21" t="n"/>
-      <c r="E111" s="21" t="n"/>
-      <c r="F111" s="21" t="n"/>
-      <c r="G111" s="21" t="n"/>
+      <c r="A111" s="32" t="n"/>
+      <c r="B111" s="32" t="n"/>
+      <c r="C111" s="32" t="n"/>
+      <c r="D111" s="32" t="n"/>
+      <c r="E111" s="32" t="n"/>
+      <c r="F111" s="32" t="n"/>
+      <c r="G111" s="32" t="n"/>
       <c r="H111" s="32" t="n"/>
       <c r="I111" s="32" t="n"/>
       <c r="J111" s="32" t="n"/>
       <c r="K111" s="32" t="n"/>
+      <c r="L111" s="32" t="n"/>
     </row>
     <row r="112" ht="15.75" customHeight="1" s="27">
-      <c r="A112" s="21" t="n"/>
-      <c r="B112" s="21" t="n"/>
-      <c r="C112" s="21" t="n"/>
-      <c r="D112" s="21" t="n"/>
-      <c r="E112" s="21" t="n"/>
-      <c r="F112" s="21" t="n"/>
-      <c r="G112" s="21" t="n"/>
+      <c r="A112" s="32" t="n"/>
+      <c r="B112" s="32" t="n"/>
+      <c r="C112" s="32" t="n"/>
+      <c r="D112" s="32" t="n"/>
+      <c r="E112" s="32" t="n"/>
+      <c r="F112" s="32" t="n"/>
+      <c r="G112" s="32" t="n"/>
       <c r="H112" s="32" t="n"/>
       <c r="I112" s="32" t="n"/>
       <c r="J112" s="32" t="n"/>
       <c r="K112" s="32" t="n"/>
+      <c r="L112" s="32" t="n"/>
     </row>
     <row r="113" ht="15.75" customHeight="1" s="27">
-      <c r="A113" s="21" t="n"/>
-      <c r="B113" s="21" t="n"/>
-      <c r="C113" s="21" t="n"/>
-      <c r="D113" s="21" t="n"/>
-      <c r="E113" s="21" t="n"/>
-      <c r="F113" s="21" t="n"/>
-      <c r="G113" s="21" t="n"/>
+      <c r="A113" s="32" t="n"/>
+      <c r="B113" s="32" t="n"/>
+      <c r="C113" s="32" t="n"/>
+      <c r="D113" s="32" t="n"/>
+      <c r="E113" s="32" t="n"/>
+      <c r="F113" s="32" t="n"/>
+      <c r="G113" s="32" t="n"/>
       <c r="H113" s="32" t="n"/>
       <c r="I113" s="32" t="n"/>
       <c r="J113" s="32" t="n"/>
       <c r="K113" s="32" t="n"/>
+      <c r="L113" s="32" t="n"/>
     </row>
     <row r="114" ht="15.75" customHeight="1" s="27">
-      <c r="A114" s="21" t="n"/>
-      <c r="B114" s="21" t="n"/>
-      <c r="C114" s="21" t="n"/>
-      <c r="D114" s="21" t="n"/>
-      <c r="E114" s="21" t="n"/>
-      <c r="F114" s="21" t="n"/>
-      <c r="G114" s="21" t="n"/>
+      <c r="A114" s="32" t="n"/>
+      <c r="B114" s="32" t="n"/>
+      <c r="C114" s="32" t="n"/>
+      <c r="D114" s="32" t="n"/>
+      <c r="E114" s="32" t="n"/>
+      <c r="F114" s="32" t="n"/>
+      <c r="G114" s="32" t="n"/>
       <c r="H114" s="32" t="n"/>
       <c r="I114" s="32" t="n"/>
       <c r="J114" s="32" t="n"/>
       <c r="K114" s="32" t="n"/>
+      <c r="L114" s="32" t="n"/>
     </row>
     <row r="115" ht="15.75" customHeight="1" s="27">
-      <c r="A115" s="21" t="n"/>
-      <c r="B115" s="21" t="n"/>
-      <c r="C115" s="21" t="n"/>
-      <c r="D115" s="21" t="n"/>
-      <c r="E115" s="21" t="n"/>
-      <c r="F115" s="21" t="n"/>
-      <c r="G115" s="21" t="n"/>
+      <c r="A115" s="32" t="n"/>
+      <c r="B115" s="32" t="n"/>
+      <c r="C115" s="32" t="n"/>
+      <c r="D115" s="32" t="n"/>
+      <c r="E115" s="32" t="n"/>
+      <c r="F115" s="32" t="n"/>
+      <c r="G115" s="32" t="n"/>
       <c r="H115" s="32" t="n"/>
       <c r="I115" s="32" t="n"/>
       <c r="J115" s="32" t="n"/>
       <c r="K115" s="32" t="n"/>
+      <c r="L115" s="32" t="n"/>
     </row>
     <row r="116" ht="15.75" customHeight="1" s="27">
-      <c r="A116" s="21" t="n"/>
-      <c r="B116" s="21" t="n"/>
-      <c r="C116" s="21" t="n"/>
-      <c r="D116" s="21" t="n"/>
-      <c r="E116" s="21" t="n"/>
-      <c r="F116" s="21" t="n"/>
-      <c r="G116" s="21" t="n"/>
+      <c r="A116" s="32" t="n"/>
+      <c r="B116" s="32" t="n"/>
+      <c r="C116" s="32" t="n"/>
+      <c r="D116" s="32" t="n"/>
+      <c r="E116" s="32" t="n"/>
+      <c r="F116" s="32" t="n"/>
+      <c r="G116" s="32" t="n"/>
       <c r="H116" s="32" t="n"/>
       <c r="I116" s="32" t="n"/>
       <c r="J116" s="32" t="n"/>
       <c r="K116" s="32" t="n"/>
+      <c r="L116" s="32" t="n"/>
     </row>
     <row r="117" ht="15.75" customHeight="1" s="27">
-      <c r="A117" s="21" t="n"/>
-      <c r="B117" s="21" t="n"/>
-      <c r="C117" s="21" t="n"/>
-      <c r="D117" s="21" t="n"/>
-      <c r="E117" s="21" t="n"/>
-      <c r="F117" s="21" t="n"/>
-      <c r="G117" s="21" t="n"/>
+      <c r="A117" s="32" t="n"/>
+      <c r="B117" s="32" t="n"/>
+      <c r="C117" s="32" t="n"/>
+      <c r="D117" s="32" t="n"/>
+      <c r="E117" s="32" t="n"/>
+      <c r="F117" s="32" t="n"/>
+      <c r="G117" s="32" t="n"/>
       <c r="H117" s="32" t="n"/>
       <c r="I117" s="32" t="n"/>
       <c r="J117" s="32" t="n"/>
       <c r="K117" s="32" t="n"/>
+      <c r="L117" s="32" t="n"/>
     </row>
     <row r="118" ht="15.75" customHeight="1" s="27">
-      <c r="A118" s="21" t="n"/>
-      <c r="B118" s="21" t="n"/>
-      <c r="C118" s="21" t="n"/>
-      <c r="D118" s="21" t="n"/>
-      <c r="E118" s="21" t="n"/>
-      <c r="F118" s="21" t="n"/>
-      <c r="G118" s="21" t="n"/>
+      <c r="A118" s="32" t="n"/>
+      <c r="B118" s="32" t="n"/>
+      <c r="C118" s="32" t="n"/>
+      <c r="D118" s="32" t="n"/>
+      <c r="E118" s="32" t="n"/>
+      <c r="F118" s="32" t="n"/>
+      <c r="G118" s="32" t="n"/>
       <c r="H118" s="32" t="n"/>
       <c r="I118" s="32" t="n"/>
       <c r="J118" s="32" t="n"/>
       <c r="K118" s="32" t="n"/>
+      <c r="L118" s="32" t="n"/>
     </row>
     <row r="119" ht="15.75" customHeight="1" s="27">
-      <c r="A119" s="21" t="n"/>
-      <c r="B119" s="21" t="n"/>
-      <c r="C119" s="21" t="n"/>
-      <c r="D119" s="21" t="n"/>
-      <c r="E119" s="21" t="n"/>
-      <c r="F119" s="21" t="n"/>
-      <c r="G119" s="21" t="n"/>
+      <c r="A119" s="32" t="n"/>
+      <c r="B119" s="32" t="n"/>
+      <c r="C119" s="32" t="n"/>
+      <c r="D119" s="32" t="n"/>
+      <c r="E119" s="32" t="n"/>
+      <c r="F119" s="32" t="n"/>
+      <c r="G119" s="32" t="n"/>
       <c r="H119" s="32" t="n"/>
       <c r="I119" s="32" t="n"/>
       <c r="J119" s="32" t="n"/>
       <c r="K119" s="32" t="n"/>
+      <c r="L119" s="32" t="n"/>
     </row>
     <row r="120" ht="15.75" customHeight="1" s="27">
-      <c r="A120" s="21" t="n"/>
-      <c r="B120" s="21" t="n"/>
-      <c r="C120" s="21" t="n"/>
-      <c r="D120" s="21" t="n"/>
-      <c r="E120" s="21" t="n"/>
-      <c r="F120" s="21" t="n"/>
-      <c r="G120" s="21" t="n"/>
+      <c r="A120" s="32" t="n"/>
+      <c r="B120" s="32" t="n"/>
+      <c r="C120" s="32" t="n"/>
+      <c r="D120" s="32" t="n"/>
+      <c r="E120" s="32" t="n"/>
+      <c r="F120" s="32" t="n"/>
+      <c r="G120" s="32" t="n"/>
       <c r="H120" s="32" t="n"/>
       <c r="I120" s="32" t="n"/>
       <c r="J120" s="32" t="n"/>
       <c r="K120" s="32" t="n"/>
+      <c r="L120" s="32" t="n"/>
     </row>
     <row r="121" ht="15.75" customHeight="1" s="27">
-      <c r="A121" s="21" t="n"/>
-      <c r="B121" s="21" t="n"/>
-      <c r="C121" s="21" t="n"/>
-      <c r="D121" s="21" t="n"/>
-      <c r="E121" s="21" t="n"/>
-      <c r="F121" s="21" t="n"/>
-      <c r="G121" s="21" t="n"/>
+      <c r="A121" s="32" t="n"/>
+      <c r="B121" s="32" t="n"/>
+      <c r="C121" s="32" t="n"/>
+      <c r="D121" s="32" t="n"/>
+      <c r="E121" s="32" t="n"/>
+      <c r="F121" s="32" t="n"/>
+      <c r="G121" s="32" t="n"/>
       <c r="H121" s="32" t="n"/>
       <c r="I121" s="32" t="n"/>
       <c r="J121" s="32" t="n"/>
       <c r="K121" s="32" t="n"/>
+      <c r="L121" s="32" t="n"/>
     </row>
     <row r="122" ht="15.75" customHeight="1" s="27">
-      <c r="A122" s="21" t="n"/>
-      <c r="B122" s="21" t="n"/>
-      <c r="C122" s="21" t="n"/>
-      <c r="D122" s="21" t="n"/>
-      <c r="E122" s="21" t="n"/>
-      <c r="F122" s="21" t="n"/>
-      <c r="G122" s="21" t="n"/>
+      <c r="A122" s="32" t="n"/>
+      <c r="B122" s="32" t="n"/>
+      <c r="C122" s="32" t="n"/>
+      <c r="D122" s="32" t="n"/>
+      <c r="E122" s="32" t="n"/>
+      <c r="F122" s="32" t="n"/>
+      <c r="G122" s="32" t="n"/>
       <c r="H122" s="32" t="n"/>
       <c r="I122" s="32" t="n"/>
       <c r="J122" s="32" t="n"/>
       <c r="K122" s="32" t="n"/>
+      <c r="L122" s="32" t="n"/>
     </row>
     <row r="123" ht="15.75" customHeight="1" s="27">
-      <c r="A123" s="21" t="n"/>
-      <c r="B123" s="21" t="n"/>
-      <c r="C123" s="21" t="n"/>
-      <c r="D123" s="21" t="n"/>
-      <c r="E123" s="21" t="n"/>
-      <c r="F123" s="21" t="n"/>
-      <c r="G123" s="21" t="n"/>
+      <c r="A123" s="32" t="n"/>
+      <c r="B123" s="32" t="n"/>
+      <c r="C123" s="32" t="n"/>
+      <c r="D123" s="32" t="n"/>
+      <c r="E123" s="32" t="n"/>
+      <c r="F123" s="32" t="n"/>
+      <c r="G123" s="32" t="n"/>
       <c r="H123" s="32" t="n"/>
       <c r="I123" s="32" t="n"/>
       <c r="J123" s="32" t="n"/>
       <c r="K123" s="32" t="n"/>
+      <c r="L123" s="32" t="n"/>
     </row>
     <row r="124" ht="15.75" customHeight="1" s="27">
-      <c r="A124" s="21" t="n"/>
-      <c r="B124" s="21" t="n"/>
-      <c r="C124" s="21" t="n"/>
-      <c r="D124" s="21" t="n"/>
-      <c r="E124" s="21" t="n"/>
-      <c r="F124" s="21" t="n"/>
-      <c r="G124" s="21" t="n"/>
+      <c r="A124" s="32" t="n"/>
+      <c r="B124" s="32" t="n"/>
+      <c r="C124" s="32" t="n"/>
+      <c r="D124" s="32" t="n"/>
+      <c r="E124" s="32" t="n"/>
+      <c r="F124" s="32" t="n"/>
+      <c r="G124" s="32" t="n"/>
       <c r="H124" s="32" t="n"/>
       <c r="I124" s="32" t="n"/>
       <c r="J124" s="32" t="n"/>
       <c r="K124" s="32" t="n"/>
+      <c r="L124" s="32" t="n"/>
     </row>
     <row r="125" ht="15.75" customHeight="1" s="27">
-      <c r="A125" s="21" t="n"/>
-      <c r="B125" s="21" t="n"/>
-      <c r="C125" s="21" t="n"/>
-      <c r="D125" s="21" t="n"/>
-      <c r="E125" s="21" t="n"/>
-      <c r="F125" s="21" t="n"/>
-      <c r="G125" s="21" t="n"/>
+      <c r="A125" s="32" t="n"/>
+      <c r="B125" s="32" t="n"/>
+      <c r="C125" s="32" t="n"/>
+      <c r="D125" s="32" t="n"/>
+      <c r="E125" s="32" t="n"/>
+      <c r="F125" s="32" t="n"/>
+      <c r="G125" s="32" t="n"/>
       <c r="H125" s="32" t="n"/>
       <c r="I125" s="32" t="n"/>
       <c r="J125" s="32" t="n"/>
       <c r="K125" s="32" t="n"/>
+      <c r="L125" s="32" t="n"/>
     </row>
     <row r="126" ht="15.75" customHeight="1" s="27">
-      <c r="A126" s="21" t="n"/>
-      <c r="B126" s="21" t="n"/>
-      <c r="C126" s="21" t="n"/>
-      <c r="D126" s="21" t="n"/>
-      <c r="E126" s="21" t="n"/>
-      <c r="F126" s="21" t="n"/>
-      <c r="G126" s="21" t="n"/>
+      <c r="A126" s="32" t="n"/>
+      <c r="B126" s="32" t="n"/>
+      <c r="C126" s="32" t="n"/>
+      <c r="D126" s="32" t="n"/>
+      <c r="E126" s="32" t="n"/>
+      <c r="F126" s="32" t="n"/>
+      <c r="G126" s="32" t="n"/>
       <c r="H126" s="32" t="n"/>
       <c r="I126" s="32" t="n"/>
       <c r="J126" s="32" t="n"/>
       <c r="K126" s="32" t="n"/>
+      <c r="L126" s="32" t="n"/>
     </row>
     <row r="127" ht="15.75" customHeight="1" s="27">
-      <c r="A127" s="21" t="n"/>
-      <c r="B127" s="21" t="n"/>
-      <c r="C127" s="21" t="n"/>
-      <c r="D127" s="21" t="n"/>
-      <c r="E127" s="21" t="n"/>
-      <c r="F127" s="21" t="n"/>
-      <c r="G127" s="21" t="n"/>
+      <c r="A127" s="32" t="n"/>
+      <c r="B127" s="32" t="n"/>
+      <c r="C127" s="32" t="n"/>
+      <c r="D127" s="32" t="n"/>
+      <c r="E127" s="32" t="n"/>
+      <c r="F127" s="32" t="n"/>
+      <c r="G127" s="32" t="n"/>
       <c r="H127" s="32" t="n"/>
       <c r="I127" s="32" t="n"/>
       <c r="J127" s="32" t="n"/>
       <c r="K127" s="32" t="n"/>
+      <c r="L127" s="32" t="n"/>
     </row>
     <row r="128" ht="15.75" customHeight="1" s="27">
-      <c r="A128" s="21" t="n"/>
-      <c r="B128" s="21" t="n"/>
-      <c r="C128" s="21" t="n"/>
-      <c r="D128" s="21" t="n"/>
-      <c r="E128" s="21" t="n"/>
-      <c r="F128" s="21" t="n"/>
-      <c r="G128" s="21" t="n"/>
+      <c r="A128" s="32" t="n"/>
+      <c r="B128" s="32" t="n"/>
+      <c r="C128" s="32" t="n"/>
+      <c r="D128" s="32" t="n"/>
+      <c r="E128" s="32" t="n"/>
+      <c r="F128" s="32" t="n"/>
+      <c r="G128" s="32" t="n"/>
       <c r="H128" s="32" t="n"/>
       <c r="I128" s="32" t="n"/>
       <c r="J128" s="32" t="n"/>
       <c r="K128" s="32" t="n"/>
+      <c r="L128" s="32" t="n"/>
     </row>
     <row r="129" ht="15.75" customHeight="1" s="27">
-      <c r="A129" s="21" t="n"/>
-      <c r="B129" s="21" t="n"/>
-      <c r="C129" s="21" t="n"/>
-      <c r="D129" s="21" t="n"/>
-      <c r="E129" s="21" t="n"/>
-      <c r="F129" s="21" t="n"/>
-      <c r="G129" s="21" t="n"/>
+      <c r="A129" s="32" t="n"/>
+      <c r="B129" s="32" t="n"/>
+      <c r="C129" s="32" t="n"/>
+      <c r="D129" s="32" t="n"/>
+      <c r="E129" s="32" t="n"/>
+      <c r="F129" s="32" t="n"/>
+      <c r="G129" s="32" t="n"/>
       <c r="H129" s="32" t="n"/>
       <c r="I129" s="32" t="n"/>
       <c r="J129" s="32" t="n"/>
       <c r="K129" s="32" t="n"/>
+      <c r="L129" s="32" t="n"/>
     </row>
     <row r="130" ht="15.75" customHeight="1" s="27">
-      <c r="A130" s="21" t="n"/>
-      <c r="B130" s="21" t="n"/>
-      <c r="C130" s="21" t="n"/>
-      <c r="D130" s="21" t="n"/>
-      <c r="E130" s="21" t="n"/>
-      <c r="F130" s="21" t="n"/>
-      <c r="G130" s="21" t="n"/>
+      <c r="A130" s="32" t="n"/>
+      <c r="B130" s="32" t="n"/>
+      <c r="C130" s="32" t="n"/>
+      <c r="D130" s="32" t="n"/>
+      <c r="E130" s="32" t="n"/>
+      <c r="F130" s="32" t="n"/>
+      <c r="G130" s="32" t="n"/>
       <c r="H130" s="32" t="n"/>
       <c r="I130" s="32" t="n"/>
       <c r="J130" s="32" t="n"/>
       <c r="K130" s="32" t="n"/>
+      <c r="L130" s="32" t="n"/>
     </row>
     <row r="131" ht="15.75" customHeight="1" s="27">
-      <c r="A131" s="21" t="n"/>
-      <c r="B131" s="21" t="n"/>
-      <c r="C131" s="21" t="n"/>
-      <c r="D131" s="21" t="n"/>
-      <c r="E131" s="21" t="n"/>
-      <c r="F131" s="21" t="n"/>
-      <c r="G131" s="21" t="n"/>
+      <c r="A131" s="32" t="n"/>
+      <c r="B131" s="32" t="n"/>
+      <c r="C131" s="32" t="n"/>
+      <c r="D131" s="32" t="n"/>
+      <c r="E131" s="32" t="n"/>
+      <c r="F131" s="32" t="n"/>
+      <c r="G131" s="32" t="n"/>
       <c r="H131" s="32" t="n"/>
       <c r="I131" s="32" t="n"/>
       <c r="J131" s="32" t="n"/>
       <c r="K131" s="32" t="n"/>
+      <c r="L131" s="32" t="n"/>
     </row>
     <row r="132" ht="15.75" customHeight="1" s="27">
-      <c r="A132" s="21" t="n"/>
-      <c r="B132" s="21" t="n"/>
-      <c r="C132" s="21" t="n"/>
-      <c r="D132" s="21" t="n"/>
-      <c r="E132" s="21" t="n"/>
-      <c r="F132" s="21" t="n"/>
-      <c r="G132" s="21" t="n"/>
+      <c r="A132" s="32" t="n"/>
+      <c r="B132" s="32" t="n"/>
+      <c r="C132" s="32" t="n"/>
+      <c r="D132" s="32" t="n"/>
+      <c r="E132" s="32" t="n"/>
+      <c r="F132" s="32" t="n"/>
+      <c r="G132" s="32" t="n"/>
       <c r="H132" s="32" t="n"/>
       <c r="I132" s="32" t="n"/>
       <c r="J132" s="32" t="n"/>
       <c r="K132" s="32" t="n"/>
+      <c r="L132" s="32" t="n"/>
     </row>
     <row r="133" ht="15.75" customHeight="1" s="27">
-      <c r="A133" s="21" t="n"/>
-      <c r="B133" s="21" t="n"/>
-      <c r="C133" s="21" t="n"/>
-      <c r="D133" s="21" t="n"/>
-      <c r="E133" s="21" t="n"/>
-      <c r="F133" s="21" t="n"/>
-      <c r="G133" s="21" t="n"/>
+      <c r="A133" s="32" t="n"/>
+      <c r="B133" s="32" t="n"/>
+      <c r="C133" s="32" t="n"/>
+      <c r="D133" s="32" t="n"/>
+      <c r="E133" s="32" t="n"/>
+      <c r="F133" s="32" t="n"/>
+      <c r="G133" s="32" t="n"/>
       <c r="H133" s="32" t="n"/>
       <c r="I133" s="32" t="n"/>
       <c r="J133" s="32" t="n"/>
       <c r="K133" s="32" t="n"/>
+      <c r="L133" s="32" t="n"/>
     </row>
     <row r="134" ht="15.75" customHeight="1" s="27">
-      <c r="A134" s="21" t="n"/>
-      <c r="B134" s="21" t="n"/>
-      <c r="C134" s="21" t="n"/>
-      <c r="D134" s="21" t="n"/>
-      <c r="E134" s="21" t="n"/>
-      <c r="F134" s="21" t="n"/>
-      <c r="G134" s="21" t="n"/>
+      <c r="A134" s="32" t="n"/>
+      <c r="B134" s="32" t="n"/>
+      <c r="C134" s="32" t="n"/>
+      <c r="D134" s="32" t="n"/>
+      <c r="E134" s="32" t="n"/>
+      <c r="F134" s="32" t="n"/>
+      <c r="G134" s="32" t="n"/>
       <c r="H134" s="32" t="n"/>
       <c r="I134" s="32" t="n"/>
       <c r="J134" s="32" t="n"/>
       <c r="K134" s="32" t="n"/>
+      <c r="L134" s="32" t="n"/>
     </row>
     <row r="135" ht="15.75" customHeight="1" s="27">
-      <c r="A135" s="21" t="n"/>
-      <c r="B135" s="21" t="n"/>
-      <c r="C135" s="21" t="n"/>
-      <c r="D135" s="21" t="n"/>
-      <c r="E135" s="21" t="n"/>
-      <c r="F135" s="21" t="n"/>
-      <c r="G135" s="21" t="n"/>
+      <c r="A135" s="32" t="n"/>
+      <c r="B135" s="32" t="n"/>
+      <c r="C135" s="32" t="n"/>
+      <c r="D135" s="32" t="n"/>
+      <c r="E135" s="32" t="n"/>
+      <c r="F135" s="32" t="n"/>
+      <c r="G135" s="32" t="n"/>
       <c r="H135" s="32" t="n"/>
       <c r="I135" s="32" t="n"/>
       <c r="J135" s="32" t="n"/>
       <c r="K135" s="32" t="n"/>
+      <c r="L135" s="32" t="n"/>
     </row>
     <row r="136" ht="15.75" customHeight="1" s="27">
-      <c r="A136" s="21" t="n"/>
-      <c r="B136" s="21" t="n"/>
-      <c r="C136" s="21" t="n"/>
-      <c r="D136" s="21" t="n"/>
-      <c r="E136" s="21" t="n"/>
-      <c r="F136" s="21" t="n"/>
-      <c r="G136" s="21" t="n"/>
+      <c r="A136" s="32" t="n"/>
+      <c r="B136" s="32" t="n"/>
+      <c r="C136" s="32" t="n"/>
+      <c r="D136" s="32" t="n"/>
+      <c r="E136" s="32" t="n"/>
+      <c r="F136" s="32" t="n"/>
+      <c r="G136" s="32" t="n"/>
       <c r="H136" s="32" t="n"/>
       <c r="I136" s="32" t="n"/>
       <c r="J136" s="32" t="n"/>
       <c r="K136" s="32" t="n"/>
+      <c r="L136" s="32" t="n"/>
     </row>
     <row r="137" ht="15.75" customHeight="1" s="27">
-      <c r="A137" s="21" t="n"/>
-      <c r="B137" s="21" t="n"/>
-      <c r="C137" s="21" t="n"/>
-      <c r="D137" s="21" t="n"/>
-      <c r="E137" s="21" t="n"/>
-      <c r="F137" s="21" t="n"/>
-      <c r="G137" s="21" t="n"/>
+      <c r="A137" s="32" t="n"/>
+      <c r="B137" s="32" t="n"/>
+      <c r="C137" s="32" t="n"/>
+      <c r="D137" s="32" t="n"/>
+      <c r="E137" s="32" t="n"/>
+      <c r="F137" s="32" t="n"/>
+      <c r="G137" s="32" t="n"/>
       <c r="H137" s="32" t="n"/>
       <c r="I137" s="32" t="n"/>
       <c r="J137" s="32" t="n"/>
       <c r="K137" s="32" t="n"/>
+      <c r="L137" s="32" t="n"/>
     </row>
     <row r="138" ht="15.75" customHeight="1" s="27">
-      <c r="A138" s="21" t="n"/>
-      <c r="B138" s="21" t="n"/>
-      <c r="C138" s="21" t="n"/>
-      <c r="D138" s="21" t="n"/>
-      <c r="E138" s="21" t="n"/>
-      <c r="F138" s="21" t="n"/>
-      <c r="G138" s="21" t="n"/>
+      <c r="A138" s="32" t="n"/>
+      <c r="B138" s="32" t="n"/>
+      <c r="C138" s="32" t="n"/>
+      <c r="D138" s="32" t="n"/>
+      <c r="E138" s="32" t="n"/>
+      <c r="F138" s="32" t="n"/>
+      <c r="G138" s="32" t="n"/>
       <c r="H138" s="32" t="n"/>
       <c r="I138" s="32" t="n"/>
       <c r="J138" s="32" t="n"/>
       <c r="K138" s="32" t="n"/>
+      <c r="L138" s="32" t="n"/>
     </row>
     <row r="139" ht="15.75" customHeight="1" s="27">
-      <c r="A139" s="21" t="n"/>
-      <c r="B139" s="21" t="n"/>
-      <c r="C139" s="21" t="n"/>
-      <c r="D139" s="21" t="n"/>
-      <c r="E139" s="21" t="n"/>
-      <c r="F139" s="21" t="n"/>
-      <c r="G139" s="21" t="n"/>
+      <c r="A139" s="32" t="n"/>
+      <c r="B139" s="32" t="n"/>
+      <c r="C139" s="32" t="n"/>
+      <c r="D139" s="32" t="n"/>
+      <c r="E139" s="32" t="n"/>
+      <c r="F139" s="32" t="n"/>
+      <c r="G139" s="32" t="n"/>
       <c r="H139" s="32" t="n"/>
       <c r="I139" s="32" t="n"/>
       <c r="J139" s="32" t="n"/>
       <c r="K139" s="32" t="n"/>
+      <c r="L139" s="32" t="n"/>
     </row>
     <row r="140" ht="15.75" customHeight="1" s="27">
-      <c r="A140" s="21" t="n"/>
-      <c r="B140" s="21" t="n"/>
-      <c r="C140" s="21" t="n"/>
-      <c r="D140" s="21" t="n"/>
-      <c r="E140" s="21" t="n"/>
-      <c r="F140" s="21" t="n"/>
-      <c r="G140" s="21" t="n"/>
+      <c r="A140" s="32" t="n"/>
+      <c r="B140" s="32" t="n"/>
+      <c r="C140" s="32" t="n"/>
+      <c r="D140" s="32" t="n"/>
+      <c r="E140" s="32" t="n"/>
+      <c r="F140" s="32" t="n"/>
+      <c r="G140" s="32" t="n"/>
       <c r="H140" s="32" t="n"/>
       <c r="I140" s="32" t="n"/>
       <c r="J140" s="32" t="n"/>
       <c r="K140" s="32" t="n"/>
+      <c r="L140" s="32" t="n"/>
     </row>
     <row r="141" ht="15.75" customHeight="1" s="27">
-      <c r="A141" s="21" t="n"/>
-      <c r="B141" s="21" t="n"/>
-      <c r="C141" s="21" t="n"/>
-      <c r="D141" s="21" t="n"/>
-      <c r="E141" s="21" t="n"/>
-      <c r="F141" s="21" t="n"/>
-      <c r="G141" s="21" t="n"/>
+      <c r="A141" s="32" t="n"/>
+      <c r="B141" s="32" t="n"/>
+      <c r="C141" s="32" t="n"/>
+      <c r="D141" s="32" t="n"/>
+      <c r="E141" s="32" t="n"/>
+      <c r="F141" s="32" t="n"/>
+      <c r="G141" s="32" t="n"/>
       <c r="H141" s="32" t="n"/>
       <c r="I141" s="32" t="n"/>
       <c r="J141" s="32" t="n"/>
       <c r="K141" s="32" t="n"/>
+      <c r="L141" s="32" t="n"/>
     </row>
     <row r="142" ht="15.75" customHeight="1" s="27">
-      <c r="A142" s="21" t="n"/>
-      <c r="B142" s="21" t="n"/>
-      <c r="C142" s="21" t="n"/>
-      <c r="D142" s="21" t="n"/>
-      <c r="E142" s="21" t="n"/>
-      <c r="F142" s="21" t="n"/>
-      <c r="G142" s="21" t="n"/>
+      <c r="A142" s="32" t="n"/>
+      <c r="B142" s="32" t="n"/>
+      <c r="C142" s="32" t="n"/>
+      <c r="D142" s="32" t="n"/>
+      <c r="E142" s="32" t="n"/>
+      <c r="F142" s="32" t="n"/>
+      <c r="G142" s="32" t="n"/>
       <c r="H142" s="32" t="n"/>
       <c r="I142" s="32" t="n"/>
       <c r="J142" s="32" t="n"/>
       <c r="K142" s="32" t="n"/>
+      <c r="L142" s="32" t="n"/>
     </row>
     <row r="143" ht="15.75" customHeight="1" s="27">
-      <c r="A143" s="21" t="n"/>
-      <c r="B143" s="21" t="n"/>
-      <c r="C143" s="21" t="n"/>
-      <c r="D143" s="21" t="n"/>
-      <c r="E143" s="21" t="n"/>
-      <c r="F143" s="21" t="n"/>
-      <c r="G143" s="21" t="n"/>
+      <c r="A143" s="32" t="n"/>
+      <c r="B143" s="32" t="n"/>
+      <c r="C143" s="32" t="n"/>
+      <c r="D143" s="32" t="n"/>
+      <c r="E143" s="32" t="n"/>
+      <c r="F143" s="32" t="n"/>
+      <c r="G143" s="32" t="n"/>
       <c r="H143" s="32" t="n"/>
       <c r="I143" s="32" t="n"/>
       <c r="J143" s="32" t="n"/>
       <c r="K143" s="32" t="n"/>
+      <c r="L143" s="32" t="n"/>
     </row>
     <row r="144" ht="15.75" customHeight="1" s="27">
-      <c r="A144" s="21" t="n"/>
-      <c r="B144" s="21" t="n"/>
-      <c r="C144" s="21" t="n"/>
-      <c r="D144" s="21" t="n"/>
-      <c r="E144" s="21" t="n"/>
-      <c r="F144" s="21" t="n"/>
-      <c r="G144" s="21" t="n"/>
+      <c r="A144" s="32" t="n"/>
+      <c r="B144" s="32" t="n"/>
+      <c r="C144" s="32" t="n"/>
+      <c r="D144" s="32" t="n"/>
+      <c r="E144" s="32" t="n"/>
+      <c r="F144" s="32" t="n"/>
+      <c r="G144" s="32" t="n"/>
       <c r="H144" s="32" t="n"/>
       <c r="I144" s="32" t="n"/>
       <c r="J144" s="32" t="n"/>
       <c r="K144" s="32" t="n"/>
+      <c r="L144" s="32" t="n"/>
     </row>
     <row r="145" ht="15.75" customHeight="1" s="27">
-      <c r="A145" s="21" t="n"/>
-      <c r="B145" s="21" t="n"/>
-      <c r="C145" s="21" t="n"/>
-      <c r="D145" s="21" t="n"/>
-      <c r="E145" s="21" t="n"/>
-      <c r="F145" s="21" t="n"/>
-      <c r="G145" s="21" t="n"/>
+      <c r="A145" s="32" t="n"/>
+      <c r="B145" s="32" t="n"/>
+      <c r="C145" s="32" t="n"/>
+      <c r="D145" s="32" t="n"/>
+      <c r="E145" s="32" t="n"/>
+      <c r="F145" s="32" t="n"/>
+      <c r="G145" s="32" t="n"/>
       <c r="H145" s="32" t="n"/>
       <c r="I145" s="32" t="n"/>
       <c r="J145" s="32" t="n"/>
       <c r="K145" s="32" t="n"/>
+      <c r="L145" s="32" t="n"/>
     </row>
     <row r="146" ht="15.75" customHeight="1" s="27">
-      <c r="A146" s="21" t="n"/>
-      <c r="B146" s="21" t="n"/>
-      <c r="C146" s="21" t="n"/>
-      <c r="D146" s="21" t="n"/>
-      <c r="E146" s="21" t="n"/>
-      <c r="F146" s="21" t="n"/>
-      <c r="G146" s="21" t="n"/>
+      <c r="A146" s="32" t="n"/>
+      <c r="B146" s="32" t="n"/>
+      <c r="C146" s="32" t="n"/>
+      <c r="D146" s="32" t="n"/>
+      <c r="E146" s="32" t="n"/>
+      <c r="F146" s="32" t="n"/>
+      <c r="G146" s="32" t="n"/>
       <c r="H146" s="32" t="n"/>
       <c r="I146" s="32" t="n"/>
       <c r="J146" s="32" t="n"/>
       <c r="K146" s="32" t="n"/>
+      <c r="L146" s="32" t="n"/>
     </row>
     <row r="147" ht="15.75" customHeight="1" s="27">
-      <c r="A147" s="21" t="n"/>
-      <c r="B147" s="21" t="n"/>
-      <c r="C147" s="21" t="n"/>
-      <c r="D147" s="21" t="n"/>
-      <c r="E147" s="21" t="n"/>
-      <c r="F147" s="21" t="n"/>
-      <c r="G147" s="21" t="n"/>
+      <c r="A147" s="32" t="n"/>
+      <c r="B147" s="32" t="n"/>
+      <c r="C147" s="32" t="n"/>
+      <c r="D147" s="32" t="n"/>
+      <c r="E147" s="32" t="n"/>
+      <c r="F147" s="32" t="n"/>
+      <c r="G147" s="32" t="n"/>
       <c r="H147" s="32" t="n"/>
       <c r="I147" s="32" t="n"/>
       <c r="J147" s="32" t="n"/>
       <c r="K147" s="32" t="n"/>
+      <c r="L147" s="32" t="n"/>
     </row>
     <row r="148" ht="15.75" customHeight="1" s="27">
-      <c r="A148" s="21" t="n"/>
-      <c r="B148" s="21" t="n"/>
-      <c r="C148" s="21" t="n"/>
-      <c r="D148" s="21" t="n"/>
-      <c r="E148" s="21" t="n"/>
-      <c r="F148" s="21" t="n"/>
-      <c r="G148" s="21" t="n"/>
+      <c r="A148" s="32" t="n"/>
+      <c r="B148" s="32" t="n"/>
+      <c r="C148" s="32" t="n"/>
+      <c r="D148" s="32" t="n"/>
+      <c r="E148" s="32" t="n"/>
+      <c r="F148" s="32" t="n"/>
+      <c r="G148" s="32" t="n"/>
       <c r="H148" s="32" t="n"/>
       <c r="I148" s="32" t="n"/>
       <c r="J148" s="32" t="n"/>
       <c r="K148" s="32" t="n"/>
+      <c r="L148" s="32" t="n"/>
     </row>
     <row r="149" ht="15.75" customHeight="1" s="27">
-      <c r="A149" s="21" t="n"/>
-      <c r="B149" s="21" t="n"/>
-      <c r="C149" s="21" t="n"/>
-      <c r="D149" s="21" t="n"/>
-      <c r="E149" s="21" t="n"/>
-      <c r="F149" s="21" t="n"/>
-      <c r="G149" s="21" t="n"/>
+      <c r="A149" s="32" t="n"/>
+      <c r="B149" s="32" t="n"/>
+      <c r="C149" s="32" t="n"/>
+      <c r="D149" s="32" t="n"/>
+      <c r="E149" s="32" t="n"/>
+      <c r="F149" s="32" t="n"/>
+      <c r="G149" s="32" t="n"/>
       <c r="H149" s="32" t="n"/>
       <c r="I149" s="32" t="n"/>
       <c r="J149" s="32" t="n"/>
       <c r="K149" s="32" t="n"/>
+      <c r="L149" s="32" t="n"/>
     </row>
     <row r="150" ht="15.75" customHeight="1" s="27">
-      <c r="A150" s="21" t="n"/>
-      <c r="B150" s="21" t="n"/>
-      <c r="C150" s="21" t="n"/>
-      <c r="D150" s="21" t="n"/>
-      <c r="E150" s="21" t="n"/>
-      <c r="F150" s="21" t="n"/>
-      <c r="G150" s="21" t="n"/>
+      <c r="A150" s="32" t="n"/>
+      <c r="B150" s="32" t="n"/>
+      <c r="C150" s="32" t="n"/>
+      <c r="D150" s="32" t="n"/>
+      <c r="E150" s="32" t="n"/>
+      <c r="F150" s="32" t="n"/>
+      <c r="G150" s="32" t="n"/>
       <c r="H150" s="32" t="n"/>
       <c r="I150" s="32" t="n"/>
       <c r="J150" s="32" t="n"/>
       <c r="K150" s="32" t="n"/>
+      <c r="L150" s="32" t="n"/>
     </row>
     <row r="151" ht="15.75" customHeight="1" s="27">
-      <c r="A151" s="21" t="n"/>
-      <c r="B151" s="21" t="n"/>
-      <c r="C151" s="21" t="n"/>
-      <c r="D151" s="21" t="n"/>
-      <c r="E151" s="21" t="n"/>
-      <c r="F151" s="21" t="n"/>
-      <c r="G151" s="21" t="n"/>
+      <c r="A151" s="32" t="n"/>
+      <c r="B151" s="32" t="n"/>
+      <c r="C151" s="32" t="n"/>
+      <c r="D151" s="32" t="n"/>
+      <c r="E151" s="32" t="n"/>
+      <c r="F151" s="32" t="n"/>
+      <c r="G151" s="32" t="n"/>
       <c r="H151" s="32" t="n"/>
       <c r="I151" s="32" t="n"/>
       <c r="J151" s="32" t="n"/>
       <c r="K151" s="32" t="n"/>
+      <c r="L151" s="32" t="n"/>
     </row>
     <row r="152" ht="15.75" customHeight="1" s="27">
-      <c r="A152" s="21" t="n"/>
-      <c r="B152" s="21" t="n"/>
-      <c r="C152" s="21" t="n"/>
-      <c r="D152" s="21" t="n"/>
-      <c r="E152" s="21" t="n"/>
-      <c r="F152" s="21" t="n"/>
-      <c r="G152" s="21" t="n"/>
+      <c r="A152" s="32" t="n"/>
+      <c r="B152" s="32" t="n"/>
+      <c r="C152" s="32" t="n"/>
+      <c r="D152" s="32" t="n"/>
+      <c r="E152" s="32" t="n"/>
+      <c r="F152" s="32" t="n"/>
+      <c r="G152" s="32" t="n"/>
       <c r="H152" s="32" t="n"/>
       <c r="I152" s="32" t="n"/>
       <c r="J152" s="32" t="n"/>
       <c r="K152" s="32" t="n"/>
+      <c r="L152" s="32" t="n"/>
     </row>
     <row r="153" ht="15.75" customHeight="1" s="27">
-      <c r="A153" s="21" t="n"/>
-      <c r="B153" s="21" t="n"/>
-      <c r="C153" s="21" t="n"/>
-      <c r="D153" s="21" t="n"/>
-      <c r="E153" s="21" t="n"/>
-      <c r="F153" s="21" t="n"/>
-      <c r="G153" s="21" t="n"/>
+      <c r="A153" s="32" t="n"/>
+      <c r="B153" s="32" t="n"/>
+      <c r="C153" s="32" t="n"/>
+      <c r="D153" s="32" t="n"/>
+      <c r="E153" s="32" t="n"/>
+      <c r="F153" s="32" t="n"/>
+      <c r="G153" s="32" t="n"/>
       <c r="H153" s="32" t="n"/>
       <c r="I153" s="32" t="n"/>
       <c r="J153" s="32" t="n"/>
       <c r="K153" s="32" t="n"/>
+      <c r="L153" s="32" t="n"/>
     </row>
     <row r="154" ht="15.75" customHeight="1" s="27">
-      <c r="A154" s="21" t="n"/>
-      <c r="B154" s="21" t="n"/>
-      <c r="C154" s="21" t="n"/>
-      <c r="D154" s="21" t="n"/>
-      <c r="E154" s="21" t="n"/>
-      <c r="F154" s="21" t="n"/>
-      <c r="G154" s="21" t="n"/>
+      <c r="A154" s="32" t="n"/>
+      <c r="B154" s="32" t="n"/>
+      <c r="C154" s="32" t="n"/>
+      <c r="D154" s="32" t="n"/>
+      <c r="E154" s="32" t="n"/>
+      <c r="F154" s="32" t="n"/>
+      <c r="G154" s="32" t="n"/>
       <c r="H154" s="32" t="n"/>
       <c r="I154" s="32" t="n"/>
       <c r="J154" s="32" t="n"/>
       <c r="K154" s="32" t="n"/>
+      <c r="L154" s="32" t="n"/>
     </row>
     <row r="155" ht="15.75" customHeight="1" s="27">
-      <c r="A155" s="21" t="n"/>
-      <c r="B155" s="21" t="n"/>
-      <c r="C155" s="21" t="n"/>
-      <c r="D155" s="21" t="n"/>
-      <c r="E155" s="21" t="n"/>
-      <c r="F155" s="21" t="n"/>
-      <c r="G155" s="21" t="n"/>
+      <c r="A155" s="32" t="n"/>
+      <c r="B155" s="32" t="n"/>
+      <c r="C155" s="32" t="n"/>
+      <c r="D155" s="32" t="n"/>
+      <c r="E155" s="32" t="n"/>
+      <c r="F155" s="32" t="n"/>
+      <c r="G155" s="32" t="n"/>
       <c r="H155" s="32" t="n"/>
       <c r="I155" s="32" t="n"/>
       <c r="J155" s="32" t="n"/>
       <c r="K155" s="32" t="n"/>
+      <c r="L155" s="32" t="n"/>
     </row>
     <row r="156" ht="15.75" customHeight="1" s="27">
-      <c r="A156" s="21" t="n"/>
-      <c r="B156" s="21" t="n"/>
-      <c r="C156" s="21" t="n"/>
-      <c r="D156" s="21" t="n"/>
-      <c r="E156" s="21" t="n"/>
-      <c r="F156" s="21" t="n"/>
-      <c r="G156" s="21" t="n"/>
+      <c r="A156" s="32" t="n"/>
+      <c r="B156" s="32" t="n"/>
+      <c r="C156" s="32" t="n"/>
+      <c r="D156" s="32" t="n"/>
+      <c r="E156" s="32" t="n"/>
+      <c r="F156" s="32" t="n"/>
+      <c r="G156" s="32" t="n"/>
       <c r="H156" s="32" t="n"/>
       <c r="I156" s="32" t="n"/>
       <c r="J156" s="32" t="n"/>
       <c r="K156" s="32" t="n"/>
+      <c r="L156" s="32" t="n"/>
     </row>
     <row r="157" ht="15.75" customHeight="1" s="27">
-      <c r="A157" s="21" t="n"/>
-      <c r="B157" s="21" t="n"/>
-      <c r="C157" s="21" t="n"/>
-      <c r="D157" s="21" t="n"/>
-      <c r="E157" s="21" t="n"/>
-      <c r="F157" s="21" t="n"/>
-      <c r="G157" s="21" t="n"/>
+      <c r="A157" s="32" t="n"/>
+      <c r="B157" s="32" t="n"/>
+      <c r="C157" s="32" t="n"/>
+      <c r="D157" s="32" t="n"/>
+      <c r="E157" s="32" t="n"/>
+      <c r="F157" s="32" t="n"/>
+      <c r="G157" s="32" t="n"/>
       <c r="H157" s="32" t="n"/>
       <c r="I157" s="32" t="n"/>
       <c r="J157" s="32" t="n"/>
       <c r="K157" s="32" t="n"/>
+      <c r="L157" s="32" t="n"/>
     </row>
     <row r="158" ht="15.75" customHeight="1" s="27">
-      <c r="A158" s="21" t="n"/>
-      <c r="B158" s="21" t="n"/>
-      <c r="C158" s="21" t="n"/>
-      <c r="D158" s="21" t="n"/>
-      <c r="E158" s="21" t="n"/>
-      <c r="F158" s="21" t="n"/>
-      <c r="G158" s="21" t="n"/>
+      <c r="A158" s="32" t="n"/>
+      <c r="B158" s="32" t="n"/>
+      <c r="C158" s="32" t="n"/>
+      <c r="D158" s="32" t="n"/>
+      <c r="E158" s="32" t="n"/>
+      <c r="F158" s="32" t="n"/>
+      <c r="G158" s="32" t="n"/>
       <c r="H158" s="32" t="n"/>
       <c r="I158" s="32" t="n"/>
       <c r="J158" s="32" t="n"/>
       <c r="K158" s="32" t="n"/>
+      <c r="L158" s="32" t="n"/>
     </row>
     <row r="159" ht="15.75" customHeight="1" s="27">
-      <c r="A159" s="21" t="n"/>
-      <c r="B159" s="21" t="n"/>
-      <c r="C159" s="21" t="n"/>
-      <c r="D159" s="21" t="n"/>
-      <c r="E159" s="21" t="n"/>
-      <c r="F159" s="21" t="n"/>
-      <c r="G159" s="21" t="n"/>
+      <c r="A159" s="32" t="n"/>
+      <c r="B159" s="32" t="n"/>
+      <c r="C159" s="32" t="n"/>
+      <c r="D159" s="32" t="n"/>
+      <c r="E159" s="32" t="n"/>
+      <c r="F159" s="32" t="n"/>
+      <c r="G159" s="32" t="n"/>
       <c r="H159" s="32" t="n"/>
       <c r="I159" s="32" t="n"/>
       <c r="J159" s="32" t="n"/>
       <c r="K159" s="32" t="n"/>
+      <c r="L159" s="32" t="n"/>
     </row>
     <row r="160" ht="15.75" customHeight="1" s="27">
-      <c r="A160" s="21" t="n"/>
-      <c r="B160" s="21" t="n"/>
-      <c r="C160" s="21" t="n"/>
-      <c r="D160" s="21" t="n"/>
-      <c r="E160" s="21" t="n"/>
-      <c r="F160" s="21" t="n"/>
-      <c r="G160" s="21" t="n"/>
+      <c r="A160" s="32" t="n"/>
+      <c r="B160" s="32" t="n"/>
+      <c r="C160" s="32" t="n"/>
+      <c r="D160" s="32" t="n"/>
+      <c r="E160" s="32" t="n"/>
+      <c r="F160" s="32" t="n"/>
+      <c r="G160" s="32" t="n"/>
       <c r="H160" s="32" t="n"/>
       <c r="I160" s="32" t="n"/>
       <c r="J160" s="32" t="n"/>
       <c r="K160" s="32" t="n"/>
+      <c r="L160" s="32" t="n"/>
     </row>
     <row r="161" ht="15.75" customHeight="1" s="27">
-      <c r="A161" s="21" t="n"/>
-      <c r="B161" s="21" t="n"/>
-      <c r="C161" s="21" t="n"/>
-      <c r="D161" s="21" t="n"/>
-      <c r="E161" s="21" t="n"/>
-      <c r="F161" s="21" t="n"/>
-      <c r="G161" s="21" t="n"/>
+      <c r="A161" s="32" t="n"/>
+      <c r="B161" s="32" t="n"/>
+      <c r="C161" s="32" t="n"/>
+      <c r="D161" s="32" t="n"/>
+      <c r="E161" s="32" t="n"/>
+      <c r="F161" s="32" t="n"/>
+      <c r="G161" s="32" t="n"/>
       <c r="H161" s="32" t="n"/>
       <c r="I161" s="32" t="n"/>
       <c r="J161" s="32" t="n"/>
       <c r="K161" s="32" t="n"/>
+      <c r="L161" s="32" t="n"/>
     </row>
     <row r="162" ht="15.75" customHeight="1" s="27">
-      <c r="A162" s="21" t="n"/>
-      <c r="B162" s="21" t="n"/>
-      <c r="C162" s="21" t="n"/>
-      <c r="D162" s="21" t="n"/>
-      <c r="E162" s="21" t="n"/>
-      <c r="F162" s="21" t="n"/>
-      <c r="G162" s="21" t="n"/>
+      <c r="A162" s="32" t="n"/>
+      <c r="B162" s="32" t="n"/>
+      <c r="C162" s="32" t="n"/>
+      <c r="D162" s="32" t="n"/>
+      <c r="E162" s="32" t="n"/>
+      <c r="F162" s="32" t="n"/>
+      <c r="G162" s="32" t="n"/>
       <c r="H162" s="32" t="n"/>
       <c r="I162" s="32" t="n"/>
       <c r="J162" s="32" t="n"/>
       <c r="K162" s="32" t="n"/>
+      <c r="L162" s="32" t="n"/>
     </row>
     <row r="163" ht="15.75" customHeight="1" s="27">
-      <c r="A163" s="21" t="n"/>
-      <c r="B163" s="21" t="n"/>
-      <c r="C163" s="21" t="n"/>
-      <c r="D163" s="21" t="n"/>
-      <c r="E163" s="21" t="n"/>
-      <c r="F163" s="21" t="n"/>
-      <c r="G163" s="21" t="n"/>
+      <c r="A163" s="32" t="n"/>
+      <c r="B163" s="32" t="n"/>
+      <c r="C163" s="32" t="n"/>
+      <c r="D163" s="32" t="n"/>
+      <c r="E163" s="32" t="n"/>
+      <c r="F163" s="32" t="n"/>
+      <c r="G163" s="32" t="n"/>
       <c r="H163" s="32" t="n"/>
       <c r="I163" s="32" t="n"/>
       <c r="J163" s="32" t="n"/>
       <c r="K163" s="32" t="n"/>
+      <c r="L163" s="32" t="n"/>
     </row>
     <row r="164" ht="15.75" customHeight="1" s="27">
-      <c r="A164" s="21" t="n"/>
-      <c r="B164" s="21" t="n"/>
-      <c r="C164" s="21" t="n"/>
-      <c r="D164" s="21" t="n"/>
-      <c r="E164" s="21" t="n"/>
-      <c r="F164" s="21" t="n"/>
-      <c r="G164" s="21" t="n"/>
+      <c r="A164" s="32" t="n"/>
+      <c r="B164" s="32" t="n"/>
+      <c r="C164" s="32" t="n"/>
+      <c r="D164" s="32" t="n"/>
+      <c r="E164" s="32" t="n"/>
+      <c r="F164" s="32" t="n"/>
+      <c r="G164" s="32" t="n"/>
       <c r="H164" s="32" t="n"/>
       <c r="I164" s="32" t="n"/>
       <c r="J164" s="32" t="n"/>
       <c r="K164" s="32" t="n"/>
+      <c r="L164" s="32" t="n"/>
     </row>
     <row r="165" ht="15.75" customHeight="1" s="27">
-      <c r="A165" s="21" t="n"/>
-      <c r="B165" s="21" t="n"/>
-      <c r="C165" s="21" t="n"/>
-      <c r="D165" s="21" t="n"/>
-      <c r="E165" s="21" t="n"/>
-      <c r="F165" s="21" t="n"/>
-      <c r="G165" s="21" t="n"/>
+      <c r="A165" s="32" t="n"/>
+      <c r="B165" s="32" t="n"/>
+      <c r="C165" s="32" t="n"/>
+      <c r="D165" s="32" t="n"/>
+      <c r="E165" s="32" t="n"/>
+      <c r="F165" s="32" t="n"/>
+      <c r="G165" s="32" t="n"/>
       <c r="H165" s="32" t="n"/>
       <c r="I165" s="32" t="n"/>
       <c r="J165" s="32" t="n"/>
       <c r="K165" s="32" t="n"/>
+      <c r="L165" s="32" t="n"/>
     </row>
     <row r="166" ht="15.75" customHeight="1" s="27">
-      <c r="A166" s="21" t="n"/>
-      <c r="B166" s="21" t="n"/>
-      <c r="C166" s="21" t="n"/>
-      <c r="D166" s="21" t="n"/>
-      <c r="E166" s="21" t="n"/>
-      <c r="F166" s="21" t="n"/>
-      <c r="G166" s="21" t="n"/>
+      <c r="A166" s="32" t="n"/>
+      <c r="B166" s="32" t="n"/>
+      <c r="C166" s="32" t="n"/>
+      <c r="D166" s="32" t="n"/>
+      <c r="E166" s="32" t="n"/>
+      <c r="F166" s="32" t="n"/>
+      <c r="G166" s="32" t="n"/>
       <c r="H166" s="32" t="n"/>
       <c r="I166" s="32" t="n"/>
       <c r="J166" s="32" t="n"/>
       <c r="K166" s="32" t="n"/>
+      <c r="L166" s="32" t="n"/>
     </row>
     <row r="167" ht="15.75" customHeight="1" s="27">
-      <c r="A167" s="21" t="n"/>
-      <c r="B167" s="21" t="n"/>
-      <c r="C167" s="21" t="n"/>
-      <c r="D167" s="21" t="n"/>
-      <c r="E167" s="21" t="n"/>
-      <c r="F167" s="21" t="n"/>
-      <c r="G167" s="21" t="n"/>
+      <c r="A167" s="32" t="n"/>
+      <c r="B167" s="32" t="n"/>
+      <c r="C167" s="32" t="n"/>
+      <c r="D167" s="32" t="n"/>
+      <c r="E167" s="32" t="n"/>
+      <c r="F167" s="32" t="n"/>
+      <c r="G167" s="32" t="n"/>
       <c r="H167" s="32" t="n"/>
       <c r="I167" s="32" t="n"/>
       <c r="J167" s="32" t="n"/>
       <c r="K167" s="32" t="n"/>
+      <c r="L167" s="32" t="n"/>
     </row>
     <row r="168" ht="15.75" customHeight="1" s="27">
-      <c r="A168" s="21" t="n"/>
-      <c r="B168" s="21" t="n"/>
-      <c r="C168" s="21" t="n"/>
-      <c r="D168" s="21" t="n"/>
-      <c r="E168" s="21" t="n"/>
-      <c r="F168" s="21" t="n"/>
-      <c r="G168" s="21" t="n"/>
+      <c r="A168" s="32" t="n"/>
+      <c r="B168" s="32" t="n"/>
+      <c r="C168" s="32" t="n"/>
+      <c r="D168" s="32" t="n"/>
+      <c r="E168" s="32" t="n"/>
+      <c r="F168" s="32" t="n"/>
+      <c r="G168" s="32" t="n"/>
       <c r="H168" s="32" t="n"/>
       <c r="I168" s="32" t="n"/>
       <c r="J168" s="32" t="n"/>
       <c r="K168" s="32" t="n"/>
+      <c r="L168" s="32" t="n"/>
     </row>
     <row r="169" ht="15.75" customHeight="1" s="27">
-      <c r="A169" s="21" t="n"/>
-      <c r="B169" s="21" t="n"/>
-      <c r="C169" s="21" t="n"/>
-      <c r="D169" s="21" t="n"/>
-      <c r="E169" s="21" t="n"/>
-      <c r="F169" s="21" t="n"/>
-      <c r="G169" s="21" t="n"/>
+      <c r="A169" s="32" t="n"/>
+      <c r="B169" s="32" t="n"/>
+      <c r="C169" s="32" t="n"/>
+      <c r="D169" s="32" t="n"/>
+      <c r="E169" s="32" t="n"/>
+      <c r="F169" s="32" t="n"/>
+      <c r="G169" s="32" t="n"/>
       <c r="H169" s="32" t="n"/>
       <c r="I169" s="32" t="n"/>
       <c r="J169" s="32" t="n"/>
       <c r="K169" s="32" t="n"/>
+      <c r="L169" s="32" t="n"/>
     </row>
     <row r="170" ht="15.75" customHeight="1" s="27">
-      <c r="A170" s="21" t="n"/>
-      <c r="B170" s="21" t="n"/>
-      <c r="C170" s="21" t="n"/>
-      <c r="D170" s="21" t="n"/>
-      <c r="E170" s="21" t="n"/>
-      <c r="F170" s="21" t="n"/>
-      <c r="G170" s="21" t="n"/>
+      <c r="A170" s="32" t="n"/>
+      <c r="B170" s="32" t="n"/>
+      <c r="C170" s="32" t="n"/>
+      <c r="D170" s="32" t="n"/>
+      <c r="E170" s="32" t="n"/>
+      <c r="F170" s="32" t="n"/>
+      <c r="G170" s="32" t="n"/>
       <c r="H170" s="32" t="n"/>
       <c r="I170" s="32" t="n"/>
       <c r="J170" s="32" t="n"/>
       <c r="K170" s="32" t="n"/>
+      <c r="L170" s="32" t="n"/>
     </row>
     <row r="171" ht="15.75" customHeight="1" s="27">
-      <c r="A171" s="21" t="n"/>
-      <c r="B171" s="21" t="n"/>
-      <c r="C171" s="21" t="n"/>
-      <c r="D171" s="21" t="n"/>
-      <c r="E171" s="21" t="n"/>
-      <c r="F171" s="21" t="n"/>
-      <c r="G171" s="21" t="n"/>
+      <c r="A171" s="32" t="n"/>
+      <c r="B171" s="32" t="n"/>
+      <c r="C171" s="32" t="n"/>
+      <c r="D171" s="32" t="n"/>
+      <c r="E171" s="32" t="n"/>
+      <c r="F171" s="32" t="n"/>
+      <c r="G171" s="32" t="n"/>
       <c r="H171" s="32" t="n"/>
       <c r="I171" s="32" t="n"/>
       <c r="J171" s="32" t="n"/>
       <c r="K171" s="32" t="n"/>
+      <c r="L171" s="32" t="n"/>
     </row>
     <row r="172" ht="15.75" customHeight="1" s="27">
-      <c r="A172" s="21" t="n"/>
-      <c r="B172" s="21" t="n"/>
-      <c r="C172" s="21" t="n"/>
-      <c r="D172" s="21" t="n"/>
-      <c r="E172" s="21" t="n"/>
-      <c r="F172" s="21" t="n"/>
-      <c r="G172" s="21" t="n"/>
+      <c r="A172" s="32" t="n"/>
+      <c r="B172" s="32" t="n"/>
+      <c r="C172" s="32" t="n"/>
+      <c r="D172" s="32" t="n"/>
+      <c r="E172" s="32" t="n"/>
+      <c r="F172" s="32" t="n"/>
+      <c r="G172" s="32" t="n"/>
       <c r="H172" s="32" t="n"/>
       <c r="I172" s="32" t="n"/>
       <c r="J172" s="32" t="n"/>
       <c r="K172" s="32" t="n"/>
+      <c r="L172" s="32" t="n"/>
     </row>
     <row r="173" ht="15.75" customHeight="1" s="27">
-      <c r="A173" s="21" t="n"/>
-      <c r="B173" s="21" t="n"/>
-      <c r="C173" s="21" t="n"/>
-      <c r="D173" s="21" t="n"/>
-      <c r="E173" s="21" t="n"/>
-      <c r="F173" s="21" t="n"/>
-      <c r="G173" s="21" t="n"/>
+      <c r="A173" s="32" t="n"/>
+      <c r="B173" s="32" t="n"/>
+      <c r="C173" s="32" t="n"/>
+      <c r="D173" s="32" t="n"/>
+      <c r="E173" s="32" t="n"/>
+      <c r="F173" s="32" t="n"/>
+      <c r="G173" s="32" t="n"/>
       <c r="H173" s="32" t="n"/>
       <c r="I173" s="32" t="n"/>
       <c r="J173" s="32" t="n"/>
       <c r="K173" s="32" t="n"/>
+      <c r="L173" s="32" t="n"/>
     </row>
     <row r="174" ht="15.75" customHeight="1" s="27">
-      <c r="A174" s="21" t="n"/>
-      <c r="B174" s="21" t="n"/>
-      <c r="C174" s="21" t="n"/>
-      <c r="D174" s="21" t="n"/>
-      <c r="E174" s="21" t="n"/>
-      <c r="F174" s="21" t="n"/>
-      <c r="G174" s="21" t="n"/>
+      <c r="A174" s="32" t="n"/>
+      <c r="B174" s="32" t="n"/>
+      <c r="C174" s="32" t="n"/>
+      <c r="D174" s="32" t="n"/>
+      <c r="E174" s="32" t="n"/>
+      <c r="F174" s="32" t="n"/>
+      <c r="G174" s="32" t="n"/>
       <c r="H174" s="32" t="n"/>
       <c r="I174" s="32" t="n"/>
       <c r="J174" s="32" t="n"/>
       <c r="K174" s="32" t="n"/>
+      <c r="L174" s="32" t="n"/>
     </row>
     <row r="175" ht="15.75" customHeight="1" s="27">
-      <c r="A175" s="21" t="n"/>
-      <c r="B175" s="21" t="n"/>
-      <c r="C175" s="21" t="n"/>
-      <c r="D175" s="21" t="n"/>
-      <c r="E175" s="21" t="n"/>
-      <c r="F175" s="21" t="n"/>
-      <c r="G175" s="21" t="n"/>
+      <c r="A175" s="32" t="n"/>
+      <c r="B175" s="32" t="n"/>
+      <c r="C175" s="32" t="n"/>
+      <c r="D175" s="32" t="n"/>
+      <c r="E175" s="32" t="n"/>
+      <c r="F175" s="32" t="n"/>
+      <c r="G175" s="32" t="n"/>
       <c r="H175" s="32" t="n"/>
       <c r="I175" s="32" t="n"/>
       <c r="J175" s="32" t="n"/>
       <c r="K175" s="32" t="n"/>
+      <c r="L175" s="32" t="n"/>
     </row>
     <row r="176" ht="15.75" customHeight="1" s="27">
-      <c r="A176" s="21" t="n"/>
-      <c r="B176" s="21" t="n"/>
-      <c r="C176" s="21" t="n"/>
-      <c r="D176" s="21" t="n"/>
-      <c r="E176" s="21" t="n"/>
-      <c r="F176" s="21" t="n"/>
-      <c r="G176" s="21" t="n"/>
+      <c r="A176" s="32" t="n"/>
+      <c r="B176" s="32" t="n"/>
+      <c r="C176" s="32" t="n"/>
+      <c r="D176" s="32" t="n"/>
+      <c r="E176" s="32" t="n"/>
+      <c r="F176" s="32" t="n"/>
+      <c r="G176" s="32" t="n"/>
       <c r="H176" s="32" t="n"/>
       <c r="I176" s="32" t="n"/>
       <c r="J176" s="32" t="n"/>
       <c r="K176" s="32" t="n"/>
+      <c r="L176" s="32" t="n"/>
     </row>
     <row r="177" ht="15.75" customHeight="1" s="27">
-      <c r="A177" s="21" t="n"/>
-      <c r="B177" s="21" t="n"/>
-      <c r="C177" s="21" t="n"/>
-      <c r="D177" s="21" t="n"/>
-      <c r="E177" s="21" t="n"/>
-      <c r="F177" s="21" t="n"/>
-      <c r="G177" s="21" t="n"/>
+      <c r="A177" s="32" t="n"/>
+      <c r="B177" s="32" t="n"/>
+      <c r="C177" s="32" t="n"/>
+      <c r="D177" s="32" t="n"/>
+      <c r="E177" s="32" t="n"/>
+      <c r="F177" s="32" t="n"/>
+      <c r="G177" s="32" t="n"/>
       <c r="H177" s="32" t="n"/>
       <c r="I177" s="32" t="n"/>
       <c r="J177" s="32" t="n"/>
       <c r="K177" s="32" t="n"/>
+      <c r="L177" s="32" t="n"/>
     </row>
     <row r="178" ht="15.75" customHeight="1" s="27">
-      <c r="A178" s="21" t="n"/>
-      <c r="B178" s="21" t="n"/>
-      <c r="C178" s="21" t="n"/>
-      <c r="D178" s="21" t="n"/>
-      <c r="E178" s="21" t="n"/>
-      <c r="F178" s="21" t="n"/>
-      <c r="G178" s="21" t="n"/>
+      <c r="A178" s="32" t="n"/>
+      <c r="B178" s="32" t="n"/>
+      <c r="C178" s="32" t="n"/>
+      <c r="D178" s="32" t="n"/>
+      <c r="E178" s="32" t="n"/>
+      <c r="F178" s="32" t="n"/>
+      <c r="G178" s="32" t="n"/>
       <c r="H178" s="32" t="n"/>
       <c r="I178" s="32" t="n"/>
       <c r="J178" s="32" t="n"/>
       <c r="K178" s="32" t="n"/>
+      <c r="L178" s="32" t="n"/>
     </row>
     <row r="179" ht="15.75" customHeight="1" s="27">
-      <c r="A179" s="21" t="n"/>
-      <c r="B179" s="21" t="n"/>
-      <c r="C179" s="21" t="n"/>
-      <c r="D179" s="21" t="n"/>
-      <c r="E179" s="21" t="n"/>
-      <c r="F179" s="21" t="n"/>
-      <c r="G179" s="21" t="n"/>
+      <c r="A179" s="32" t="n"/>
+      <c r="B179" s="32" t="n"/>
+      <c r="C179" s="32" t="n"/>
+      <c r="D179" s="32" t="n"/>
+      <c r="E179" s="32" t="n"/>
+      <c r="F179" s="32" t="n"/>
+      <c r="G179" s="32" t="n"/>
       <c r="H179" s="32" t="n"/>
       <c r="I179" s="32" t="n"/>
       <c r="J179" s="32" t="n"/>
       <c r="K179" s="32" t="n"/>
+      <c r="L179" s="32" t="n"/>
     </row>
     <row r="180" ht="15.75" customHeight="1" s="27">
-      <c r="A180" s="21" t="n"/>
-      <c r="B180" s="21" t="n"/>
-      <c r="C180" s="21" t="n"/>
-      <c r="D180" s="21" t="n"/>
-      <c r="E180" s="21" t="n"/>
-      <c r="F180" s="21" t="n"/>
-      <c r="G180" s="21" t="n"/>
+      <c r="A180" s="32" t="n"/>
+      <c r="B180" s="32" t="n"/>
+      <c r="C180" s="32" t="n"/>
+      <c r="D180" s="32" t="n"/>
+      <c r="E180" s="32" t="n"/>
+      <c r="F180" s="32" t="n"/>
+      <c r="G180" s="32" t="n"/>
       <c r="H180" s="32" t="n"/>
       <c r="I180" s="32" t="n"/>
       <c r="J180" s="32" t="n"/>
       <c r="K180" s="32" t="n"/>
+      <c r="L180" s="32" t="n"/>
     </row>
     <row r="181" ht="15.75" customHeight="1" s="27">
-      <c r="A181" s="21" t="n"/>
-      <c r="B181" s="21" t="n"/>
-      <c r="C181" s="21" t="n"/>
-      <c r="D181" s="21" t="n"/>
-      <c r="E181" s="21" t="n"/>
-      <c r="F181" s="21" t="n"/>
-      <c r="G181" s="21" t="n"/>
+      <c r="A181" s="32" t="n"/>
+      <c r="B181" s="32" t="n"/>
+      <c r="C181" s="32" t="n"/>
+      <c r="D181" s="32" t="n"/>
+      <c r="E181" s="32" t="n"/>
+      <c r="F181" s="32" t="n"/>
+      <c r="G181" s="32" t="n"/>
       <c r="H181" s="32" t="n"/>
       <c r="I181" s="32" t="n"/>
       <c r="J181" s="32" t="n"/>
       <c r="K181" s="32" t="n"/>
+      <c r="L181" s="32" t="n"/>
     </row>
     <row r="182" ht="15.75" customHeight="1" s="27">
-      <c r="A182" s="21" t="n"/>
-      <c r="B182" s="21" t="n"/>
-      <c r="C182" s="21" t="n"/>
-      <c r="D182" s="21" t="n"/>
-      <c r="E182" s="21" t="n"/>
-      <c r="F182" s="21" t="n"/>
-      <c r="G182" s="21" t="n"/>
+      <c r="A182" s="32" t="n"/>
+      <c r="B182" s="32" t="n"/>
+      <c r="C182" s="32" t="n"/>
+      <c r="D182" s="32" t="n"/>
+      <c r="E182" s="32" t="n"/>
+      <c r="F182" s="32" t="n"/>
+      <c r="G182" s="32" t="n"/>
       <c r="H182" s="32" t="n"/>
       <c r="I182" s="32" t="n"/>
       <c r="J182" s="32" t="n"/>
       <c r="K182" s="32" t="n"/>
+      <c r="L182" s="32" t="n"/>
     </row>
     <row r="183" ht="15.75" customHeight="1" s="27">
-      <c r="A183" s="21" t="n"/>
-      <c r="B183" s="21" t="n"/>
-      <c r="C183" s="21" t="n"/>
-      <c r="D183" s="21" t="n"/>
-      <c r="E183" s="21" t="n"/>
-      <c r="F183" s="21" t="n"/>
-      <c r="G183" s="21" t="n"/>
+      <c r="A183" s="32" t="n"/>
+      <c r="B183" s="32" t="n"/>
+      <c r="C183" s="32" t="n"/>
+      <c r="D183" s="32" t="n"/>
+      <c r="E183" s="32" t="n"/>
+      <c r="F183" s="32" t="n"/>
+      <c r="G183" s="32" t="n"/>
       <c r="H183" s="32" t="n"/>
       <c r="I183" s="32" t="n"/>
       <c r="J183" s="32" t="n"/>
       <c r="K183" s="32" t="n"/>
+      <c r="L183" s="32" t="n"/>
     </row>
     <row r="184" ht="15.75" customHeight="1" s="27">
-      <c r="A184" s="21" t="n"/>
-      <c r="B184" s="21" t="n"/>
-      <c r="C184" s="21" t="n"/>
-      <c r="D184" s="21" t="n"/>
-      <c r="E184" s="21" t="n"/>
-      <c r="F184" s="21" t="n"/>
-      <c r="G184" s="21" t="n"/>
+      <c r="A184" s="32" t="n"/>
+      <c r="B184" s="32" t="n"/>
+      <c r="C184" s="32" t="n"/>
+      <c r="D184" s="32" t="n"/>
+      <c r="E184" s="32" t="n"/>
+      <c r="F184" s="32" t="n"/>
+      <c r="G184" s="32" t="n"/>
       <c r="H184" s="32" t="n"/>
       <c r="I184" s="32" t="n"/>
       <c r="J184" s="32" t="n"/>
       <c r="K184" s="32" t="n"/>
+      <c r="L184" s="32" t="n"/>
     </row>
     <row r="185" ht="15.75" customHeight="1" s="27">
-      <c r="A185" s="21" t="n"/>
-      <c r="B185" s="21" t="n"/>
-      <c r="C185" s="21" t="n"/>
-      <c r="D185" s="21" t="n"/>
-      <c r="E185" s="21" t="n"/>
-      <c r="F185" s="21" t="n"/>
-      <c r="G185" s="21" t="n"/>
+      <c r="A185" s="32" t="n"/>
+      <c r="B185" s="32" t="n"/>
+      <c r="C185" s="32" t="n"/>
+      <c r="D185" s="32" t="n"/>
+      <c r="E185" s="32" t="n"/>
+      <c r="F185" s="32" t="n"/>
+      <c r="G185" s="32" t="n"/>
       <c r="H185" s="32" t="n"/>
       <c r="I185" s="32" t="n"/>
       <c r="J185" s="32" t="n"/>
       <c r="K185" s="32" t="n"/>
+      <c r="L185" s="32" t="n"/>
     </row>
     <row r="186" ht="15.75" customHeight="1" s="27">
-      <c r="A186" s="21" t="n"/>
-      <c r="B186" s="21" t="n"/>
-      <c r="C186" s="21" t="n"/>
-      <c r="D186" s="21" t="n"/>
-      <c r="E186" s="21" t="n"/>
-      <c r="F186" s="21" t="n"/>
-      <c r="G186" s="21" t="n"/>
+      <c r="A186" s="32" t="n"/>
+      <c r="B186" s="32" t="n"/>
+      <c r="C186" s="32" t="n"/>
+      <c r="D186" s="32" t="n"/>
+      <c r="E186" s="32" t="n"/>
+      <c r="F186" s="32" t="n"/>
+      <c r="G186" s="32" t="n"/>
       <c r="H186" s="32" t="n"/>
       <c r="I186" s="32" t="n"/>
       <c r="J186" s="32" t="n"/>
       <c r="K186" s="32" t="n"/>
+      <c r="L186" s="32" t="n"/>
     </row>
     <row r="187" ht="15.75" customHeight="1" s="27">
-      <c r="A187" s="21" t="n"/>
-      <c r="B187" s="21" t="n"/>
-      <c r="C187" s="21" t="n"/>
-      <c r="D187" s="21" t="n"/>
-      <c r="E187" s="21" t="n"/>
-      <c r="F187" s="21" t="n"/>
-      <c r="G187" s="21" t="n"/>
+      <c r="A187" s="32" t="n"/>
+      <c r="B187" s="32" t="n"/>
+      <c r="C187" s="32" t="n"/>
+      <c r="D187" s="32" t="n"/>
+      <c r="E187" s="32" t="n"/>
+      <c r="F187" s="32" t="n"/>
+      <c r="G187" s="32" t="n"/>
       <c r="H187" s="32" t="n"/>
       <c r="I187" s="32" t="n"/>
       <c r="J187" s="32" t="n"/>
       <c r="K187" s="32" t="n"/>
+      <c r="L187" s="32" t="n"/>
     </row>
     <row r="188" ht="15.75" customHeight="1" s="27">
-      <c r="A188" s="21" t="n"/>
-      <c r="B188" s="21" t="n"/>
-      <c r="C188" s="21" t="n"/>
-      <c r="D188" s="21" t="n"/>
-      <c r="E188" s="21" t="n"/>
-      <c r="F188" s="21" t="n"/>
-      <c r="G188" s="21" t="n"/>
+      <c r="A188" s="32" t="n"/>
+      <c r="B188" s="32" t="n"/>
+      <c r="C188" s="32" t="n"/>
+      <c r="D188" s="32" t="n"/>
+      <c r="E188" s="32" t="n"/>
+      <c r="F188" s="32" t="n"/>
+      <c r="G188" s="32" t="n"/>
       <c r="H188" s="32" t="n"/>
       <c r="I188" s="32" t="n"/>
       <c r="J188" s="32" t="n"/>
       <c r="K188" s="32" t="n"/>
+      <c r="L188" s="32" t="n"/>
     </row>
     <row r="189" ht="15.75" customHeight="1" s="27">
-      <c r="A189" s="21" t="n"/>
-      <c r="B189" s="21" t="n"/>
-      <c r="C189" s="21" t="n"/>
-      <c r="D189" s="21" t="n"/>
-      <c r="E189" s="21" t="n"/>
-      <c r="F189" s="21" t="n"/>
-      <c r="G189" s="21" t="n"/>
+      <c r="A189" s="32" t="n"/>
+      <c r="B189" s="32" t="n"/>
+      <c r="C189" s="32" t="n"/>
+      <c r="D189" s="32" t="n"/>
+      <c r="E189" s="32" t="n"/>
+      <c r="F189" s="32" t="n"/>
+      <c r="G189" s="32" t="n"/>
       <c r="H189" s="32" t="n"/>
       <c r="I189" s="32" t="n"/>
       <c r="J189" s="32" t="n"/>
       <c r="K189" s="32" t="n"/>
+      <c r="L189" s="32" t="n"/>
     </row>
     <row r="190" ht="15.75" customHeight="1" s="27">
-      <c r="A190" s="21" t="n"/>
-      <c r="B190" s="21" t="n"/>
-      <c r="C190" s="21" t="n"/>
-      <c r="D190" s="21" t="n"/>
-      <c r="E190" s="21" t="n"/>
-      <c r="F190" s="21" t="n"/>
-      <c r="G190" s="21" t="n"/>
+      <c r="A190" s="32" t="n"/>
+      <c r="B190" s="32" t="n"/>
+      <c r="C190" s="32" t="n"/>
+      <c r="D190" s="32" t="n"/>
+      <c r="E190" s="32" t="n"/>
+      <c r="F190" s="32" t="n"/>
+      <c r="G190" s="32" t="n"/>
       <c r="H190" s="32" t="n"/>
       <c r="I190" s="32" t="n"/>
       <c r="J190" s="32" t="n"/>
       <c r="K190" s="32" t="n"/>
+      <c r="L190" s="32" t="n"/>
     </row>
     <row r="191" ht="15.75" customHeight="1" s="27">
-      <c r="A191" s="21" t="n"/>
-      <c r="B191" s="21" t="n"/>
-      <c r="C191" s="21" t="n"/>
-      <c r="D191" s="21" t="n"/>
-      <c r="E191" s="21" t="n"/>
-      <c r="F191" s="21" t="n"/>
-      <c r="G191" s="21" t="n"/>
+      <c r="A191" s="32" t="n"/>
+      <c r="B191" s="32" t="n"/>
+      <c r="C191" s="32" t="n"/>
+      <c r="D191" s="32" t="n"/>
+      <c r="E191" s="32" t="n"/>
+      <c r="F191" s="32" t="n"/>
+      <c r="G191" s="32" t="n"/>
       <c r="H191" s="32" t="n"/>
       <c r="I191" s="32" t="n"/>
       <c r="J191" s="32" t="n"/>
       <c r="K191" s="32" t="n"/>
+      <c r="L191" s="32" t="n"/>
     </row>
     <row r="192" ht="15.75" customHeight="1" s="27">
-      <c r="A192" s="21" t="n"/>
-      <c r="B192" s="21" t="n"/>
-      <c r="C192" s="21" t="n"/>
-      <c r="D192" s="21" t="n"/>
-      <c r="E192" s="21" t="n"/>
-      <c r="F192" s="21" t="n"/>
-      <c r="G192" s="21" t="n"/>
+      <c r="A192" s="32" t="n"/>
+      <c r="B192" s="32" t="n"/>
+      <c r="C192" s="32" t="n"/>
+      <c r="D192" s="32" t="n"/>
+      <c r="E192" s="32" t="n"/>
+      <c r="F192" s="32" t="n"/>
+      <c r="G192" s="32" t="n"/>
       <c r="H192" s="32" t="n"/>
       <c r="I192" s="32" t="n"/>
       <c r="J192" s="32" t="n"/>
       <c r="K192" s="32" t="n"/>
+      <c r="L192" s="32" t="n"/>
     </row>
     <row r="193" ht="15.75" customHeight="1" s="27">
-      <c r="A193" s="21" t="n"/>
-      <c r="B193" s="21" t="n"/>
-      <c r="C193" s="21" t="n"/>
-      <c r="D193" s="21" t="n"/>
-      <c r="E193" s="21" t="n"/>
-      <c r="F193" s="21" t="n"/>
-      <c r="G193" s="21" t="n"/>
+      <c r="A193" s="32" t="n"/>
+      <c r="B193" s="32" t="n"/>
+      <c r="C193" s="32" t="n"/>
+      <c r="D193" s="32" t="n"/>
+      <c r="E193" s="32" t="n"/>
+      <c r="F193" s="32" t="n"/>
+      <c r="G193" s="32" t="n"/>
       <c r="H193" s="32" t="n"/>
       <c r="I193" s="32" t="n"/>
       <c r="J193" s="32" t="n"/>
       <c r="K193" s="32" t="n"/>
+      <c r="L193" s="32" t="n"/>
     </row>
     <row r="194" ht="15.75" customHeight="1" s="27">
-      <c r="A194" s="21" t="n"/>
-      <c r="B194" s="21" t="n"/>
-      <c r="C194" s="21" t="n"/>
-      <c r="D194" s="21" t="n"/>
-      <c r="E194" s="21" t="n"/>
-      <c r="F194" s="21" t="n"/>
-      <c r="G194" s="21" t="n"/>
+      <c r="A194" s="32" t="n"/>
+      <c r="B194" s="32" t="n"/>
+      <c r="C194" s="32" t="n"/>
+      <c r="D194" s="32" t="n"/>
+      <c r="E194" s="32" t="n"/>
+      <c r="F194" s="32" t="n"/>
+      <c r="G194" s="32" t="n"/>
       <c r="H194" s="32" t="n"/>
       <c r="I194" s="32" t="n"/>
       <c r="J194" s="32" t="n"/>
       <c r="K194" s="32" t="n"/>
+      <c r="L194" s="32" t="n"/>
     </row>
     <row r="195" ht="15.75" customHeight="1" s="27">
-      <c r="A195" s="21" t="n"/>
-      <c r="B195" s="21" t="n"/>
-      <c r="C195" s="21" t="n"/>
-      <c r="D195" s="21" t="n"/>
-      <c r="E195" s="21" t="n"/>
-      <c r="F195" s="21" t="n"/>
-      <c r="G195" s="21" t="n"/>
+      <c r="A195" s="32" t="n"/>
+      <c r="B195" s="32" t="n"/>
+      <c r="C195" s="32" t="n"/>
+      <c r="D195" s="32" t="n"/>
+      <c r="E195" s="32" t="n"/>
+      <c r="F195" s="32" t="n"/>
+      <c r="G195" s="32" t="n"/>
       <c r="H195" s="32" t="n"/>
       <c r="I195" s="32" t="n"/>
       <c r="J195" s="32" t="n"/>
       <c r="K195" s="32" t="n"/>
+      <c r="L195" s="32" t="n"/>
     </row>
     <row r="196" ht="15.75" customHeight="1" s="27">
-      <c r="A196" s="21" t="n"/>
-      <c r="B196" s="21" t="n"/>
-      <c r="C196" s="21" t="n"/>
-      <c r="D196" s="21" t="n"/>
-      <c r="E196" s="21" t="n"/>
-      <c r="F196" s="21" t="n"/>
-      <c r="G196" s="21" t="n"/>
+      <c r="A196" s="32" t="n"/>
+      <c r="B196" s="32" t="n"/>
+      <c r="C196" s="32" t="n"/>
+      <c r="D196" s="32" t="n"/>
+      <c r="E196" s="32" t="n"/>
+      <c r="F196" s="32" t="n"/>
+      <c r="G196" s="32" t="n"/>
       <c r="H196" s="32" t="n"/>
       <c r="I196" s="32" t="n"/>
       <c r="J196" s="32" t="n"/>
       <c r="K196" s="32" t="n"/>
+      <c r="L196" s="32" t="n"/>
     </row>
     <row r="197" ht="15.75" customHeight="1" s="27">
-      <c r="A197" s="21" t="n"/>
-      <c r="B197" s="21" t="n"/>
-      <c r="C197" s="21" t="n"/>
-      <c r="D197" s="21" t="n"/>
-      <c r="E197" s="21" t="n"/>
-      <c r="F197" s="21" t="n"/>
-      <c r="G197" s="21" t="n"/>
+      <c r="A197" s="32" t="n"/>
+      <c r="B197" s="32" t="n"/>
+      <c r="C197" s="32" t="n"/>
+      <c r="D197" s="32" t="n"/>
+      <c r="E197" s="32" t="n"/>
+      <c r="F197" s="32" t="n"/>
+      <c r="G197" s="32" t="n"/>
       <c r="H197" s="32" t="n"/>
       <c r="I197" s="32" t="n"/>
       <c r="J197" s="32" t="n"/>
       <c r="K197" s="32" t="n"/>
+      <c r="L197" s="32" t="n"/>
     </row>
     <row r="198" ht="15.75" customHeight="1" s="27">
-      <c r="A198" s="21" t="n"/>
-      <c r="B198" s="21" t="n"/>
-      <c r="C198" s="21" t="n"/>
-      <c r="D198" s="21" t="n"/>
-      <c r="E198" s="21" t="n"/>
-      <c r="F198" s="21" t="n"/>
-      <c r="G198" s="21" t="n"/>
+      <c r="A198" s="32" t="n"/>
+      <c r="B198" s="32" t="n"/>
+      <c r="C198" s="32" t="n"/>
+      <c r="D198" s="32" t="n"/>
+      <c r="E198" s="32" t="n"/>
+      <c r="F198" s="32" t="n"/>
+      <c r="G198" s="32" t="n"/>
       <c r="H198" s="32" t="n"/>
       <c r="I198" s="32" t="n"/>
       <c r="J198" s="32" t="n"/>
       <c r="K198" s="32" t="n"/>
+      <c r="L198" s="32" t="n"/>
     </row>
     <row r="199" ht="15.75" customHeight="1" s="27">
-      <c r="A199" s="21" t="n"/>
-      <c r="B199" s="21" t="n"/>
-      <c r="C199" s="21" t="n"/>
-      <c r="D199" s="21" t="n"/>
-      <c r="E199" s="21" t="n"/>
-      <c r="F199" s="21" t="n"/>
-      <c r="G199" s="21" t="n"/>
+      <c r="A199" s="32" t="n"/>
+      <c r="B199" s="32" t="n"/>
+      <c r="C199" s="32" t="n"/>
+      <c r="D199" s="32" t="n"/>
+      <c r="E199" s="32" t="n"/>
+      <c r="F199" s="32" t="n"/>
+      <c r="G199" s="32" t="n"/>
       <c r="H199" s="32" t="n"/>
       <c r="I199" s="32" t="n"/>
       <c r="J199" s="32" t="n"/>
       <c r="K199" s="32" t="n"/>
+      <c r="L199" s="32" t="n"/>
     </row>
     <row r="200" ht="15.75" customHeight="1" s="27">
-      <c r="A200" s="21" t="n"/>
-      <c r="B200" s="21" t="n"/>
-      <c r="C200" s="21" t="n"/>
-      <c r="D200" s="21" t="n"/>
-      <c r="E200" s="21" t="n"/>
-      <c r="F200" s="21" t="n"/>
-      <c r="G200" s="21" t="n"/>
+      <c r="A200" s="32" t="n"/>
+      <c r="B200" s="32" t="n"/>
+      <c r="C200" s="32" t="n"/>
+      <c r="D200" s="32" t="n"/>
+      <c r="E200" s="32" t="n"/>
+      <c r="F200" s="32" t="n"/>
+      <c r="G200" s="32" t="n"/>
       <c r="H200" s="32" t="n"/>
       <c r="I200" s="32" t="n"/>
       <c r="J200" s="32" t="n"/>
       <c r="K200" s="32" t="n"/>
+      <c r="L200" s="32" t="n"/>
     </row>
     <row r="201" ht="15.75" customHeight="1" s="27">
-      <c r="A201" s="21" t="n"/>
-      <c r="B201" s="21" t="n"/>
-      <c r="C201" s="21" t="n"/>
-      <c r="D201" s="21" t="n"/>
-      <c r="E201" s="21" t="n"/>
-      <c r="F201" s="21" t="n"/>
-      <c r="G201" s="21" t="n"/>
+      <c r="A201" s="32" t="n"/>
+      <c r="B201" s="32" t="n"/>
+      <c r="C201" s="32" t="n"/>
+      <c r="D201" s="32" t="n"/>
+      <c r="E201" s="32" t="n"/>
+      <c r="F201" s="32" t="n"/>
+      <c r="G201" s="32" t="n"/>
       <c r="H201" s="32" t="n"/>
       <c r="I201" s="32" t="n"/>
       <c r="J201" s="32" t="n"/>
       <c r="K201" s="32" t="n"/>
+      <c r="L201" s="32" t="n"/>
     </row>
     <row r="202" ht="15.75" customHeight="1" s="27">
-      <c r="A202" s="21" t="n"/>
-      <c r="B202" s="21" t="n"/>
-      <c r="C202" s="21" t="n"/>
-      <c r="D202" s="21" t="n"/>
-      <c r="E202" s="21" t="n"/>
-      <c r="F202" s="21" t="n"/>
-      <c r="G202" s="21" t="n"/>
+      <c r="A202" s="32" t="n"/>
+      <c r="B202" s="32" t="n"/>
+      <c r="C202" s="32" t="n"/>
+      <c r="D202" s="32" t="n"/>
+      <c r="E202" s="32" t="n"/>
+      <c r="F202" s="32" t="n"/>
+      <c r="G202" s="32" t="n"/>
       <c r="H202" s="32" t="n"/>
       <c r="I202" s="32" t="n"/>
       <c r="J202" s="32" t="n"/>
       <c r="K202" s="32" t="n"/>
+      <c r="L202" s="32" t="n"/>
     </row>
     <row r="203" ht="15.75" customHeight="1" s="27">
-      <c r="A203" s="21" t="n"/>
-      <c r="B203" s="21" t="n"/>
-      <c r="C203" s="21" t="n"/>
-      <c r="D203" s="21" t="n"/>
-      <c r="E203" s="21" t="n"/>
-      <c r="F203" s="21" t="n"/>
-      <c r="G203" s="21" t="n"/>
+      <c r="A203" s="32" t="n"/>
+      <c r="B203" s="32" t="n"/>
+      <c r="C203" s="32" t="n"/>
+      <c r="D203" s="32" t="n"/>
+      <c r="E203" s="32" t="n"/>
+      <c r="F203" s="32" t="n"/>
+      <c r="G203" s="32" t="n"/>
       <c r="H203" s="32" t="n"/>
       <c r="I203" s="32" t="n"/>
       <c r="J203" s="32" t="n"/>
       <c r="K203" s="32" t="n"/>
+      <c r="L203" s="32" t="n"/>
     </row>
     <row r="204" ht="15.75" customHeight="1" s="27">
-      <c r="A204" s="21" t="n"/>
-      <c r="B204" s="21" t="n"/>
-      <c r="C204" s="21" t="n"/>
-      <c r="D204" s="21" t="n"/>
-      <c r="E204" s="21" t="n"/>
-      <c r="F204" s="21" t="n"/>
-      <c r="G204" s="21" t="n"/>
+      <c r="A204" s="32" t="n"/>
+      <c r="B204" s="32" t="n"/>
+      <c r="C204" s="32" t="n"/>
+      <c r="D204" s="32" t="n"/>
+      <c r="E204" s="32" t="n"/>
+      <c r="F204" s="32" t="n"/>
+      <c r="G204" s="32" t="n"/>
       <c r="H204" s="32" t="n"/>
       <c r="I204" s="32" t="n"/>
       <c r="J204" s="32" t="n"/>
       <c r="K204" s="32" t="n"/>
+      <c r="L204" s="32" t="n"/>
     </row>
     <row r="205" ht="15.75" customHeight="1" s="27">
-      <c r="A205" s="21" t="n"/>
-      <c r="B205" s="21" t="n"/>
-      <c r="C205" s="21" t="n"/>
-      <c r="D205" s="21" t="n"/>
-      <c r="E205" s="21" t="n"/>
-      <c r="F205" s="21" t="n"/>
-      <c r="G205" s="21" t="n"/>
+      <c r="A205" s="32" t="n"/>
+      <c r="B205" s="32" t="n"/>
+      <c r="C205" s="32" t="n"/>
+      <c r="D205" s="32" t="n"/>
+      <c r="E205" s="32" t="n"/>
+      <c r="F205" s="32" t="n"/>
+      <c r="G205" s="32" t="n"/>
       <c r="H205" s="32" t="n"/>
       <c r="I205" s="32" t="n"/>
       <c r="J205" s="32" t="n"/>
       <c r="K205" s="32" t="n"/>
+      <c r="L205" s="32" t="n"/>
     </row>
     <row r="206" ht="15.75" customHeight="1" s="27">
-      <c r="A206" s="21" t="n"/>
-      <c r="B206" s="21" t="n"/>
-      <c r="C206" s="21" t="n"/>
-      <c r="D206" s="21" t="n"/>
-      <c r="E206" s="21" t="n"/>
-      <c r="F206" s="21" t="n"/>
-      <c r="G206" s="21" t="n"/>
+      <c r="A206" s="32" t="n"/>
+      <c r="B206" s="32" t="n"/>
+      <c r="C206" s="32" t="n"/>
+      <c r="D206" s="32" t="n"/>
+      <c r="E206" s="32" t="n"/>
+      <c r="F206" s="32" t="n"/>
+      <c r="G206" s="32" t="n"/>
       <c r="H206" s="32" t="n"/>
       <c r="I206" s="32" t="n"/>
       <c r="J206" s="32" t="n"/>
       <c r="K206" s="32" t="n"/>
+      <c r="L206" s="32" t="n"/>
     </row>
     <row r="207" ht="15.75" customHeight="1" s="27">
-      <c r="A207" s="21" t="n"/>
-      <c r="B207" s="21" t="n"/>
-      <c r="C207" s="21" t="n"/>
-      <c r="D207" s="21" t="n"/>
-      <c r="E207" s="21" t="n"/>
-      <c r="F207" s="21" t="n"/>
-      <c r="G207" s="21" t="n"/>
+      <c r="A207" s="32" t="n"/>
+      <c r="B207" s="32" t="n"/>
+      <c r="C207" s="32" t="n"/>
+      <c r="D207" s="32" t="n"/>
+      <c r="E207" s="32" t="n"/>
+      <c r="F207" s="32" t="n"/>
+      <c r="G207" s="32" t="n"/>
       <c r="H207" s="32" t="n"/>
       <c r="I207" s="32" t="n"/>
       <c r="J207" s="32" t="n"/>
       <c r="K207" s="32" t="n"/>
+      <c r="L207" s="32" t="n"/>
     </row>
     <row r="208" ht="15.75" customHeight="1" s="27">
-      <c r="A208" s="21" t="n"/>
-      <c r="B208" s="21" t="n"/>
-      <c r="C208" s="21" t="n"/>
-      <c r="D208" s="21" t="n"/>
-      <c r="E208" s="21" t="n"/>
-      <c r="F208" s="21" t="n"/>
-      <c r="G208" s="21" t="n"/>
+      <c r="A208" s="32" t="n"/>
+      <c r="B208" s="32" t="n"/>
+      <c r="C208" s="32" t="n"/>
+      <c r="D208" s="32" t="n"/>
+      <c r="E208" s="32" t="n"/>
+      <c r="F208" s="32" t="n"/>
+      <c r="G208" s="32" t="n"/>
       <c r="H208" s="32" t="n"/>
       <c r="I208" s="32" t="n"/>
       <c r="J208" s="32" t="n"/>
       <c r="K208" s="32" t="n"/>
+      <c r="L208" s="32" t="n"/>
     </row>
     <row r="209" ht="15.75" customHeight="1" s="27">
-      <c r="A209" s="21" t="n"/>
-      <c r="B209" s="21" t="n"/>
-      <c r="C209" s="21" t="n"/>
-      <c r="D209" s="21" t="n"/>
-      <c r="E209" s="21" t="n"/>
-      <c r="F209" s="21" t="n"/>
-      <c r="G209" s="21" t="n"/>
+      <c r="A209" s="32" t="n"/>
+      <c r="B209" s="32" t="n"/>
+      <c r="C209" s="32" t="n"/>
+      <c r="D209" s="32" t="n"/>
+      <c r="E209" s="32" t="n"/>
+      <c r="F209" s="32" t="n"/>
+      <c r="G209" s="32" t="n"/>
       <c r="H209" s="32" t="n"/>
       <c r="I209" s="32" t="n"/>
       <c r="J209" s="32" t="n"/>
       <c r="K209" s="32" t="n"/>
+      <c r="L209" s="32" t="n"/>
     </row>
     <row r="210" ht="15.75" customHeight="1" s="27">
-      <c r="A210" s="21" t="n"/>
-      <c r="B210" s="21" t="n"/>
-      <c r="C210" s="21" t="n"/>
-      <c r="D210" s="21" t="n"/>
-      <c r="E210" s="21" t="n"/>
-      <c r="F210" s="21" t="n"/>
-      <c r="G210" s="21" t="n"/>
+      <c r="A210" s="32" t="n"/>
+      <c r="B210" s="32" t="n"/>
+      <c r="C210" s="32" t="n"/>
+      <c r="D210" s="32" t="n"/>
+      <c r="E210" s="32" t="n"/>
+      <c r="F210" s="32" t="n"/>
+      <c r="G210" s="32" t="n"/>
       <c r="H210" s="32" t="n"/>
       <c r="I210" s="32" t="n"/>
       <c r="J210" s="32" t="n"/>
       <c r="K210" s="32" t="n"/>
+      <c r="L210" s="32" t="n"/>
     </row>
     <row r="211" ht="15.75" customHeight="1" s="27">
-      <c r="A211" s="21" t="n"/>
-      <c r="B211" s="21" t="n"/>
-      <c r="C211" s="21" t="n"/>
-      <c r="D211" s="21" t="n"/>
-      <c r="E211" s="21" t="n"/>
-      <c r="F211" s="21" t="n"/>
-      <c r="G211" s="21" t="n"/>
+      <c r="A211" s="32" t="n"/>
+      <c r="B211" s="32" t="n"/>
+      <c r="C211" s="32" t="n"/>
+      <c r="D211" s="32" t="n"/>
+      <c r="E211" s="32" t="n"/>
+      <c r="F211" s="32" t="n"/>
+      <c r="G211" s="32" t="n"/>
       <c r="H211" s="32" t="n"/>
       <c r="I211" s="32" t="n"/>
       <c r="J211" s="32" t="n"/>
       <c r="K211" s="32" t="n"/>
+      <c r="L211" s="32" t="n"/>
     </row>
     <row r="212" ht="15.75" customHeight="1" s="27">
-      <c r="A212" s="21" t="n"/>
-      <c r="B212" s="21" t="n"/>
-      <c r="C212" s="21" t="n"/>
-      <c r="D212" s="21" t="n"/>
-      <c r="E212" s="21" t="n"/>
-      <c r="F212" s="21" t="n"/>
-      <c r="G212" s="21" t="n"/>
+      <c r="A212" s="32" t="n"/>
+      <c r="B212" s="32" t="n"/>
+      <c r="C212" s="32" t="n"/>
+      <c r="D212" s="32" t="n"/>
+      <c r="E212" s="32" t="n"/>
+      <c r="F212" s="32" t="n"/>
+      <c r="G212" s="32" t="n"/>
       <c r="H212" s="32" t="n"/>
       <c r="I212" s="32" t="n"/>
       <c r="J212" s="32" t="n"/>
       <c r="K212" s="32" t="n"/>
+      <c r="L212" s="32" t="n"/>
     </row>
     <row r="213" ht="15.75" customHeight="1" s="27">
-      <c r="A213" s="21" t="n"/>
-      <c r="B213" s="21" t="n"/>
-      <c r="C213" s="21" t="n"/>
-      <c r="D213" s="21" t="n"/>
-      <c r="E213" s="21" t="n"/>
-      <c r="F213" s="21" t="n"/>
-      <c r="G213" s="21" t="n"/>
+      <c r="A213" s="32" t="n"/>
+      <c r="B213" s="32" t="n"/>
+      <c r="C213" s="32" t="n"/>
+      <c r="D213" s="32" t="n"/>
+      <c r="E213" s="32" t="n"/>
+      <c r="F213" s="32" t="n"/>
+      <c r="G213" s="32" t="n"/>
       <c r="H213" s="32" t="n"/>
       <c r="I213" s="32" t="n"/>
       <c r="J213" s="32" t="n"/>
       <c r="K213" s="32" t="n"/>
+      <c r="L213" s="32" t="n"/>
     </row>
     <row r="214" ht="15.75" customHeight="1" s="27">
-      <c r="A214" s="21" t="n"/>
-      <c r="B214" s="21" t="n"/>
-      <c r="C214" s="21" t="n"/>
-      <c r="D214" s="21" t="n"/>
-      <c r="E214" s="21" t="n"/>
-      <c r="F214" s="21" t="n"/>
-      <c r="G214" s="21" t="n"/>
+      <c r="A214" s="32" t="n"/>
+      <c r="B214" s="32" t="n"/>
+      <c r="C214" s="32" t="n"/>
+      <c r="D214" s="32" t="n"/>
+      <c r="E214" s="32" t="n"/>
+      <c r="F214" s="32" t="n"/>
+      <c r="G214" s="32" t="n"/>
       <c r="H214" s="32" t="n"/>
       <c r="I214" s="32" t="n"/>
       <c r="J214" s="32" t="n"/>
       <c r="K214" s="32" t="n"/>
+      <c r="L214" s="32" t="n"/>
     </row>
     <row r="215" ht="15.75" customHeight="1" s="27">
-      <c r="A215" s="21" t="n"/>
-      <c r="B215" s="21" t="n"/>
-      <c r="C215" s="21" t="n"/>
-      <c r="D215" s="21" t="n"/>
-      <c r="E215" s="21" t="n"/>
-      <c r="F215" s="21" t="n"/>
-      <c r="G215" s="21" t="n"/>
+      <c r="A215" s="32" t="n"/>
+      <c r="B215" s="32" t="n"/>
+      <c r="C215" s="32" t="n"/>
+      <c r="D215" s="32" t="n"/>
+      <c r="E215" s="32" t="n"/>
+      <c r="F215" s="32" t="n"/>
+      <c r="G215" s="32" t="n"/>
       <c r="H215" s="32" t="n"/>
       <c r="I215" s="32" t="n"/>
       <c r="J215" s="32" t="n"/>
       <c r="K215" s="32" t="n"/>
+      <c r="L215" s="32" t="n"/>
     </row>
     <row r="216" ht="15.75" customHeight="1" s="27">
-      <c r="A216" s="21" t="n"/>
-      <c r="B216" s="21" t="n"/>
-      <c r="C216" s="21" t="n"/>
-      <c r="D216" s="21" t="n"/>
-      <c r="E216" s="21" t="n"/>
-      <c r="F216" s="21" t="n"/>
-      <c r="G216" s="21" t="n"/>
+      <c r="A216" s="32" t="n"/>
+      <c r="B216" s="32" t="n"/>
+      <c r="C216" s="32" t="n"/>
+      <c r="D216" s="32" t="n"/>
+      <c r="E216" s="32" t="n"/>
+      <c r="F216" s="32" t="n"/>
+      <c r="G216" s="32" t="n"/>
       <c r="H216" s="32" t="n"/>
       <c r="I216" s="32" t="n"/>
       <c r="J216" s="32" t="n"/>
       <c r="K216" s="32" t="n"/>
+      <c r="L216" s="32" t="n"/>
     </row>
     <row r="217" ht="15.75" customHeight="1" s="27">
-      <c r="A217" s="21" t="n"/>
-      <c r="B217" s="21" t="n"/>
-      <c r="C217" s="21" t="n"/>
-      <c r="D217" s="21" t="n"/>
-      <c r="E217" s="21" t="n"/>
-      <c r="F217" s="21" t="n"/>
-      <c r="G217" s="21" t="n"/>
+      <c r="A217" s="32" t="n"/>
+      <c r="B217" s="32" t="n"/>
+      <c r="C217" s="32" t="n"/>
+      <c r="D217" s="32" t="n"/>
+      <c r="E217" s="32" t="n"/>
+      <c r="F217" s="32" t="n"/>
+      <c r="G217" s="32" t="n"/>
       <c r="H217" s="32" t="n"/>
       <c r="I217" s="32" t="n"/>
       <c r="J217" s="32" t="n"/>
       <c r="K217" s="32" t="n"/>
+      <c r="L217" s="32" t="n"/>
     </row>
     <row r="218" ht="15.75" customHeight="1" s="27">
-      <c r="A218" s="21" t="n"/>
-      <c r="B218" s="21" t="n"/>
-      <c r="C218" s="21" t="n"/>
-      <c r="D218" s="21" t="n"/>
-      <c r="E218" s="21" t="n"/>
-      <c r="F218" s="21" t="n"/>
-      <c r="G218" s="21" t="n"/>
+      <c r="A218" s="32" t="n"/>
+      <c r="B218" s="32" t="n"/>
+      <c r="C218" s="32" t="n"/>
+      <c r="D218" s="32" t="n"/>
+      <c r="E218" s="32" t="n"/>
+      <c r="F218" s="32" t="n"/>
+      <c r="G218" s="32" t="n"/>
       <c r="H218" s="32" t="n"/>
       <c r="I218" s="32" t="n"/>
       <c r="J218" s="32" t="n"/>
       <c r="K218" s="32" t="n"/>
+      <c r="L218" s="32" t="n"/>
     </row>
     <row r="219" ht="15.75" customHeight="1" s="27">
-      <c r="A219" s="21" t="n"/>
-      <c r="B219" s="21" t="n"/>
-      <c r="C219" s="21" t="n"/>
-      <c r="D219" s="21" t="n"/>
-      <c r="E219" s="21" t="n"/>
-      <c r="F219" s="21" t="n"/>
-      <c r="G219" s="21" t="n"/>
+      <c r="A219" s="32" t="n"/>
+      <c r="B219" s="32" t="n"/>
+      <c r="C219" s="32" t="n"/>
+      <c r="D219" s="32" t="n"/>
+      <c r="E219" s="32" t="n"/>
+      <c r="F219" s="32" t="n"/>
+      <c r="G219" s="32" t="n"/>
       <c r="H219" s="32" t="n"/>
       <c r="I219" s="32" t="n"/>
       <c r="J219" s="32" t="n"/>
       <c r="K219" s="32" t="n"/>
+      <c r="L219" s="32" t="n"/>
     </row>
     <row r="220" ht="15.75" customHeight="1" s="27">
-      <c r="A220" s="21" t="n"/>
-      <c r="B220" s="21" t="n"/>
-      <c r="C220" s="21" t="n"/>
-      <c r="D220" s="21" t="n"/>
-      <c r="E220" s="21" t="n"/>
-      <c r="F220" s="21" t="n"/>
-      <c r="G220" s="21" t="n"/>
+      <c r="A220" s="32" t="n"/>
+      <c r="B220" s="32" t="n"/>
+      <c r="C220" s="32" t="n"/>
+      <c r="D220" s="32" t="n"/>
+      <c r="E220" s="32" t="n"/>
+      <c r="F220" s="32" t="n"/>
+      <c r="G220" s="32" t="n"/>
       <c r="H220" s="32" t="n"/>
       <c r="I220" s="32" t="n"/>
       <c r="J220" s="32" t="n"/>
       <c r="K220" s="32" t="n"/>
+      <c r="L220" s="32" t="n"/>
     </row>
     <row r="221" ht="15.75" customHeight="1" s="27">
       <c r="B221" s="26" t="n"/>
@@ -4705,6 +4945,7 @@
       <c r="I221" s="32" t="n"/>
       <c r="J221" s="32" t="n"/>
       <c r="K221" s="32" t="n"/>
+      <c r="L221" s="32" t="n"/>
     </row>
     <row r="222" ht="15.75" customHeight="1" s="27">
       <c r="B222" s="26" t="n"/>
@@ -4713,6 +4954,7 @@
       <c r="I222" s="32" t="n"/>
       <c r="J222" s="32" t="n"/>
       <c r="K222" s="32" t="n"/>
+      <c r="L222" s="32" t="n"/>
     </row>
     <row r="223" ht="15.75" customHeight="1" s="27">
       <c r="B223" s="26" t="n"/>
@@ -4721,6 +4963,7 @@
       <c r="I223" s="32" t="n"/>
       <c r="J223" s="32" t="n"/>
       <c r="K223" s="32" t="n"/>
+      <c r="L223" s="32" t="n"/>
     </row>
     <row r="224" ht="15.75" customHeight="1" s="27">
       <c r="B224" s="26" t="n"/>
@@ -4729,6 +4972,7 @@
       <c r="I224" s="32" t="n"/>
       <c r="J224" s="32" t="n"/>
       <c r="K224" s="32" t="n"/>
+      <c r="L224" s="32" t="n"/>
     </row>
     <row r="225" ht="15.75" customHeight="1" s="27">
       <c r="B225" s="26" t="n"/>
@@ -4737,6 +4981,7 @@
       <c r="I225" s="32" t="n"/>
       <c r="J225" s="32" t="n"/>
       <c r="K225" s="32" t="n"/>
+      <c r="L225" s="32" t="n"/>
     </row>
     <row r="226" ht="15.75" customHeight="1" s="27">
       <c r="B226" s="26" t="n"/>
@@ -4745,6 +4990,7 @@
       <c r="I226" s="32" t="n"/>
       <c r="J226" s="32" t="n"/>
       <c r="K226" s="32" t="n"/>
+      <c r="L226" s="32" t="n"/>
     </row>
     <row r="227" ht="15.75" customHeight="1" s="27">
       <c r="B227" s="26" t="n"/>
@@ -4753,6 +4999,7 @@
       <c r="I227" s="32" t="n"/>
       <c r="J227" s="32" t="n"/>
       <c r="K227" s="32" t="n"/>
+      <c r="L227" s="32" t="n"/>
     </row>
     <row r="228" ht="15.75" customHeight="1" s="27">
       <c r="B228" s="26" t="n"/>
@@ -4761,6 +5008,7 @@
       <c r="I228" s="32" t="n"/>
       <c r="J228" s="32" t="n"/>
       <c r="K228" s="32" t="n"/>
+      <c r="L228" s="32" t="n"/>
     </row>
     <row r="229" ht="15.75" customHeight="1" s="27">
       <c r="B229" s="26" t="n"/>
@@ -4769,6 +5017,7 @@
       <c r="I229" s="32" t="n"/>
       <c r="J229" s="32" t="n"/>
       <c r="K229" s="32" t="n"/>
+      <c r="L229" s="32" t="n"/>
     </row>
     <row r="230" ht="15.75" customHeight="1" s="27">
       <c r="B230" s="26" t="n"/>
@@ -4777,6 +5026,7 @@
       <c r="I230" s="32" t="n"/>
       <c r="J230" s="32" t="n"/>
       <c r="K230" s="32" t="n"/>
+      <c r="L230" s="32" t="n"/>
     </row>
     <row r="231" ht="15.75" customHeight="1" s="27">
       <c r="B231" s="26" t="n"/>
@@ -4785,6 +5035,7 @@
       <c r="I231" s="32" t="n"/>
       <c r="J231" s="32" t="n"/>
       <c r="K231" s="32" t="n"/>
+      <c r="L231" s="32" t="n"/>
     </row>
     <row r="232" ht="15.75" customHeight="1" s="27">
       <c r="B232" s="26" t="n"/>
@@ -4793,6 +5044,7 @@
       <c r="I232" s="32" t="n"/>
       <c r="J232" s="32" t="n"/>
       <c r="K232" s="32" t="n"/>
+      <c r="L232" s="32" t="n"/>
     </row>
     <row r="233" ht="15.75" customHeight="1" s="27">
       <c r="B233" s="26" t="n"/>
@@ -4801,6 +5053,7 @@
       <c r="I233" s="32" t="n"/>
       <c r="J233" s="32" t="n"/>
       <c r="K233" s="32" t="n"/>
+      <c r="L233" s="32" t="n"/>
     </row>
     <row r="234" ht="15.75" customHeight="1" s="27">
       <c r="B234" s="26" t="n"/>
@@ -4809,6 +5062,7 @@
       <c r="I234" s="32" t="n"/>
       <c r="J234" s="32" t="n"/>
       <c r="K234" s="32" t="n"/>
+      <c r="L234" s="32" t="n"/>
     </row>
     <row r="235" ht="15.75" customHeight="1" s="27">
       <c r="B235" s="26" t="n"/>
@@ -4817,6 +5071,7 @@
       <c r="I235" s="32" t="n"/>
       <c r="J235" s="32" t="n"/>
       <c r="K235" s="32" t="n"/>
+      <c r="L235" s="32" t="n"/>
     </row>
     <row r="236" ht="15.75" customHeight="1" s="27">
       <c r="B236" s="26" t="n"/>
@@ -4825,6 +5080,7 @@
       <c r="I236" s="32" t="n"/>
       <c r="J236" s="32" t="n"/>
       <c r="K236" s="32" t="n"/>
+      <c r="L236" s="32" t="n"/>
     </row>
     <row r="237" ht="15.75" customHeight="1" s="27">
       <c r="B237" s="26" t="n"/>
@@ -4833,6 +5089,7 @@
       <c r="I237" s="32" t="n"/>
       <c r="J237" s="32" t="n"/>
       <c r="K237" s="32" t="n"/>
+      <c r="L237" s="32" t="n"/>
     </row>
     <row r="238" ht="15.75" customHeight="1" s="27">
       <c r="B238" s="26" t="n"/>
@@ -4841,6 +5098,7 @@
       <c r="I238" s="32" t="n"/>
       <c r="J238" s="32" t="n"/>
       <c r="K238" s="32" t="n"/>
+      <c r="L238" s="32" t="n"/>
     </row>
     <row r="239" ht="15.75" customHeight="1" s="27">
       <c r="B239" s="26" t="n"/>
@@ -4849,6 +5107,7 @@
       <c r="I239" s="32" t="n"/>
       <c r="J239" s="32" t="n"/>
       <c r="K239" s="32" t="n"/>
+      <c r="L239" s="32" t="n"/>
     </row>
     <row r="240" ht="15.75" customHeight="1" s="27">
       <c r="B240" s="26" t="n"/>
@@ -4857,6 +5116,7 @@
       <c r="I240" s="32" t="n"/>
       <c r="J240" s="32" t="n"/>
       <c r="K240" s="32" t="n"/>
+      <c r="L240" s="32" t="n"/>
     </row>
     <row r="241" ht="15.75" customHeight="1" s="27">
       <c r="B241" s="26" t="n"/>
@@ -4865,6 +5125,7 @@
       <c r="I241" s="32" t="n"/>
       <c r="J241" s="32" t="n"/>
       <c r="K241" s="32" t="n"/>
+      <c r="L241" s="32" t="n"/>
     </row>
     <row r="242" ht="15.75" customHeight="1" s="27">
       <c r="B242" s="26" t="n"/>
@@ -4873,6 +5134,7 @@
       <c r="I242" s="32" t="n"/>
       <c r="J242" s="32" t="n"/>
       <c r="K242" s="32" t="n"/>
+      <c r="L242" s="32" t="n"/>
     </row>
     <row r="243" ht="15.75" customHeight="1" s="27">
       <c r="B243" s="26" t="n"/>
@@ -4881,6 +5143,7 @@
       <c r="I243" s="32" t="n"/>
       <c r="J243" s="32" t="n"/>
       <c r="K243" s="32" t="n"/>
+      <c r="L243" s="32" t="n"/>
     </row>
     <row r="244" ht="15.75" customHeight="1" s="27">
       <c r="B244" s="26" t="n"/>
@@ -4889,6 +5152,7 @@
       <c r="I244" s="32" t="n"/>
       <c r="J244" s="32" t="n"/>
       <c r="K244" s="32" t="n"/>
+      <c r="L244" s="32" t="n"/>
     </row>
     <row r="245" ht="15.75" customHeight="1" s="27">
       <c r="B245" s="26" t="n"/>
@@ -4897,6 +5161,7 @@
       <c r="I245" s="32" t="n"/>
       <c r="J245" s="32" t="n"/>
       <c r="K245" s="32" t="n"/>
+      <c r="L245" s="32" t="n"/>
     </row>
     <row r="246" ht="15.75" customHeight="1" s="27">
       <c r="B246" s="26" t="n"/>
@@ -4905,6 +5170,7 @@
       <c r="I246" s="32" t="n"/>
       <c r="J246" s="32" t="n"/>
       <c r="K246" s="32" t="n"/>
+      <c r="L246" s="32" t="n"/>
     </row>
     <row r="247" ht="15.75" customHeight="1" s="27">
       <c r="B247" s="26" t="n"/>
@@ -4913,6 +5179,7 @@
       <c r="I247" s="32" t="n"/>
       <c r="J247" s="32" t="n"/>
       <c r="K247" s="32" t="n"/>
+      <c r="L247" s="32" t="n"/>
     </row>
     <row r="248" ht="15.75" customHeight="1" s="27">
       <c r="B248" s="26" t="n"/>
@@ -4921,6 +5188,7 @@
       <c r="I248" s="32" t="n"/>
       <c r="J248" s="32" t="n"/>
       <c r="K248" s="32" t="n"/>
+      <c r="L248" s="32" t="n"/>
     </row>
     <row r="249" ht="15.75" customHeight="1" s="27">
       <c r="B249" s="26" t="n"/>
@@ -4929,6 +5197,7 @@
       <c r="I249" s="32" t="n"/>
       <c r="J249" s="32" t="n"/>
       <c r="K249" s="32" t="n"/>
+      <c r="L249" s="32" t="n"/>
     </row>
     <row r="250" ht="15.75" customHeight="1" s="27">
       <c r="B250" s="26" t="n"/>
@@ -4937,6 +5206,7 @@
       <c r="I250" s="32" t="n"/>
       <c r="J250" s="32" t="n"/>
       <c r="K250" s="32" t="n"/>
+      <c r="L250" s="32" t="n"/>
     </row>
     <row r="251" ht="15.75" customHeight="1" s="27">
       <c r="B251" s="26" t="n"/>
@@ -4945,6 +5215,7 @@
       <c r="I251" s="32" t="n"/>
       <c r="J251" s="32" t="n"/>
       <c r="K251" s="32" t="n"/>
+      <c r="L251" s="32" t="n"/>
     </row>
     <row r="252" ht="15.75" customHeight="1" s="27">
       <c r="B252" s="26" t="n"/>
@@ -4953,6 +5224,7 @@
       <c r="I252" s="32" t="n"/>
       <c r="J252" s="32" t="n"/>
       <c r="K252" s="32" t="n"/>
+      <c r="L252" s="32" t="n"/>
     </row>
     <row r="253" ht="15.75" customHeight="1" s="27">
       <c r="B253" s="26" t="n"/>
@@ -4961,6 +5233,7 @@
       <c r="I253" s="32" t="n"/>
       <c r="J253" s="32" t="n"/>
       <c r="K253" s="32" t="n"/>
+      <c r="L253" s="32" t="n"/>
     </row>
     <row r="254" ht="15.75" customHeight="1" s="27">
       <c r="B254" s="26" t="n"/>
@@ -4969,6 +5242,7 @@
       <c r="I254" s="32" t="n"/>
       <c r="J254" s="32" t="n"/>
       <c r="K254" s="32" t="n"/>
+      <c r="L254" s="32" t="n"/>
     </row>
     <row r="255" ht="15.75" customHeight="1" s="27">
       <c r="B255" s="26" t="n"/>
@@ -4977,6 +5251,7 @@
       <c r="I255" s="32" t="n"/>
       <c r="J255" s="32" t="n"/>
       <c r="K255" s="32" t="n"/>
+      <c r="L255" s="32" t="n"/>
     </row>
     <row r="256" ht="15.75" customHeight="1" s="27">
       <c r="B256" s="26" t="n"/>
@@ -4985,6 +5260,7 @@
       <c r="I256" s="32" t="n"/>
       <c r="J256" s="32" t="n"/>
       <c r="K256" s="32" t="n"/>
+      <c r="L256" s="32" t="n"/>
     </row>
     <row r="257" ht="15.75" customHeight="1" s="27">
       <c r="B257" s="26" t="n"/>
@@ -4993,6 +5269,7 @@
       <c r="I257" s="32" t="n"/>
       <c r="J257" s="32" t="n"/>
       <c r="K257" s="32" t="n"/>
+      <c r="L257" s="32" t="n"/>
     </row>
     <row r="258" ht="15.75" customHeight="1" s="27">
       <c r="B258" s="26" t="n"/>
@@ -5001,6 +5278,7 @@
       <c r="I258" s="32" t="n"/>
       <c r="J258" s="32" t="n"/>
       <c r="K258" s="32" t="n"/>
+      <c r="L258" s="32" t="n"/>
     </row>
     <row r="259" ht="15.75" customHeight="1" s="27">
       <c r="B259" s="26" t="n"/>
@@ -5009,6 +5287,7 @@
       <c r="I259" s="32" t="n"/>
       <c r="J259" s="32" t="n"/>
       <c r="K259" s="32" t="n"/>
+      <c r="L259" s="32" t="n"/>
     </row>
     <row r="260" ht="15.75" customHeight="1" s="27">
       <c r="B260" s="26" t="n"/>
@@ -5017,6 +5296,7 @@
       <c r="I260" s="32" t="n"/>
       <c r="J260" s="32" t="n"/>
       <c r="K260" s="32" t="n"/>
+      <c r="L260" s="32" t="n"/>
     </row>
     <row r="261" ht="15.75" customHeight="1" s="27">
       <c r="B261" s="26" t="n"/>
@@ -5025,6 +5305,7 @@
       <c r="I261" s="32" t="n"/>
       <c r="J261" s="32" t="n"/>
       <c r="K261" s="32" t="n"/>
+      <c r="L261" s="32" t="n"/>
     </row>
     <row r="262" ht="15.75" customHeight="1" s="27">
       <c r="B262" s="26" t="n"/>
@@ -5033,6 +5314,7 @@
       <c r="I262" s="32" t="n"/>
       <c r="J262" s="32" t="n"/>
       <c r="K262" s="32" t="n"/>
+      <c r="L262" s="32" t="n"/>
     </row>
     <row r="263" ht="15.75" customHeight="1" s="27">
       <c r="B263" s="26" t="n"/>
@@ -5041,6 +5323,7 @@
       <c r="I263" s="32" t="n"/>
       <c r="J263" s="32" t="n"/>
       <c r="K263" s="32" t="n"/>
+      <c r="L263" s="32" t="n"/>
     </row>
     <row r="264" ht="15.75" customHeight="1" s="27">
       <c r="B264" s="26" t="n"/>
@@ -5049,6 +5332,7 @@
       <c r="I264" s="32" t="n"/>
       <c r="J264" s="32" t="n"/>
       <c r="K264" s="32" t="n"/>
+      <c r="L264" s="32" t="n"/>
     </row>
     <row r="265" ht="15.75" customHeight="1" s="27">
       <c r="B265" s="26" t="n"/>
@@ -5057,6 +5341,7 @@
       <c r="I265" s="32" t="n"/>
       <c r="J265" s="32" t="n"/>
       <c r="K265" s="32" t="n"/>
+      <c r="L265" s="32" t="n"/>
     </row>
     <row r="266" ht="15.75" customHeight="1" s="27">
       <c r="B266" s="26" t="n"/>
@@ -5065,6 +5350,7 @@
       <c r="I266" s="32" t="n"/>
       <c r="J266" s="32" t="n"/>
       <c r="K266" s="32" t="n"/>
+      <c r="L266" s="32" t="n"/>
     </row>
     <row r="267" ht="15.75" customHeight="1" s="27">
       <c r="B267" s="26" t="n"/>
@@ -5073,6 +5359,7 @@
       <c r="I267" s="32" t="n"/>
       <c r="J267" s="32" t="n"/>
       <c r="K267" s="32" t="n"/>
+      <c r="L267" s="32" t="n"/>
     </row>
     <row r="268" ht="15.75" customHeight="1" s="27">
       <c r="B268" s="26" t="n"/>
@@ -5081,6 +5368,7 @@
       <c r="I268" s="32" t="n"/>
       <c r="J268" s="32" t="n"/>
       <c r="K268" s="32" t="n"/>
+      <c r="L268" s="32" t="n"/>
     </row>
     <row r="269" ht="15.75" customHeight="1" s="27">
       <c r="B269" s="26" t="n"/>
@@ -5089,6 +5377,7 @@
       <c r="I269" s="32" t="n"/>
       <c r="J269" s="32" t="n"/>
       <c r="K269" s="32" t="n"/>
+      <c r="L269" s="32" t="n"/>
     </row>
     <row r="270" ht="15.75" customHeight="1" s="27">
       <c r="B270" s="26" t="n"/>
@@ -5097,6 +5386,7 @@
       <c r="I270" s="32" t="n"/>
       <c r="J270" s="32" t="n"/>
       <c r="K270" s="32" t="n"/>
+      <c r="L270" s="32" t="n"/>
     </row>
     <row r="271" ht="15.75" customHeight="1" s="27">
       <c r="B271" s="26" t="n"/>
@@ -5105,6 +5395,7 @@
       <c r="I271" s="32" t="n"/>
       <c r="J271" s="32" t="n"/>
       <c r="K271" s="32" t="n"/>
+      <c r="L271" s="32" t="n"/>
     </row>
     <row r="272" ht="15.75" customHeight="1" s="27">
       <c r="B272" s="26" t="n"/>
@@ -5113,6 +5404,7 @@
       <c r="I272" s="32" t="n"/>
       <c r="J272" s="32" t="n"/>
       <c r="K272" s="32" t="n"/>
+      <c r="L272" s="32" t="n"/>
     </row>
     <row r="273" ht="15.75" customHeight="1" s="27">
       <c r="B273" s="26" t="n"/>
@@ -5121,6 +5413,7 @@
       <c r="I273" s="32" t="n"/>
       <c r="J273" s="32" t="n"/>
       <c r="K273" s="32" t="n"/>
+      <c r="L273" s="32" t="n"/>
     </row>
     <row r="274" ht="15.75" customHeight="1" s="27">
       <c r="B274" s="26" t="n"/>
@@ -5129,6 +5422,7 @@
       <c r="I274" s="32" t="n"/>
       <c r="J274" s="32" t="n"/>
       <c r="K274" s="32" t="n"/>
+      <c r="L274" s="32" t="n"/>
     </row>
     <row r="275" ht="15.75" customHeight="1" s="27">
       <c r="B275" s="26" t="n"/>
@@ -5137,6 +5431,7 @@
       <c r="I275" s="32" t="n"/>
       <c r="J275" s="32" t="n"/>
       <c r="K275" s="32" t="n"/>
+      <c r="L275" s="32" t="n"/>
     </row>
     <row r="276" ht="15.75" customHeight="1" s="27">
       <c r="B276" s="26" t="n"/>
@@ -5145,6 +5440,7 @@
       <c r="I276" s="32" t="n"/>
       <c r="J276" s="32" t="n"/>
       <c r="K276" s="32" t="n"/>
+      <c r="L276" s="32" t="n"/>
     </row>
     <row r="277" ht="15.75" customHeight="1" s="27">
       <c r="B277" s="26" t="n"/>
@@ -5153,6 +5449,7 @@
       <c r="I277" s="32" t="n"/>
       <c r="J277" s="32" t="n"/>
       <c r="K277" s="32" t="n"/>
+      <c r="L277" s="32" t="n"/>
     </row>
     <row r="278" ht="15.75" customHeight="1" s="27">
       <c r="B278" s="26" t="n"/>
@@ -5161,6 +5458,7 @@
       <c r="I278" s="32" t="n"/>
       <c r="J278" s="32" t="n"/>
       <c r="K278" s="32" t="n"/>
+      <c r="L278" s="32" t="n"/>
     </row>
     <row r="279" ht="15.75" customHeight="1" s="27">
       <c r="B279" s="26" t="n"/>
@@ -5169,6 +5467,7 @@
       <c r="I279" s="32" t="n"/>
       <c r="J279" s="32" t="n"/>
       <c r="K279" s="32" t="n"/>
+      <c r="L279" s="32" t="n"/>
     </row>
     <row r="280" ht="15.75" customHeight="1" s="27">
       <c r="B280" s="26" t="n"/>
@@ -5177,6 +5476,7 @@
       <c r="I280" s="32" t="n"/>
       <c r="J280" s="32" t="n"/>
       <c r="K280" s="32" t="n"/>
+      <c r="L280" s="32" t="n"/>
     </row>
     <row r="281" ht="15.75" customHeight="1" s="27">
       <c r="B281" s="26" t="n"/>
@@ -5185,6 +5485,7 @@
       <c r="I281" s="32" t="n"/>
       <c r="J281" s="32" t="n"/>
       <c r="K281" s="32" t="n"/>
+      <c r="L281" s="32" t="n"/>
     </row>
     <row r="282" ht="15.75" customHeight="1" s="27">
       <c r="B282" s="26" t="n"/>
@@ -5193,6 +5494,7 @@
       <c r="I282" s="32" t="n"/>
       <c r="J282" s="32" t="n"/>
       <c r="K282" s="32" t="n"/>
+      <c r="L282" s="32" t="n"/>
     </row>
     <row r="283" ht="15.75" customHeight="1" s="27">
       <c r="B283" s="26" t="n"/>
@@ -5201,6 +5503,7 @@
       <c r="I283" s="32" t="n"/>
       <c r="J283" s="32" t="n"/>
       <c r="K283" s="32" t="n"/>
+      <c r="L283" s="32" t="n"/>
     </row>
     <row r="284" ht="15.75" customHeight="1" s="27">
       <c r="B284" s="26" t="n"/>
@@ -5209,6 +5512,7 @@
       <c r="I284" s="32" t="n"/>
       <c r="J284" s="32" t="n"/>
       <c r="K284" s="32" t="n"/>
+      <c r="L284" s="32" t="n"/>
     </row>
     <row r="285" ht="15.75" customHeight="1" s="27">
       <c r="B285" s="26" t="n"/>
@@ -5217,6 +5521,7 @@
       <c r="I285" s="32" t="n"/>
       <c r="J285" s="32" t="n"/>
       <c r="K285" s="32" t="n"/>
+      <c r="L285" s="32" t="n"/>
     </row>
     <row r="286" ht="15.75" customHeight="1" s="27">
       <c r="B286" s="26" t="n"/>
@@ -5225,6 +5530,7 @@
       <c r="I286" s="32" t="n"/>
       <c r="J286" s="32" t="n"/>
       <c r="K286" s="32" t="n"/>
+      <c r="L286" s="32" t="n"/>
     </row>
     <row r="287" ht="15.75" customHeight="1" s="27">
       <c r="B287" s="26" t="n"/>
@@ -5233,6 +5539,7 @@
       <c r="I287" s="32" t="n"/>
       <c r="J287" s="32" t="n"/>
       <c r="K287" s="32" t="n"/>
+      <c r="L287" s="32" t="n"/>
     </row>
     <row r="288" ht="15.75" customHeight="1" s="27">
       <c r="B288" s="26" t="n"/>
@@ -5241,6 +5548,7 @@
       <c r="I288" s="32" t="n"/>
       <c r="J288" s="32" t="n"/>
       <c r="K288" s="32" t="n"/>
+      <c r="L288" s="32" t="n"/>
     </row>
     <row r="289" ht="15.75" customHeight="1" s="27">
       <c r="B289" s="26" t="n"/>
@@ -5249,6 +5557,7 @@
       <c r="I289" s="32" t="n"/>
       <c r="J289" s="32" t="n"/>
       <c r="K289" s="32" t="n"/>
+      <c r="L289" s="32" t="n"/>
     </row>
     <row r="290" ht="15.75" customHeight="1" s="27">
       <c r="B290" s="26" t="n"/>
@@ -5257,6 +5566,7 @@
       <c r="I290" s="32" t="n"/>
       <c r="J290" s="32" t="n"/>
       <c r="K290" s="32" t="n"/>
+      <c r="L290" s="32" t="n"/>
     </row>
     <row r="291" ht="15.75" customHeight="1" s="27">
       <c r="B291" s="26" t="n"/>
@@ -5265,6 +5575,7 @@
       <c r="I291" s="32" t="n"/>
       <c r="J291" s="32" t="n"/>
       <c r="K291" s="32" t="n"/>
+      <c r="L291" s="32" t="n"/>
     </row>
     <row r="292" ht="15.75" customHeight="1" s="27">
       <c r="B292" s="26" t="n"/>
@@ -5273,6 +5584,7 @@
       <c r="I292" s="32" t="n"/>
       <c r="J292" s="32" t="n"/>
       <c r="K292" s="32" t="n"/>
+      <c r="L292" s="32" t="n"/>
     </row>
     <row r="293" ht="15.75" customHeight="1" s="27">
       <c r="B293" s="26" t="n"/>
@@ -5281,6 +5593,7 @@
       <c r="I293" s="32" t="n"/>
       <c r="J293" s="32" t="n"/>
       <c r="K293" s="32" t="n"/>
+      <c r="L293" s="32" t="n"/>
     </row>
     <row r="294" ht="15.75" customHeight="1" s="27">
       <c r="B294" s="26" t="n"/>
@@ -5289,6 +5602,7 @@
       <c r="I294" s="32" t="n"/>
       <c r="J294" s="32" t="n"/>
       <c r="K294" s="32" t="n"/>
+      <c r="L294" s="32" t="n"/>
     </row>
     <row r="295" ht="15.75" customHeight="1" s="27">
       <c r="B295" s="26" t="n"/>
@@ -5297,6 +5611,7 @@
       <c r="I295" s="32" t="n"/>
       <c r="J295" s="32" t="n"/>
       <c r="K295" s="32" t="n"/>
+      <c r="L295" s="32" t="n"/>
     </row>
     <row r="296" ht="15.75" customHeight="1" s="27">
       <c r="B296" s="26" t="n"/>
@@ -5305,6 +5620,7 @@
       <c r="I296" s="32" t="n"/>
       <c r="J296" s="32" t="n"/>
       <c r="K296" s="32" t="n"/>
+      <c r="L296" s="32" t="n"/>
     </row>
     <row r="297" ht="15.75" customHeight="1" s="27">
       <c r="B297" s="26" t="n"/>
@@ -5313,6 +5629,7 @@
       <c r="I297" s="32" t="n"/>
       <c r="J297" s="32" t="n"/>
       <c r="K297" s="32" t="n"/>
+      <c r="L297" s="32" t="n"/>
     </row>
     <row r="298" ht="15.75" customHeight="1" s="27">
       <c r="B298" s="26" t="n"/>
@@ -5321,6 +5638,7 @@
       <c r="I298" s="32" t="n"/>
       <c r="J298" s="32" t="n"/>
       <c r="K298" s="32" t="n"/>
+      <c r="L298" s="32" t="n"/>
     </row>
     <row r="299" ht="15.75" customHeight="1" s="27">
       <c r="B299" s="26" t="n"/>
@@ -5329,6 +5647,7 @@
       <c r="I299" s="32" t="n"/>
       <c r="J299" s="32" t="n"/>
       <c r="K299" s="32" t="n"/>
+      <c r="L299" s="32" t="n"/>
     </row>
     <row r="300" ht="15.75" customHeight="1" s="27">
       <c r="B300" s="26" t="n"/>
@@ -5337,6 +5656,7 @@
       <c r="I300" s="32" t="n"/>
       <c r="J300" s="32" t="n"/>
       <c r="K300" s="32" t="n"/>
+      <c r="L300" s="32" t="n"/>
     </row>
     <row r="301" ht="15.75" customHeight="1" s="27">
       <c r="B301" s="26" t="n"/>
@@ -5345,6 +5665,7 @@
       <c r="I301" s="32" t="n"/>
       <c r="J301" s="32" t="n"/>
       <c r="K301" s="32" t="n"/>
+      <c r="L301" s="32" t="n"/>
     </row>
     <row r="302" ht="15.75" customHeight="1" s="27"/>
     <row r="303" ht="15.75" customHeight="1" s="27"/>
@@ -6095,292 +6416,292 @@
       </c>
     </row>
     <row r="2" ht="33.75" customHeight="1" s="27">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>Fan / filter cleaning  •  Alarm &amp; fault-history review  •  DC / AC terminal torque check  •  Insulation resistance reading  •  Firmware / communication health</t>
         </is>
       </c>
     </row>
     <row r="3" ht="33.75" customHeight="1" s="27">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Piling and Foundation</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Foundation inspection  •  Pile condition check  •  Settlement / alignment check  •  Crack / damage inspection  •  Corrective action review</t>
         </is>
       </c>
     </row>
     <row r="4" ht="33.75" customHeight="1" s="27">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>WMS</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Sensor cleaning  •  Irradiance / temperature sensor validation  •  Communication check  •  Calibration comparison  •  Mounting / cable inspection</t>
         </is>
       </c>
     </row>
     <row r="5" ht="33.75" customHeight="1" s="27">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>ACCB Panel</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Breaker operation check  •  Busbar / terminal thermal scan  •  Protection &amp; metering check  •  Cable gland / lug inspection  •  Panel cleaning</t>
         </is>
       </c>
     </row>
     <row r="6" ht="33.75" customHeight="1" s="27">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>VCB Panel</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Breaker mechanical operation  •  Contact / terminal inspection  •  Relay &amp; trip-circuit test  •  Spring charging mechanism  •  Interlock / indication check</t>
         </is>
       </c>
     </row>
     <row r="7" ht="33.75" customHeight="1" s="27">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>MCCB</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Visual / thermal inspection  •  Terminal tightening  •  Trip and manual operation test  •  Rating / label verification  •  Panel cleaning</t>
         </is>
       </c>
     </row>
     <row r="8" ht="33.75" customHeight="1" s="27">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Transformer</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Oil level / leakage inspection  •  BDV / moisture / DGA test as scheduled  •  Bushing &amp; breather inspection  •  Protection / temperature checks  •  Earthing &amp; terminal tightening</t>
         </is>
       </c>
     </row>
     <row r="9" ht="33.75" customHeight="1" s="27">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Aux. Transformer</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>Oil / enclosure inspection  •  Bushing &amp; cable check  •  Voltage / current reading  •  Protection check  •  Earthing continuity</t>
         </is>
       </c>
     </row>
     <row r="10" ht="33.75" customHeight="1" s="27">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>OLTC(RTCC)</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>Tap-changer position / indication check  •  Auto-manual mode operation  •  Control wiring and relay inspection  •  Communication / SCADA signal check  •  Panel cleaning</t>
         </is>
       </c>
     </row>
     <row r="11" ht="33.75" customHeight="1" s="27">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>RMS</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Communication availability  •  Data-gap / timestamp review  •  Router / modem / network check  •  Power / UPS backup check  •  Portal value validation</t>
         </is>
       </c>
     </row>
     <row r="12" ht="33.75" customHeight="1" s="27">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Earthing</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Earth-pit condition  •  Resistance measurement  •  Connection tightening  •  Corrosion check  •  Watering / treatment where applicable</t>
         </is>
       </c>
     </row>
     <row r="13" ht="33.75" customHeight="1" s="27">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>ABT meters</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Meter reading validation  •  RTC / time sync  •  Seal / wiring inspection  •  Communication availability  •  Energy-data reconciliation</t>
         </is>
       </c>
     </row>
     <row r="14" ht="33.75" customHeight="1" s="27">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>LA</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Visual condition  •  Counter reading  •  Connection tightening  •  Earth continuity  •  Post-lightning inspection</t>
         </is>
       </c>
     </row>
     <row r="15" ht="33.75" customHeight="1" s="27">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>CCTV</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Camera feed check  •  Lens / housing cleaning  •  NVR / DVR recording &amp; storage check  •  UPS / network check  •  Coverage / night-vision verification</t>
         </is>
       </c>
     </row>
     <row r="16" ht="33.75" customHeight="1" s="27">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>VCB - GSS side</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>Breaker mechanical operation  •  Contact / terminal inspection  •  Relay &amp; trip-circuit test  •  Spring charging mechanism  •  Interlock / indication check</t>
         </is>
       </c>
     </row>
     <row r="17" ht="33.75" customHeight="1" s="27">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>4 Pole</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>Structure and foundation inspection  •  Insulator / jumper inspection  •  Earthing connection check  •  Hardware tightening  •  Hotspot / corona inspection</t>
         </is>
       </c>
     </row>
     <row r="18" ht="33.75" customHeight="1" s="27">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Transmission line</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Line patrol  •  Conductor / sag inspection  •  Insulator / jumper inspection  •  Tower / pole / foundation inspection  •  Vegetation &amp; ROW clearance</t>
         </is>
       </c>
     </row>
     <row r="19" ht="33.75" customHeight="1" s="27">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>Boundary wall</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Wall / fencing patrol  •  Crack / settlement inspection  •  Gate / access check  •  Breach / damage repair review  •  Drainage / erosion observation</t>
         </is>
       </c>
     </row>
     <row r="20" ht="33.75" customHeight="1" s="27">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>Water pipe line</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>Leak / blockage inspection  •  Pump / valve operation  •  Pressure / flow observation  •  Joint / support inspection  •  Repair / flushing requirement</t>
         </is>
       </c>
     </row>
     <row r="21" ht="33.75" customHeight="1" s="27">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>Vegetation</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Grass / weed cutting  •  Module shading check  •  Fire-risk / dry biomass removal  •  ROW / access clearing  •  Waste disposal</t>
         </is>
       </c>
     </row>
     <row r="22" ht="33.75" customHeight="1" s="27">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>Street Light</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>Fixture operation  •  Timer / controller check  •  Cable / pole inspection  •  Earthing check  •  Night operation verification</t>
         </is>
       </c>
     </row>
     <row r="23" ht="33.75" customHeight="1" s="27">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>BIKE</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>Bike Not Starting  •  Accident / Body Damage  •  Functional check  •  Engine Problem  •  Corrective action review</t>
         </is>
       </c>
     </row>
     <row r="24" ht="33.75" customHeight="1" s="27">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>Define task-specific checklist  •  Capture measurements / readings  •  Attach photo / video evidence  •  Record remarks / anomalies  •  Escalate problem to Issue if required</t>
         </is>
       </c>
     </row>
     <row r="25" ht="33.75" customHeight="1" s="27">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="7" t="n"/>
+      <c r="A25" s="28" t="n"/>
+      <c r="B25" s="29" t="n"/>
     </row>
     <row r="26" ht="33.75" customHeight="1" s="27">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="7" t="n"/>
+      <c r="A26" s="28" t="n"/>
+      <c r="B26" s="29" t="n"/>
     </row>
     <row r="27" ht="33.75" customHeight="1" s="27">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="7" t="n"/>
+      <c r="A27" s="28" t="n"/>
+      <c r="B27" s="29" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="27"/>
     <row r="29" ht="15.75" customHeight="1" s="27"/>
@@ -7367,7 +7688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="28" customWidth="1" style="27" min="1" max="3"/>

--- a/frontend/static/templates/PM_Task_Plan_Template.xlsx
+++ b/frontend/static/templates/PM_Task_Plan_Template.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:C24"/>
+  <dimension ref="B2:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3" customWidth="1" style="27" min="1" max="1"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="C11" s="29" t="inlineStr">
         <is>
-          <t>First date the task is due. Type as DD-MM-YYYY or YYYY-MM-DD. Next dates are calculated from Frequency.</t>
+          <t>First date the task is due. Type as DD-MM-YYYY or YYYY-MM-DD. Next dates are calculated from Frequency. When the upload is set to follow the 30-day PM cycle, this is the cycle start (day 1) and the portal sets each equipment's dates from its turn: Plant side Inverter days 1-7, ACCB Panel + MCCB 8-9, VCB Panel 10-11, Transformer (IDT) 12-13, Aux. Transformer 14-15, 4 Pole 16-17, Earthing 18-19, other equipment 20-22, Transmission line 23-24; GSS side VCB 25-26, 4 Pole 27-28, Transmission line 29-30. Leave blank to use the cycle start chosen in the portal.</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="30" customHeight="1" s="27">
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -6369,7 +6368,7 @@
   </sheetData>
   <dataValidations count="5">
     <dataValidation sqref="A2:A301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=Lists!$A$2:$A$24</formula1>
+      <formula1>=Lists!$A$2:$A$26</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$B$2:$B$7</formula1>
@@ -7884,50 +7883,58 @@
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>Boundary wall</t>
+          <t>4 Pole - GSS side</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
         <is>
-          <t>Water pipe line</t>
+          <t>Transmission line - GSS side</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="27">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>Vegetation</t>
+          <t>Boundary wall</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="27">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>Street Light</t>
+          <t>Water pipe line</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="27">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>Vegetation</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="27">
       <c r="A24" s="23" t="inlineStr">
         <is>
+          <t>Street Light</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="27">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="27">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" s="27">
-      <c r="A25" s="23" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" s="27">
-      <c r="A26" s="23" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="27">
       <c r="A27" s="23" t="n"/>

--- a/frontend/static/templates/PM_Task_Plan_Template.xlsx
+++ b/frontend/static/templates/PM_Task_Plan_Template.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C11" s="29" t="inlineStr">
         <is>
-          <t>First date the task is due. Type as DD-MM-YYYY or YYYY-MM-DD. Next dates are calculated from Frequency. When the upload is set to follow the 30-day PM cycle, this is the cycle start (day 1) and the portal sets each equipment's dates from its turn: Plant side Inverter days 1-7, ACCB Panel + MCCB 8-9, VCB Panel 10-11, Transformer (IDT) 12-13, Aux. Transformer 14-15, 4 Pole 16-17, Earthing 18-19, other equipment 20-22, Transmission line 23-24; GSS side VCB 25-26, 4 Pole 27-28, Transmission line 29-30. Leave blank to use the cycle start chosen in the portal.</t>
+          <t>First date the task is due. Type as DD-MM-YYYY or YYYY-MM-DD. Next dates are calculated from Frequency. When the upload is set to follow the 30-day PM cycle, this is the cycle start (day 1) and the portal sets each equipment's dates from its turn: Plant side Inverter days 1-7, ACCB Panel 8-9, VCB Panel 10-11, Transformer (IDT) 12-13, Aux. Transformer + ACDB 14-15, 4 Pole 16-17, Earthing 18-19, Miscellaneous (Street Light, ERT, …) and other equipment 20-22, Transmission line 23-24; GSS side VCB 25-26, 4 Pole 27-28, Transmission line 29-30. Leave blank to use the cycle start chosen in the portal.</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="C15" s="29" t="inlineStr">
         <is>
-          <t>How many units of this equipment the plant has (e.g. 10 inverters). Leave blank to use the plant's saved Unit configuration or the Equipment Register.</t>
+          <t>How many units of this equipment the plant has (e.g. 10 inverters). Leave blank to use the plant's saved Unit configuration or the Equipment Register. ACCB Panel (ACCB-1 + ACCB-2), Aux. Transformer, ACDB and Miscellaneous are always one job per plant, whatever the number. MCCB is no longer part of Preventive Maintenance.</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>What is going on right now, in plain words (e.g. 'Spare filters ordered; fans at INV-04 noisy'). Added to the log of every task the row creates.</t>
+          <t>What is going on right now, in plain words (e.g. 'Spare filters ordered; fans at INV-04 noisy'). Added to the log of every task the row creates. For Miscellaneous, list the items the job covers, e.g. Street Light, ERT.</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
   </sheetData>
   <dataValidations count="5">
     <dataValidation sqref="A2:A301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=Lists!$A$2:$A$26</formula1>
+      <formula1>=Lists!$A$2:$A$27</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$B$2:$B$7</formula1>
@@ -6477,36 +6477,36 @@
     <row r="7" ht="33.75" customHeight="1" s="27">
       <c r="A7" s="28" t="inlineStr">
         <is>
-          <t>MCCB</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>Visual / thermal inspection  •  Terminal tightening  •  Trip and manual operation test  •  Rating / label verification  •  Panel cleaning</t>
+          <t>Oil level / leakage inspection  •  BDV / moisture / DGA test as scheduled  •  Bushing &amp; breather inspection  •  Protection / temperature checks  •  Earthing &amp; terminal tightening</t>
         </is>
       </c>
     </row>
     <row r="8" ht="33.75" customHeight="1" s="27">
       <c r="A8" s="28" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Aux. Transformer</t>
         </is>
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>Oil level / leakage inspection  •  BDV / moisture / DGA test as scheduled  •  Bushing &amp; breather inspection  •  Protection / temperature checks  •  Earthing &amp; terminal tightening</t>
+          <t>Oil / enclosure inspection  •  Bushing &amp; cable check  •  Voltage / current reading  •  Protection check  •  Earthing continuity</t>
         </is>
       </c>
     </row>
     <row r="9" ht="33.75" customHeight="1" s="27">
       <c r="A9" s="28" t="inlineStr">
         <is>
-          <t>Aux. Transformer</t>
+          <t>ACDB</t>
         </is>
       </c>
       <c r="B9" s="29" t="inlineStr">
         <is>
-          <t>Oil / enclosure inspection  •  Bushing &amp; cable check  •  Voltage / current reading  •  Protection check  •  Earthing continuity</t>
+          <t>Incomer / outgoing breaker operation  ·  Busbar / terminal thermal scan  ·  Cable / lug tightening  ·  Indication / metering check  ·  Panel cleaning</t>
         </is>
       </c>
     </row>
@@ -6549,150 +6549,158 @@
     <row r="13" ht="33.75" customHeight="1" s="27">
       <c r="A13" s="28" t="inlineStr">
         <is>
-          <t>ABT meters</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="B13" s="29" t="inlineStr">
         <is>
-          <t>Meter reading validation  •  RTC / time sync  •  Seal / wiring inspection  •  Communication availability  •  Energy-data reconciliation</t>
+          <t>One job per plant for the small items: Street Light  ·  ERT  ·  any other item. Name the items in Remarks.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="33.75" customHeight="1" s="27">
       <c r="A14" s="28" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>ABT meters</t>
         </is>
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>Visual condition  •  Counter reading  •  Connection tightening  •  Earth continuity  •  Post-lightning inspection</t>
+          <t>Meter reading validation  •  RTC / time sync  •  Seal / wiring inspection  •  Communication availability  •  Energy-data reconciliation</t>
         </is>
       </c>
     </row>
     <row r="15" ht="33.75" customHeight="1" s="27">
       <c r="A15" s="28" t="inlineStr">
         <is>
-          <t>CCTV</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Camera feed check  •  Lens / housing cleaning  •  NVR / DVR recording &amp; storage check  •  UPS / network check  •  Coverage / night-vision verification</t>
+          <t>Visual condition  •  Counter reading  •  Connection tightening  •  Earth continuity  •  Post-lightning inspection</t>
         </is>
       </c>
     </row>
     <row r="16" ht="33.75" customHeight="1" s="27">
       <c r="A16" s="28" t="inlineStr">
         <is>
-          <t>VCB - GSS side</t>
+          <t>CCTV</t>
         </is>
       </c>
       <c r="B16" s="29" t="inlineStr">
         <is>
-          <t>Breaker mechanical operation  •  Contact / terminal inspection  •  Relay &amp; trip-circuit test  •  Spring charging mechanism  •  Interlock / indication check</t>
+          <t>Camera feed check  •  Lens / housing cleaning  •  NVR / DVR recording &amp; storage check  •  UPS / network check  •  Coverage / night-vision verification</t>
         </is>
       </c>
     </row>
     <row r="17" ht="33.75" customHeight="1" s="27">
       <c r="A17" s="28" t="inlineStr">
         <is>
-          <t>4 Pole</t>
+          <t>VCB - GSS side</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t>Structure and foundation inspection  •  Insulator / jumper inspection  •  Earthing connection check  •  Hardware tightening  •  Hotspot / corona inspection</t>
+          <t>Breaker mechanical operation  •  Contact / terminal inspection  •  Relay &amp; trip-circuit test  •  Spring charging mechanism  •  Interlock / indication check</t>
         </is>
       </c>
     </row>
     <row r="18" ht="33.75" customHeight="1" s="27">
       <c r="A18" s="28" t="inlineStr">
         <is>
-          <t>Transmission line</t>
+          <t>4 Pole</t>
         </is>
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>Line patrol  •  Conductor / sag inspection  •  Insulator / jumper inspection  •  Tower / pole / foundation inspection  •  Vegetation &amp; ROW clearance</t>
+          <t>Structure and foundation inspection  •  Insulator / jumper inspection  •  Earthing connection check  •  Hardware tightening  •  Hotspot / corona inspection</t>
         </is>
       </c>
     </row>
     <row r="19" ht="33.75" customHeight="1" s="27">
       <c r="A19" s="28" t="inlineStr">
         <is>
-          <t>Boundary wall</t>
+          <t>Transmission line</t>
         </is>
       </c>
       <c r="B19" s="29" t="inlineStr">
         <is>
-          <t>Wall / fencing patrol  •  Crack / settlement inspection  •  Gate / access check  •  Breach / damage repair review  •  Drainage / erosion observation</t>
+          <t>Line patrol  •  Conductor / sag inspection  •  Insulator / jumper inspection  •  Tower / pole / foundation inspection  •  Vegetation &amp; ROW clearance</t>
         </is>
       </c>
     </row>
     <row r="20" ht="33.75" customHeight="1" s="27">
       <c r="A20" s="28" t="inlineStr">
         <is>
-          <t>Water pipe line</t>
+          <t>Boundary wall</t>
         </is>
       </c>
       <c r="B20" s="29" t="inlineStr">
         <is>
-          <t>Leak / blockage inspection  •  Pump / valve operation  •  Pressure / flow observation  •  Joint / support inspection  •  Repair / flushing requirement</t>
+          <t>Wall / fencing patrol  •  Crack / settlement inspection  •  Gate / access check  •  Breach / damage repair review  •  Drainage / erosion observation</t>
         </is>
       </c>
     </row>
     <row r="21" ht="33.75" customHeight="1" s="27">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>Vegetation</t>
+          <t>Water pipe line</t>
         </is>
       </c>
       <c r="B21" s="29" t="inlineStr">
         <is>
-          <t>Grass / weed cutting  •  Module shading check  •  Fire-risk / dry biomass removal  •  ROW / access clearing  •  Waste disposal</t>
+          <t>Leak / blockage inspection  •  Pump / valve operation  •  Pressure / flow observation  •  Joint / support inspection  •  Repair / flushing requirement</t>
         </is>
       </c>
     </row>
     <row r="22" ht="33.75" customHeight="1" s="27">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>Street Light</t>
+          <t>Vegetation</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
         <is>
-          <t>Fixture operation  •  Timer / controller check  •  Cable / pole inspection  •  Earthing check  •  Night operation verification</t>
+          <t>Grass / weed cutting  •  Module shading check  •  Fire-risk / dry biomass removal  •  ROW / access clearing  •  Waste disposal</t>
         </is>
       </c>
     </row>
     <row r="23" ht="33.75" customHeight="1" s="27">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>Street Light</t>
         </is>
       </c>
       <c r="B23" s="29" t="inlineStr">
         <is>
-          <t>Bike Not Starting  •  Accident / Body Damage  •  Functional check  •  Engine Problem  •  Corrective action review</t>
+          <t>Fixture operation  •  Timer / controller check  •  Cable / pole inspection  •  Earthing check  •  Night operation verification</t>
         </is>
       </c>
     </row>
     <row r="24" ht="33.75" customHeight="1" s="27">
       <c r="A24" s="28" t="inlineStr">
         <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>Bike Not Starting  •  Accident / Body Damage  •  Functional check  •  Engine Problem  •  Corrective action review</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="33.75" customHeight="1" s="27">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>Define task-specific checklist  •  Capture measurements / readings  •  Attach photo / video evidence  •  Record remarks / anomalies  •  Escalate problem to Issue if required</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="33.75" customHeight="1" s="27">
-      <c r="A25" s="28" t="n"/>
-      <c r="B25" s="29" t="n"/>
     </row>
     <row r="26" ht="33.75" customHeight="1" s="27">
       <c r="A26" s="28" t="n"/>
@@ -7794,7 +7802,7 @@
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>MCCB</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="B7" s="23" t="inlineStr">
@@ -7806,14 +7814,14 @@
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Aux. Transformer</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>Aux. Transformer</t>
+          <t>ACDB</t>
         </is>
       </c>
     </row>
@@ -7841,103 +7849,107 @@
     <row r="13">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>ABT meters</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>ABT meters</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>CCTV</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
         <is>
-          <t>VCB - GSS side</t>
+          <t>CCTV</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>4 Pole</t>
+          <t>VCB - GSS side</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>Transmission line</t>
+          <t>4 Pole</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>4 Pole - GSS side</t>
+          <t>Transmission line</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
         <is>
-          <t>Transmission line - GSS side</t>
+          <t>4 Pole - GSS side</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="27">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>Boundary wall</t>
+          <t>Transmission line - GSS side</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="27">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>Water pipe line</t>
+          <t>Boundary wall</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="27">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>Vegetation</t>
+          <t>Water pipe line</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="27">
       <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>Street Light</t>
+          <t>Vegetation</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="27">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>Street Light</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="27">
       <c r="A26" s="23" t="inlineStr">
         <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" s="27">
-      <c r="A27" s="23" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="27"/>
     <row r="29" ht="15.75" customHeight="1" s="27"/>
